--- a/data/empresas/[GRUPO] Consolidado Terra Parent/map_balance.xlsx
+++ b/data/empresas/[GRUPO] Consolidado Terra Parent/map_balance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4059" uniqueCount="1644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4003" uniqueCount="1641">
   <si>
     <t>N° de Cuenta</t>
   </si>
@@ -28,7 +28,7 @@
     <t>nota 1</t>
   </si>
   <si>
-    <t>nota 2</t>
+    <t>Unnamed: 4</t>
   </si>
   <si>
     <t>Unnamed: 5</t>
@@ -2080,6 +2080,9 @@
     <t>3106107</t>
   </si>
   <si>
+    <t>3107101</t>
+  </si>
+  <si>
     <t>3108103</t>
   </si>
   <si>
@@ -2359,9 +2362,6 @@
     <t>9999999</t>
   </si>
   <si>
-    <t>32107101</t>
-  </si>
-  <si>
     <t>Ganancias/pérdidas no distribuidas</t>
   </si>
   <si>
@@ -4336,6 +4336,9 @@
     <t>COSTO POR VENTA MATERIAL A TERCEROS</t>
   </si>
   <si>
+    <t>COSTO FACTURADO POR PROVEEDORES</t>
+  </si>
+  <si>
     <t>GANANCIA EN INSTRUMENTOS DE COBERTURA</t>
   </si>
   <si>
@@ -4609,9 +4612,6 @@
     <t>CUENTA PUENTE CARGA INICIAL</t>
   </si>
   <si>
-    <t>COSTO FACTURADO POR PROVEEDORES</t>
-  </si>
-  <si>
     <t>Resultados acumulados</t>
   </si>
   <si>
@@ -4744,7 +4744,7 @@
     <t>Deudores varios</t>
   </si>
   <si>
-    <t>Bodega en transito</t>
+    <t>Bodega central (*)</t>
   </si>
   <si>
     <t>DB Terra Chile Parent SpA</t>
@@ -4753,12 +4753,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>Mercaderías</t>
-  </si>
-  <si>
-    <t>Deterioro por obsolescencia de materiales</t>
-  </si>
-  <si>
     <t>IVA crédito fiscal</t>
   </si>
   <si>
@@ -4888,13 +4882,10 @@
     <t>Yuan</t>
   </si>
   <si>
+    <t>Licencias</t>
+  </si>
+  <si>
     <t>Activo fijo bruto</t>
-  </si>
-  <si>
-    <t>Depreciación acumulada</t>
-  </si>
-  <si>
-    <t>Licencias</t>
   </si>
   <si>
     <t>x</t>
@@ -5335,7 +5326,7 @@
         <v>1559</v>
       </c>
       <c r="M2" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5352,10 +5343,10 @@
         <v>1560</v>
       </c>
       <c r="E3" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M3" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5372,10 +5363,10 @@
         <v>1560</v>
       </c>
       <c r="E4" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M4" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5392,10 +5383,10 @@
         <v>1560</v>
       </c>
       <c r="E5" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M5" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5412,10 +5403,10 @@
         <v>1560</v>
       </c>
       <c r="E6" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M6" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5432,10 +5423,10 @@
         <v>1561</v>
       </c>
       <c r="E7" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M7" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5452,10 +5443,10 @@
         <v>1561</v>
       </c>
       <c r="E8" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M8" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5472,10 +5463,10 @@
         <v>1561</v>
       </c>
       <c r="E9" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M9" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5492,10 +5483,10 @@
         <v>1561</v>
       </c>
       <c r="E10" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M10" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5512,10 +5503,10 @@
         <v>1562</v>
       </c>
       <c r="E11" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M11" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5532,10 +5523,10 @@
         <v>1562</v>
       </c>
       <c r="E12" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M12" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5552,10 +5543,10 @@
         <v>1562</v>
       </c>
       <c r="E13" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M13" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -5572,10 +5563,10 @@
         <v>1562</v>
       </c>
       <c r="E14" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M14" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5592,10 +5583,10 @@
         <v>1562</v>
       </c>
       <c r="E15" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M15" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5612,10 +5603,10 @@
         <v>1562</v>
       </c>
       <c r="E16" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M16" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5632,10 +5623,10 @@
         <v>1562</v>
       </c>
       <c r="E17" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M17" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5652,10 +5643,10 @@
         <v>1562</v>
       </c>
       <c r="E18" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M18" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -5672,10 +5663,10 @@
         <v>1562</v>
       </c>
       <c r="E19" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M19" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -5692,10 +5683,10 @@
         <v>1562</v>
       </c>
       <c r="E20" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M20" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -5712,10 +5703,10 @@
         <v>1562</v>
       </c>
       <c r="E21" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M21" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -5732,10 +5723,10 @@
         <v>1562</v>
       </c>
       <c r="E22" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M22" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -5752,10 +5743,10 @@
         <v>1562</v>
       </c>
       <c r="E23" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M23" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -5772,10 +5763,10 @@
         <v>1562</v>
       </c>
       <c r="E24" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M24" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -5792,10 +5783,10 @@
         <v>1562</v>
       </c>
       <c r="E25" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M25" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -5812,10 +5803,10 @@
         <v>1562</v>
       </c>
       <c r="E26" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M26" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -5832,10 +5823,10 @@
         <v>1562</v>
       </c>
       <c r="E27" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M27" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5852,10 +5843,10 @@
         <v>1562</v>
       </c>
       <c r="E28" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M28" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -5872,10 +5863,10 @@
         <v>1562</v>
       </c>
       <c r="E29" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M29" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -5892,10 +5883,10 @@
         <v>1562</v>
       </c>
       <c r="E30" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M30" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5912,10 +5903,10 @@
         <v>1562</v>
       </c>
       <c r="E31" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M31" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -5932,10 +5923,10 @@
         <v>1562</v>
       </c>
       <c r="E32" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M32" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -5952,10 +5943,10 @@
         <v>1562</v>
       </c>
       <c r="E33" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M33" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -5972,10 +5963,10 @@
         <v>1562</v>
       </c>
       <c r="E34" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M34" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -5992,10 +5983,10 @@
         <v>1562</v>
       </c>
       <c r="E35" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M35" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -6012,10 +6003,10 @@
         <v>1562</v>
       </c>
       <c r="E36" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M36" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -6032,10 +6023,10 @@
         <v>1562</v>
       </c>
       <c r="E37" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M37" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6052,10 +6043,10 @@
         <v>1562</v>
       </c>
       <c r="E38" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M38" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -6072,10 +6063,10 @@
         <v>1562</v>
       </c>
       <c r="E39" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M39" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -6092,10 +6083,10 @@
         <v>1562</v>
       </c>
       <c r="E40" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M40" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -6112,10 +6103,10 @@
         <v>1562</v>
       </c>
       <c r="E41" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M41" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -6132,10 +6123,10 @@
         <v>1562</v>
       </c>
       <c r="E42" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M42" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6152,10 +6143,10 @@
         <v>1562</v>
       </c>
       <c r="E43" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M43" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6172,10 +6163,10 @@
         <v>1562</v>
       </c>
       <c r="E44" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M44" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6192,10 +6183,10 @@
         <v>1562</v>
       </c>
       <c r="E45" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M45" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -6212,10 +6203,10 @@
         <v>1562</v>
       </c>
       <c r="E46" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M46" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -6232,10 +6223,10 @@
         <v>1562</v>
       </c>
       <c r="E47" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M47" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6252,10 +6243,10 @@
         <v>1562</v>
       </c>
       <c r="E48" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M48" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6272,10 +6263,10 @@
         <v>1562</v>
       </c>
       <c r="E49" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M49" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6292,10 +6283,10 @@
         <v>1562</v>
       </c>
       <c r="E50" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M50" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6312,10 +6303,10 @@
         <v>1562</v>
       </c>
       <c r="E51" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M51" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6332,10 +6323,10 @@
         <v>1562</v>
       </c>
       <c r="E52" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M52" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6352,10 +6343,10 @@
         <v>1562</v>
       </c>
       <c r="E53" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M53" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6372,10 +6363,10 @@
         <v>1562</v>
       </c>
       <c r="E54" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M54" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6392,10 +6383,10 @@
         <v>1562</v>
       </c>
       <c r="E55" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M55" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6412,10 +6403,10 @@
         <v>1562</v>
       </c>
       <c r="E56" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M56" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -6432,10 +6423,10 @@
         <v>1563</v>
       </c>
       <c r="E57" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M57" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6452,10 +6443,10 @@
         <v>1561</v>
       </c>
       <c r="E58" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M58" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -6472,10 +6463,10 @@
         <v>1561</v>
       </c>
       <c r="E59" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M59" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -6492,7 +6483,7 @@
         <v>1564</v>
       </c>
       <c r="M60" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6509,7 +6500,7 @@
         <v>1564</v>
       </c>
       <c r="M61" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6526,7 +6517,7 @@
         <v>1564</v>
       </c>
       <c r="M62" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6540,7 +6531,7 @@
         <v>1533</v>
       </c>
       <c r="M63" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6557,7 +6548,7 @@
         <v>1564</v>
       </c>
       <c r="M64" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6574,7 +6565,7 @@
         <v>1565</v>
       </c>
       <c r="M65" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6591,7 +6582,7 @@
         <v>1566</v>
       </c>
       <c r="M66" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6608,7 +6599,7 @@
         <v>1567</v>
       </c>
       <c r="M67" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6625,7 +6616,7 @@
         <v>1567</v>
       </c>
       <c r="M68" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6642,7 +6633,7 @@
         <v>1567</v>
       </c>
       <c r="M69" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6659,7 +6650,7 @@
         <v>1567</v>
       </c>
       <c r="M70" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6676,7 +6667,7 @@
         <v>1567</v>
       </c>
       <c r="M71" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -6693,7 +6684,7 @@
         <v>1567</v>
       </c>
       <c r="M72" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -6710,7 +6701,7 @@
         <v>1567</v>
       </c>
       <c r="M73" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -6727,7 +6718,7 @@
         <v>1567</v>
       </c>
       <c r="M74" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -6744,7 +6735,7 @@
         <v>1568</v>
       </c>
       <c r="M75" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -6761,7 +6752,7 @@
         <v>1568</v>
       </c>
       <c r="M76" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -6778,7 +6769,7 @@
         <v>1569</v>
       </c>
       <c r="M77" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6795,7 +6786,7 @@
         <v>1569</v>
       </c>
       <c r="M78" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -6812,7 +6803,7 @@
         <v>1570</v>
       </c>
       <c r="M79" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -6829,7 +6820,7 @@
         <v>1570</v>
       </c>
       <c r="M80" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -6846,7 +6837,7 @@
         <v>1567</v>
       </c>
       <c r="M81" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -6863,7 +6854,7 @@
         <v>1571</v>
       </c>
       <c r="M82" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6880,10 +6871,10 @@
         <v>1572</v>
       </c>
       <c r="E83" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M83" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -6900,7 +6891,7 @@
         <v>1567</v>
       </c>
       <c r="M84" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -6917,7 +6908,7 @@
         <v>1570</v>
       </c>
       <c r="M85" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -6934,7 +6925,7 @@
         <v>1570</v>
       </c>
       <c r="M86" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -6951,7 +6942,7 @@
         <v>1573</v>
       </c>
       <c r="M87" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -6968,10 +6959,10 @@
         <v>1572</v>
       </c>
       <c r="E88" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M88" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -6988,7 +6979,7 @@
         <v>1573</v>
       </c>
       <c r="M89" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7005,7 +6996,7 @@
         <v>1573</v>
       </c>
       <c r="M90" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7022,7 +7013,7 @@
         <v>1570</v>
       </c>
       <c r="M91" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7039,7 +7030,7 @@
         <v>1571</v>
       </c>
       <c r="M92" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7056,10 +7047,10 @@
         <v>1574</v>
       </c>
       <c r="E93" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M93" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7076,10 +7067,10 @@
         <v>1572</v>
       </c>
       <c r="E94" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M94" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7096,10 +7087,10 @@
         <v>1572</v>
       </c>
       <c r="E95" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M95" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7116,10 +7107,10 @@
         <v>1574</v>
       </c>
       <c r="E96" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="M96" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -7136,10 +7127,10 @@
         <v>1574</v>
       </c>
       <c r="E97" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M97" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7156,7 +7147,7 @@
         <v>1575</v>
       </c>
       <c r="M98" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -7176,7 +7167,7 @@
         <v>1578</v>
       </c>
       <c r="M99" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -7193,10 +7184,10 @@
         <v>1574</v>
       </c>
       <c r="E100" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="M100" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -7212,11 +7203,8 @@
       <c r="D101" t="s">
         <v>1576</v>
       </c>
-      <c r="E101" t="s">
-        <v>1578</v>
-      </c>
       <c r="M101" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -7232,11 +7220,8 @@
       <c r="D102" t="s">
         <v>1576</v>
       </c>
-      <c r="E102" t="s">
-        <v>1578</v>
-      </c>
       <c r="M102" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -7252,11 +7237,8 @@
       <c r="D103" t="s">
         <v>1576</v>
       </c>
-      <c r="E103" t="s">
-        <v>1578</v>
-      </c>
       <c r="M103" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -7272,11 +7254,8 @@
       <c r="D104" t="s">
         <v>1576</v>
       </c>
-      <c r="E104" t="s">
-        <v>1578</v>
-      </c>
       <c r="M104" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -7290,7 +7269,7 @@
         <v>1538</v>
       </c>
       <c r="M105" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -7304,7 +7283,7 @@
         <v>1538</v>
       </c>
       <c r="M106" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -7318,7 +7297,7 @@
         <v>1538</v>
       </c>
       <c r="M107" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -7332,7 +7311,7 @@
         <v>1538</v>
       </c>
       <c r="M108" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -7349,7 +7328,7 @@
         <v>1577</v>
       </c>
       <c r="M109" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -7363,7 +7342,7 @@
         <v>1539</v>
       </c>
       <c r="M110" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -7383,7 +7362,7 @@
         <v>1578</v>
       </c>
       <c r="M111" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -7400,7 +7379,7 @@
         <v>1577</v>
       </c>
       <c r="M112" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -7414,7 +7393,7 @@
         <v>1538</v>
       </c>
       <c r="M113" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -7431,7 +7410,7 @@
         <v>1577</v>
       </c>
       <c r="M114" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -7445,10 +7424,10 @@
         <v>1537</v>
       </c>
       <c r="D115" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M115" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -7462,10 +7441,10 @@
         <v>1537</v>
       </c>
       <c r="D116" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M116" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -7479,10 +7458,10 @@
         <v>1537</v>
       </c>
       <c r="D117" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M117" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -7496,10 +7475,10 @@
         <v>1537</v>
       </c>
       <c r="D118" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M118" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -7513,13 +7492,10 @@
         <v>1537</v>
       </c>
       <c r="D119" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E119" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M119" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -7533,13 +7509,10 @@
         <v>1537</v>
       </c>
       <c r="D120" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E120" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M120" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -7553,13 +7526,10 @@
         <v>1537</v>
       </c>
       <c r="D121" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E121" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M121" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -7573,13 +7543,10 @@
         <v>1537</v>
       </c>
       <c r="D122" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E122" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M122" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -7593,13 +7560,10 @@
         <v>1537</v>
       </c>
       <c r="D123" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E123" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M123" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -7613,13 +7577,10 @@
         <v>1537</v>
       </c>
       <c r="D124" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E124" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M124" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -7633,13 +7594,10 @@
         <v>1537</v>
       </c>
       <c r="D125" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M125" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -7653,13 +7611,10 @@
         <v>1537</v>
       </c>
       <c r="D126" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E126" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M126" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -7673,13 +7628,10 @@
         <v>1537</v>
       </c>
       <c r="D127" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E127" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M127" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -7693,13 +7645,10 @@
         <v>1537</v>
       </c>
       <c r="D128" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E128" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M128" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -7713,13 +7662,10 @@
         <v>1537</v>
       </c>
       <c r="D129" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="M129" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -7733,10 +7679,10 @@
         <v>1537</v>
       </c>
       <c r="D130" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M130" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -7750,10 +7696,10 @@
         <v>1537</v>
       </c>
       <c r="D131" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="M131" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -7767,10 +7713,10 @@
         <v>1537</v>
       </c>
       <c r="D132" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M132" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -7784,10 +7730,10 @@
         <v>1537</v>
       </c>
       <c r="D133" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M133" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -7801,10 +7747,10 @@
         <v>1537</v>
       </c>
       <c r="D134" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M134" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -7818,10 +7764,10 @@
         <v>1537</v>
       </c>
       <c r="D135" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M135" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -7835,10 +7781,10 @@
         <v>1537</v>
       </c>
       <c r="D136" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M136" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -7855,7 +7801,7 @@
         <v>1576</v>
       </c>
       <c r="M137" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -7872,7 +7818,7 @@
         <v>1576</v>
       </c>
       <c r="M138" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -7886,10 +7832,10 @@
         <v>1537</v>
       </c>
       <c r="D139" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M139" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -7903,10 +7849,10 @@
         <v>1540</v>
       </c>
       <c r="D140" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M140" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -7920,10 +7866,10 @@
         <v>1541</v>
       </c>
       <c r="D141" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M141" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -7937,10 +7883,10 @@
         <v>1540</v>
       </c>
       <c r="D142" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="M142" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -7954,10 +7900,10 @@
         <v>1540</v>
       </c>
       <c r="D143" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="M143" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -7971,10 +7917,10 @@
         <v>1540</v>
       </c>
       <c r="D144" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="M144" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -7988,10 +7934,10 @@
         <v>1540</v>
       </c>
       <c r="D145" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="M145" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -8005,7 +7951,7 @@
         <v>1542</v>
       </c>
       <c r="M146" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -8019,7 +7965,7 @@
         <v>1542</v>
       </c>
       <c r="M147" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -8033,10 +7979,10 @@
         <v>1543</v>
       </c>
       <c r="D148" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="M148" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -8050,10 +7996,10 @@
         <v>1543</v>
       </c>
       <c r="D149" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="M149" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -8067,10 +8013,10 @@
         <v>1543</v>
       </c>
       <c r="D150" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="M150" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -8084,10 +8030,10 @@
         <v>1543</v>
       </c>
       <c r="D151" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="M151" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -8098,13 +8044,13 @@
         <v>924</v>
       </c>
       <c r="C152" t="s">
-        <v>1534</v>
-      </c>
-      <c r="D152" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E152" t="s">
         <v>1565</v>
       </c>
       <c r="M152" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -8118,10 +8064,10 @@
         <v>1543</v>
       </c>
       <c r="D153" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="M153" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -8135,7 +8081,7 @@
         <v>1544</v>
       </c>
       <c r="M154" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -8149,7 +8095,7 @@
         <v>1544</v>
       </c>
       <c r="M155" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -8163,7 +8109,7 @@
         <v>1544</v>
       </c>
       <c r="M156" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -8177,7 +8123,7 @@
         <v>1544</v>
       </c>
       <c r="M157" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -8191,13 +8137,13 @@
         <v>1543</v>
       </c>
       <c r="D158" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="E158" t="s">
         <v>1578</v>
       </c>
       <c r="M158" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -8214,7 +8160,7 @@
         <v>1566</v>
       </c>
       <c r="M159" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -8228,10 +8174,10 @@
         <v>1545</v>
       </c>
       <c r="D160" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="M160" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -8245,10 +8191,10 @@
         <v>1546</v>
       </c>
       <c r="D161" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="M161" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -8262,13 +8208,13 @@
         <v>1546</v>
       </c>
       <c r="D162" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="E162" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="M162" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -8282,10 +8228,10 @@
         <v>1546</v>
       </c>
       <c r="D163" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="M163" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -8299,10 +8245,10 @@
         <v>1546</v>
       </c>
       <c r="D164" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="M164" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -8316,10 +8262,10 @@
         <v>1546</v>
       </c>
       <c r="D165" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="M165" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -8333,10 +8279,10 @@
         <v>1546</v>
       </c>
       <c r="D166" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="M166" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -8350,16 +8296,13 @@
         <v>1547</v>
       </c>
       <c r="D167" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E167" t="s">
+        <v>1584</v>
+      </c>
+      <c r="L167" t="s">
         <v>1624</v>
       </c>
-      <c r="L167" t="s">
-        <v>1627</v>
-      </c>
       <c r="M167" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -8373,16 +8316,13 @@
         <v>1547</v>
       </c>
       <c r="D168" t="s">
-        <v>1587</v>
-      </c>
-      <c r="E168" t="s">
+        <v>1585</v>
+      </c>
+      <c r="L168" t="s">
         <v>1624</v>
       </c>
-      <c r="L168" t="s">
-        <v>1627</v>
-      </c>
       <c r="M168" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -8396,16 +8336,13 @@
         <v>1547</v>
       </c>
       <c r="D169" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E169" t="s">
+        <v>1586</v>
+      </c>
+      <c r="L169" t="s">
         <v>1624</v>
       </c>
-      <c r="L169" t="s">
-        <v>1627</v>
-      </c>
       <c r="M169" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -8419,16 +8356,13 @@
         <v>1547</v>
       </c>
       <c r="D170" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E170" t="s">
+        <v>1586</v>
+      </c>
+      <c r="L170" t="s">
         <v>1624</v>
       </c>
-      <c r="L170" t="s">
-        <v>1627</v>
-      </c>
       <c r="M170" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -8442,16 +8376,13 @@
         <v>1547</v>
       </c>
       <c r="D171" t="s">
-        <v>1589</v>
-      </c>
-      <c r="E171" t="s">
+        <v>1587</v>
+      </c>
+      <c r="L171" t="s">
         <v>1624</v>
       </c>
-      <c r="L171" t="s">
-        <v>1627</v>
-      </c>
       <c r="M171" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="172" spans="1:13">
@@ -8465,16 +8396,13 @@
         <v>1547</v>
       </c>
       <c r="D172" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E172" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L172" t="s">
         <v>1624</v>
       </c>
-      <c r="L172" t="s">
-        <v>1627</v>
-      </c>
       <c r="M172" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -8488,16 +8416,13 @@
         <v>1547</v>
       </c>
       <c r="D173" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E173" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L173" t="s">
         <v>1624</v>
       </c>
-      <c r="L173" t="s">
-        <v>1627</v>
-      </c>
       <c r="M173" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -8511,16 +8436,13 @@
         <v>1547</v>
       </c>
       <c r="D174" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E174" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L174" t="s">
         <v>1624</v>
       </c>
-      <c r="L174" t="s">
-        <v>1627</v>
-      </c>
       <c r="M174" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -8534,16 +8456,13 @@
         <v>1547</v>
       </c>
       <c r="D175" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E175" t="s">
+        <v>1586</v>
+      </c>
+      <c r="L175" t="s">
         <v>1624</v>
       </c>
-      <c r="L175" t="s">
-        <v>1627</v>
-      </c>
       <c r="M175" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -8557,16 +8476,13 @@
         <v>1547</v>
       </c>
       <c r="D176" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E176" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L176" t="s">
         <v>1624</v>
       </c>
-      <c r="L176" t="s">
-        <v>1627</v>
-      </c>
       <c r="M176" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -8580,16 +8496,13 @@
         <v>1547</v>
       </c>
       <c r="D177" t="s">
-        <v>1591</v>
-      </c>
-      <c r="E177" t="s">
+        <v>1589</v>
+      </c>
+      <c r="L177" t="s">
         <v>1624</v>
       </c>
-      <c r="L177" t="s">
-        <v>1627</v>
-      </c>
       <c r="M177" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -8603,16 +8516,13 @@
         <v>1547</v>
       </c>
       <c r="D178" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E178" t="s">
+        <v>1590</v>
+      </c>
+      <c r="L178" t="s">
         <v>1624</v>
       </c>
-      <c r="L178" t="s">
-        <v>1627</v>
-      </c>
       <c r="M178" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -8626,16 +8536,13 @@
         <v>1547</v>
       </c>
       <c r="D179" t="s">
-        <v>1593</v>
-      </c>
-      <c r="E179" t="s">
+        <v>1591</v>
+      </c>
+      <c r="L179" t="s">
         <v>1624</v>
       </c>
-      <c r="L179" t="s">
-        <v>1627</v>
-      </c>
       <c r="M179" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -8649,16 +8556,13 @@
         <v>1547</v>
       </c>
       <c r="D180" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E180" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L180" t="s">
         <v>1624</v>
       </c>
-      <c r="L180" t="s">
-        <v>1627</v>
-      </c>
       <c r="M180" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -8672,16 +8576,13 @@
         <v>1547</v>
       </c>
       <c r="D181" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E181" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L181" t="s">
         <v>1624</v>
       </c>
-      <c r="L181" t="s">
-        <v>1627</v>
-      </c>
       <c r="M181" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -8695,16 +8596,13 @@
         <v>1547</v>
       </c>
       <c r="D182" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E182" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L182" t="s">
         <v>1624</v>
       </c>
-      <c r="L182" t="s">
-        <v>1627</v>
-      </c>
       <c r="M182" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -8718,13 +8616,10 @@
         <v>1547</v>
       </c>
       <c r="D183" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E183" t="s">
-        <v>1624</v>
+        <v>1592</v>
       </c>
       <c r="M183" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -8738,13 +8633,10 @@
         <v>1547</v>
       </c>
       <c r="D184" t="s">
-        <v>1595</v>
-      </c>
-      <c r="E184" t="s">
-        <v>1624</v>
+        <v>1593</v>
       </c>
       <c r="M184" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -8758,13 +8650,10 @@
         <v>1547</v>
       </c>
       <c r="D185" t="s">
-        <v>1596</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1624</v>
+        <v>1594</v>
       </c>
       <c r="M185" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -8778,13 +8667,10 @@
         <v>1547</v>
       </c>
       <c r="D186" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E186" t="s">
-        <v>1624</v>
+        <v>1588</v>
       </c>
       <c r="M186" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -8798,13 +8684,10 @@
         <v>1547</v>
       </c>
       <c r="D187" t="s">
-        <v>1591</v>
-      </c>
-      <c r="E187" t="s">
-        <v>1624</v>
+        <v>1589</v>
       </c>
       <c r="M187" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -8818,13 +8701,10 @@
         <v>1547</v>
       </c>
       <c r="D188" t="s">
-        <v>1597</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1624</v>
+        <v>1595</v>
       </c>
       <c r="M188" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -8838,13 +8718,10 @@
         <v>1547</v>
       </c>
       <c r="D189" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E189" t="s">
-        <v>1624</v>
+        <v>1588</v>
       </c>
       <c r="M189" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -8861,10 +8738,10 @@
         <v>1572</v>
       </c>
       <c r="E190" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M190" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -8881,10 +8758,10 @@
         <v>1574</v>
       </c>
       <c r="E191" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M191" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -8898,13 +8775,10 @@
         <v>1547</v>
       </c>
       <c r="D192" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E192" t="s">
-        <v>1624</v>
+        <v>1588</v>
       </c>
       <c r="M192" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -8917,14 +8791,11 @@
       <c r="C193" t="s">
         <v>1547</v>
       </c>
-      <c r="D193" t="s">
-        <v>1587</v>
-      </c>
       <c r="E193" t="s">
-        <v>1625</v>
+        <v>1585</v>
       </c>
       <c r="M193" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -8937,14 +8808,11 @@
       <c r="C194" t="s">
         <v>1547</v>
       </c>
-      <c r="D194" t="s">
-        <v>1588</v>
-      </c>
       <c r="E194" t="s">
-        <v>1625</v>
+        <v>1586</v>
       </c>
       <c r="M194" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -8957,14 +8825,11 @@
       <c r="C195" t="s">
         <v>1547</v>
       </c>
-      <c r="D195" t="s">
-        <v>1593</v>
-      </c>
       <c r="E195" t="s">
-        <v>1625</v>
+        <v>1591</v>
       </c>
       <c r="M195" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -8977,14 +8842,11 @@
       <c r="C196" t="s">
         <v>1547</v>
       </c>
-      <c r="D196" t="s">
-        <v>1592</v>
-      </c>
       <c r="E196" t="s">
-        <v>1625</v>
+        <v>1590</v>
       </c>
       <c r="M196" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -8997,14 +8859,11 @@
       <c r="C197" t="s">
         <v>1547</v>
       </c>
-      <c r="D197" t="s">
-        <v>1595</v>
-      </c>
       <c r="E197" t="s">
-        <v>1625</v>
+        <v>1593</v>
       </c>
       <c r="M197" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -9017,14 +8876,11 @@
       <c r="C198" t="s">
         <v>1547</v>
       </c>
-      <c r="D198" t="s">
-        <v>1590</v>
-      </c>
       <c r="E198" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M198" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -9037,14 +8893,11 @@
       <c r="C199" t="s">
         <v>1547</v>
       </c>
-      <c r="D199" t="s">
-        <v>1590</v>
-      </c>
       <c r="E199" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M199" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -9057,14 +8910,11 @@
       <c r="C200" t="s">
         <v>1547</v>
       </c>
-      <c r="D200" t="s">
-        <v>1588</v>
-      </c>
       <c r="E200" t="s">
-        <v>1625</v>
+        <v>1586</v>
       </c>
       <c r="M200" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -9077,14 +8927,11 @@
       <c r="C201" t="s">
         <v>1547</v>
       </c>
-      <c r="D201" t="s">
-        <v>1594</v>
-      </c>
       <c r="E201" t="s">
-        <v>1625</v>
+        <v>1592</v>
       </c>
       <c r="M201" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -9097,14 +8944,11 @@
       <c r="C202" t="s">
         <v>1547</v>
       </c>
-      <c r="D202" t="s">
-        <v>1589</v>
-      </c>
       <c r="E202" t="s">
-        <v>1625</v>
+        <v>1587</v>
       </c>
       <c r="M202" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -9117,14 +8961,11 @@
       <c r="C203" t="s">
         <v>1547</v>
       </c>
-      <c r="D203" t="s">
-        <v>1597</v>
-      </c>
       <c r="E203" t="s">
-        <v>1625</v>
+        <v>1595</v>
       </c>
       <c r="M203" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -9137,14 +8978,11 @@
       <c r="C204" t="s">
         <v>1547</v>
       </c>
-      <c r="D204" t="s">
-        <v>1590</v>
-      </c>
       <c r="E204" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M204" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -9157,14 +8995,11 @@
       <c r="C205" t="s">
         <v>1547</v>
       </c>
-      <c r="D205" t="s">
-        <v>1590</v>
-      </c>
       <c r="E205" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M205" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -9177,14 +9012,11 @@
       <c r="C206" t="s">
         <v>1547</v>
       </c>
-      <c r="D206" t="s">
-        <v>1590</v>
-      </c>
       <c r="E206" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M206" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -9197,14 +9029,11 @@
       <c r="C207" t="s">
         <v>1547</v>
       </c>
-      <c r="D207" t="s">
-        <v>1590</v>
-      </c>
       <c r="E207" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M207" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -9217,14 +9046,11 @@
       <c r="C208" t="s">
         <v>1547</v>
       </c>
-      <c r="D208" t="s">
-        <v>1590</v>
-      </c>
       <c r="E208" t="s">
-        <v>1625</v>
+        <v>1588</v>
       </c>
       <c r="M208" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -9237,14 +9063,11 @@
       <c r="C209" t="s">
         <v>1547</v>
       </c>
-      <c r="D209" t="s">
-        <v>1594</v>
-      </c>
       <c r="E209" t="s">
-        <v>1625</v>
+        <v>1592</v>
       </c>
       <c r="M209" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -9258,13 +9081,13 @@
         <v>1543</v>
       </c>
       <c r="D210" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="E210" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="M210" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -9278,13 +9101,13 @@
         <v>1547</v>
       </c>
       <c r="D211" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="E211" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="M211" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -9298,10 +9121,10 @@
         <v>1548</v>
       </c>
       <c r="D212" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="M212" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -9318,7 +9141,7 @@
         <v>1565</v>
       </c>
       <c r="M213" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -9335,7 +9158,7 @@
         <v>1565</v>
       </c>
       <c r="M214" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -9352,7 +9175,7 @@
         <v>1565</v>
       </c>
       <c r="M215" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -9369,7 +9192,7 @@
         <v>1565</v>
       </c>
       <c r="M216" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -9386,7 +9209,7 @@
         <v>1565</v>
       </c>
       <c r="M217" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -9403,7 +9226,7 @@
         <v>1565</v>
       </c>
       <c r="M218" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -9417,10 +9240,10 @@
         <v>1534</v>
       </c>
       <c r="D219" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M219" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -9434,10 +9257,10 @@
         <v>1544</v>
       </c>
       <c r="E220" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M220" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -9454,7 +9277,7 @@
         <v>1565</v>
       </c>
       <c r="M221" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -9468,10 +9291,10 @@
         <v>1544</v>
       </c>
       <c r="E222" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M222" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -9485,10 +9308,10 @@
         <v>1534</v>
       </c>
       <c r="D223" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M223" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -9505,7 +9328,7 @@
         <v>1565</v>
       </c>
       <c r="M224" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -9522,7 +9345,7 @@
         <v>1565</v>
       </c>
       <c r="M225" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -9539,7 +9362,7 @@
         <v>1565</v>
       </c>
       <c r="M226" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -9556,7 +9379,7 @@
         <v>1565</v>
       </c>
       <c r="M227" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -9573,7 +9396,7 @@
         <v>1565</v>
       </c>
       <c r="M228" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -9590,7 +9413,7 @@
         <v>1565</v>
       </c>
       <c r="M229" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -9607,7 +9430,7 @@
         <v>1565</v>
       </c>
       <c r="M230" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -9627,7 +9450,7 @@
         <v>1578</v>
       </c>
       <c r="M231" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -9647,7 +9470,7 @@
         <v>1578</v>
       </c>
       <c r="M232" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -9667,7 +9490,7 @@
         <v>1578</v>
       </c>
       <c r="M233" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -9687,7 +9510,7 @@
         <v>1578</v>
       </c>
       <c r="M234" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -9707,7 +9530,7 @@
         <v>1578</v>
       </c>
       <c r="M235" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -9727,7 +9550,7 @@
         <v>1578</v>
       </c>
       <c r="M236" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -9747,7 +9570,7 @@
         <v>1578</v>
       </c>
       <c r="M237" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -9767,7 +9590,7 @@
         <v>1578</v>
       </c>
       <c r="M238" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -9787,7 +9610,7 @@
         <v>1578</v>
       </c>
       <c r="M239" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -9807,7 +9630,7 @@
         <v>1578</v>
       </c>
       <c r="M240" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -9827,7 +9650,7 @@
         <v>1578</v>
       </c>
       <c r="M241" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -9847,7 +9670,7 @@
         <v>1578</v>
       </c>
       <c r="M242" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -9864,7 +9687,7 @@
         <v>1565</v>
       </c>
       <c r="M243" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -9881,7 +9704,7 @@
         <v>1565</v>
       </c>
       <c r="M244" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -9901,7 +9724,7 @@
         <v>1578</v>
       </c>
       <c r="M245" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -9921,7 +9744,7 @@
         <v>1578</v>
       </c>
       <c r="M246" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -9941,7 +9764,7 @@
         <v>1578</v>
       </c>
       <c r="M247" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -9961,7 +9784,7 @@
         <v>1578</v>
       </c>
       <c r="M248" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -9981,7 +9804,7 @@
         <v>1578</v>
       </c>
       <c r="M249" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -10001,7 +9824,7 @@
         <v>1578</v>
       </c>
       <c r="M250" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="251" spans="1:13">
@@ -10018,7 +9841,7 @@
         <v>1565</v>
       </c>
       <c r="M251" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="252" spans="1:13">
@@ -10035,7 +9858,7 @@
         <v>1565</v>
       </c>
       <c r="M252" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="253" spans="1:13">
@@ -10049,10 +9872,10 @@
         <v>1534</v>
       </c>
       <c r="D253" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M253" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="254" spans="1:13">
@@ -10066,10 +9889,10 @@
         <v>1534</v>
       </c>
       <c r="D254" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M254" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="255" spans="1:13">
@@ -10086,7 +9909,7 @@
         <v>1566</v>
       </c>
       <c r="M255" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="256" spans="1:13">
@@ -10103,7 +9926,7 @@
         <v>1566</v>
       </c>
       <c r="M256" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="257" spans="1:13">
@@ -10117,10 +9940,10 @@
         <v>1534</v>
       </c>
       <c r="D257" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M257" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="258" spans="1:13">
@@ -10134,10 +9957,10 @@
         <v>1534</v>
       </c>
       <c r="D258" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M258" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="259" spans="1:13">
@@ -10151,10 +9974,10 @@
         <v>1534</v>
       </c>
       <c r="D259" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M259" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="260" spans="1:13">
@@ -10168,10 +9991,10 @@
         <v>1534</v>
       </c>
       <c r="D260" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M260" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="261" spans="1:13">
@@ -10185,10 +10008,10 @@
         <v>1534</v>
       </c>
       <c r="D261" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M261" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="262" spans="1:13">
@@ -10202,10 +10025,10 @@
         <v>1534</v>
       </c>
       <c r="D262" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M262" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="263" spans="1:13">
@@ -10219,10 +10042,10 @@
         <v>1549</v>
       </c>
       <c r="D263" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="M263" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="264" spans="1:13">
@@ -10236,10 +10059,10 @@
         <v>1549</v>
       </c>
       <c r="D264" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="M264" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="265" spans="1:13">
@@ -10256,7 +10079,7 @@
         <v>1565</v>
       </c>
       <c r="M265" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="266" spans="1:13">
@@ -10270,10 +10093,10 @@
         <v>1534</v>
       </c>
       <c r="D266" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M266" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="267" spans="1:13">
@@ -10287,10 +10110,10 @@
         <v>1534</v>
       </c>
       <c r="D267" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M267" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="268" spans="1:13">
@@ -10304,13 +10127,13 @@
         <v>1534</v>
       </c>
       <c r="D268" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="E268" t="s">
         <v>1578</v>
       </c>
       <c r="M268" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="269" spans="1:13">
@@ -10324,13 +10147,13 @@
         <v>1534</v>
       </c>
       <c r="D269" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="E269" t="s">
         <v>1578</v>
       </c>
       <c r="M269" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="270" spans="1:13">
@@ -10347,10 +10170,10 @@
         <v>1572</v>
       </c>
       <c r="E270" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M270" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="271" spans="1:13">
@@ -10367,10 +10190,10 @@
         <v>1574</v>
       </c>
       <c r="E271" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M271" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="272" spans="1:13">
@@ -10387,10 +10210,10 @@
         <v>1574</v>
       </c>
       <c r="E272" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="M272" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="273" spans="1:13">
@@ -10407,10 +10230,10 @@
         <v>1572</v>
       </c>
       <c r="E273" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M273" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="274" spans="1:13">
@@ -10427,10 +10250,10 @@
         <v>1574</v>
       </c>
       <c r="E274" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="M274" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="275" spans="1:13">
@@ -10444,10 +10267,10 @@
         <v>1535</v>
       </c>
       <c r="E275" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M275" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="276" spans="1:13">
@@ -10461,13 +10284,13 @@
         <v>1535</v>
       </c>
       <c r="D276" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="E276" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M276" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="277" spans="1:13">
@@ -10481,10 +10304,10 @@
         <v>1550</v>
       </c>
       <c r="D277" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="M277" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="278" spans="1:13">
@@ -10498,10 +10321,10 @@
         <v>1550</v>
       </c>
       <c r="D278" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="M278" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="279" spans="1:13">
@@ -10515,13 +10338,13 @@
         <v>1535</v>
       </c>
       <c r="D279" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="E279" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M279" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="280" spans="1:13">
@@ -10535,13 +10358,13 @@
         <v>1535</v>
       </c>
       <c r="D280" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E280" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M280" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="281" spans="1:13">
@@ -10555,16 +10378,16 @@
         <v>1535</v>
       </c>
       <c r="D281" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E281" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L281" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M281" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="282" spans="1:13">
@@ -10578,16 +10401,16 @@
         <v>1535</v>
       </c>
       <c r="D282" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E282" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L282" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M282" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="283" spans="1:13">
@@ -10601,16 +10424,16 @@
         <v>1535</v>
       </c>
       <c r="D283" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E283" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L283" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M283" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="284" spans="1:13">
@@ -10624,16 +10447,16 @@
         <v>1535</v>
       </c>
       <c r="D284" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E284" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L284" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M284" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="285" spans="1:13">
@@ -10647,16 +10470,16 @@
         <v>1535</v>
       </c>
       <c r="D285" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E285" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L285" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M285" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="286" spans="1:13">
@@ -10670,16 +10493,16 @@
         <v>1535</v>
       </c>
       <c r="D286" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E286" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L286" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M286" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="287" spans="1:13">
@@ -10693,16 +10516,16 @@
         <v>1535</v>
       </c>
       <c r="D287" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E287" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L287" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M287" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="288" spans="1:13">
@@ -10716,13 +10539,13 @@
         <v>1535</v>
       </c>
       <c r="D288" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E288" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M288" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="289" spans="1:13">
@@ -10736,16 +10559,16 @@
         <v>1535</v>
       </c>
       <c r="D289" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E289" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L289" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M289" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="290" spans="1:13">
@@ -10759,16 +10582,16 @@
         <v>1535</v>
       </c>
       <c r="D290" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E290" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L290" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M290" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="291" spans="1:13">
@@ -10782,16 +10605,16 @@
         <v>1535</v>
       </c>
       <c r="D291" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E291" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L291" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M291" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="292" spans="1:13">
@@ -10805,16 +10628,16 @@
         <v>1535</v>
       </c>
       <c r="D292" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E292" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L292" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M292" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="293" spans="1:13">
@@ -10828,10 +10651,10 @@
         <v>1551</v>
       </c>
       <c r="D293" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="M293" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="294" spans="1:13">
@@ -10848,7 +10671,7 @@
         <v>1570</v>
       </c>
       <c r="M294" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="295" spans="1:13">
@@ -10862,16 +10685,16 @@
         <v>1535</v>
       </c>
       <c r="D295" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E295" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L295" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M295" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="296" spans="1:13">
@@ -10885,16 +10708,16 @@
         <v>1535</v>
       </c>
       <c r="D296" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E296" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L296" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M296" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="297" spans="1:13">
@@ -10908,16 +10731,16 @@
         <v>1535</v>
       </c>
       <c r="D297" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E297" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L297" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M297" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="298" spans="1:13">
@@ -10931,16 +10754,16 @@
         <v>1535</v>
       </c>
       <c r="D298" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E298" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L298" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M298" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="299" spans="1:13">
@@ -10954,16 +10777,16 @@
         <v>1535</v>
       </c>
       <c r="D299" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="E299" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L299" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="M299" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="300" spans="1:13">
@@ -10977,13 +10800,13 @@
         <v>1535</v>
       </c>
       <c r="D300" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="E300" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M300" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="301" spans="1:13">
@@ -10997,10 +10820,10 @@
         <v>1537</v>
       </c>
       <c r="D301" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M301" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="302" spans="1:13">
@@ -11014,13 +10837,13 @@
         <v>1535</v>
       </c>
       <c r="D302" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E302" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="M302" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="303" spans="1:13">
@@ -11034,13 +10857,13 @@
         <v>1535</v>
       </c>
       <c r="D303" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E303" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M303" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="304" spans="1:13">
@@ -11054,13 +10877,13 @@
         <v>1535</v>
       </c>
       <c r="D304" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="E304" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M304" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="305" spans="1:13">
@@ -11074,10 +10897,10 @@
         <v>1537</v>
       </c>
       <c r="D305" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M305" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="306" spans="1:13">
@@ -11091,10 +10914,10 @@
         <v>1537</v>
       </c>
       <c r="D306" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="M306" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="307" spans="1:13">
@@ -11108,13 +10931,13 @@
         <v>1535</v>
       </c>
       <c r="D307" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E307" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M307" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="308" spans="1:13">
@@ -11128,13 +10951,13 @@
         <v>1535</v>
       </c>
       <c r="D308" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E308" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M308" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="309" spans="1:13">
@@ -11148,13 +10971,13 @@
         <v>1535</v>
       </c>
       <c r="D309" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E309" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M309" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="310" spans="1:13">
@@ -11168,13 +10991,13 @@
         <v>1535</v>
       </c>
       <c r="D310" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E310" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M310" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="311" spans="1:13">
@@ -11188,10 +11011,10 @@
         <v>1544</v>
       </c>
       <c r="E311" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="M311" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="312" spans="1:13">
@@ -11205,10 +11028,10 @@
         <v>1544</v>
       </c>
       <c r="E312" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="M312" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="313" spans="1:13">
@@ -11225,7 +11048,7 @@
         <v>1577</v>
       </c>
       <c r="M313" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="314" spans="1:13">
@@ -11239,7 +11062,7 @@
         <v>1552</v>
       </c>
       <c r="M314" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="315" spans="1:13">
@@ -11253,7 +11076,7 @@
         <v>1538</v>
       </c>
       <c r="M315" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="316" spans="1:13">
@@ -11270,7 +11093,7 @@
         <v>1577</v>
       </c>
       <c r="M316" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="317" spans="1:13">
@@ -11284,7 +11107,7 @@
         <v>1539</v>
       </c>
       <c r="M317" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="318" spans="1:13">
@@ -11304,7 +11127,7 @@
         <v>1578</v>
       </c>
       <c r="M318" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="319" spans="1:13">
@@ -11321,7 +11144,7 @@
         <v>1577</v>
       </c>
       <c r="M319" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="320" spans="1:13">
@@ -11338,7 +11161,7 @@
         <v>1577</v>
       </c>
       <c r="M320" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="321" spans="1:13">
@@ -11352,10 +11175,10 @@
         <v>1541</v>
       </c>
       <c r="D321" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M321" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="322" spans="1:13">
@@ -11369,10 +11192,10 @@
         <v>1541</v>
       </c>
       <c r="D322" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="M322" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="323" spans="1:13">
@@ -11386,10 +11209,10 @@
         <v>1541</v>
       </c>
       <c r="D323" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="M323" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="324" spans="1:13">
@@ -11403,10 +11226,10 @@
         <v>1541</v>
       </c>
       <c r="D324" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="M324" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="325" spans="1:13">
@@ -11420,10 +11243,10 @@
         <v>1541</v>
       </c>
       <c r="D325" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M325" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="326" spans="1:13">
@@ -11437,10 +11260,10 @@
         <v>1541</v>
       </c>
       <c r="D326" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M326" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="327" spans="1:13">
@@ -11454,10 +11277,10 @@
         <v>1541</v>
       </c>
       <c r="D327" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="M327" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="328" spans="1:13">
@@ -11471,7 +11294,7 @@
         <v>1541</v>
       </c>
       <c r="M328" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="329" spans="1:13">
@@ -11485,10 +11308,10 @@
         <v>1541</v>
       </c>
       <c r="D329" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="M329" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="330" spans="1:13">
@@ -11502,10 +11325,10 @@
         <v>1553</v>
       </c>
       <c r="D330" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="M330" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="331" spans="1:13">
@@ -11519,13 +11342,13 @@
         <v>1535</v>
       </c>
       <c r="D331" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="E331" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M331" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="332" spans="1:13">
@@ -11539,13 +11362,13 @@
         <v>1535</v>
       </c>
       <c r="D332" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="E332" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M332" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="333" spans="1:13">
@@ -11562,7 +11385,7 @@
         <v>1565</v>
       </c>
       <c r="M333" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="334" spans="1:13">
@@ -11579,7 +11402,7 @@
         <v>1565</v>
       </c>
       <c r="M334" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="335" spans="1:13">
@@ -11596,7 +11419,7 @@
         <v>1565</v>
       </c>
       <c r="M335" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="336" spans="1:13">
@@ -11613,7 +11436,7 @@
         <v>1565</v>
       </c>
       <c r="M336" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="337" spans="1:13">
@@ -11630,7 +11453,7 @@
         <v>1565</v>
       </c>
       <c r="M337" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="338" spans="1:13">
@@ -11647,7 +11470,7 @@
         <v>1565</v>
       </c>
       <c r="M338" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="339" spans="1:13">
@@ -11664,7 +11487,7 @@
         <v>1565</v>
       </c>
       <c r="M339" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="340" spans="1:13">
@@ -11681,7 +11504,7 @@
         <v>1565</v>
       </c>
       <c r="M340" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="341" spans="1:13">
@@ -11698,7 +11521,7 @@
         <v>1565</v>
       </c>
       <c r="M341" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="342" spans="1:13">
@@ -11715,7 +11538,7 @@
         <v>1565</v>
       </c>
       <c r="M342" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="343" spans="1:13">
@@ -11732,7 +11555,7 @@
         <v>1565</v>
       </c>
       <c r="M343" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="344" spans="1:13">
@@ -11749,7 +11572,7 @@
         <v>1565</v>
       </c>
       <c r="M344" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="345" spans="1:13">
@@ -11766,7 +11589,7 @@
         <v>1565</v>
       </c>
       <c r="M345" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="346" spans="1:13">
@@ -11783,7 +11606,7 @@
         <v>1565</v>
       </c>
       <c r="M346" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="347" spans="1:13">
@@ -11800,7 +11623,7 @@
         <v>1565</v>
       </c>
       <c r="M347" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="348" spans="1:13">
@@ -11817,7 +11640,7 @@
         <v>1565</v>
       </c>
       <c r="M348" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="349" spans="1:13">
@@ -11834,7 +11657,7 @@
         <v>1565</v>
       </c>
       <c r="M349" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="350" spans="1:13">
@@ -11851,7 +11674,7 @@
         <v>1565</v>
       </c>
       <c r="M350" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="351" spans="1:13">
@@ -11868,7 +11691,7 @@
         <v>1565</v>
       </c>
       <c r="M351" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="352" spans="1:13">
@@ -11885,7 +11708,7 @@
         <v>1565</v>
       </c>
       <c r="M352" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="353" spans="1:13">
@@ -11902,7 +11725,7 @@
         <v>1565</v>
       </c>
       <c r="M353" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="354" spans="1:13">
@@ -11919,7 +11742,7 @@
         <v>1565</v>
       </c>
       <c r="M354" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="355" spans="1:13">
@@ -11936,7 +11759,7 @@
         <v>1565</v>
       </c>
       <c r="M355" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="356" spans="1:13">
@@ -11953,7 +11776,7 @@
         <v>1565</v>
       </c>
       <c r="M356" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="357" spans="1:13">
@@ -11970,7 +11793,7 @@
         <v>1565</v>
       </c>
       <c r="M357" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="358" spans="1:13">
@@ -11987,7 +11810,7 @@
         <v>1565</v>
       </c>
       <c r="M358" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="359" spans="1:13">
@@ -12004,7 +11827,7 @@
         <v>1565</v>
       </c>
       <c r="M359" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="360" spans="1:13">
@@ -12021,7 +11844,7 @@
         <v>1565</v>
       </c>
       <c r="M360" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="361" spans="1:13">
@@ -12038,7 +11861,7 @@
         <v>1565</v>
       </c>
       <c r="M361" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="362" spans="1:13">
@@ -12055,7 +11878,7 @@
         <v>1565</v>
       </c>
       <c r="M362" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="363" spans="1:13">
@@ -12072,7 +11895,7 @@
         <v>1565</v>
       </c>
       <c r="M363" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="364" spans="1:13">
@@ -12089,7 +11912,7 @@
         <v>1565</v>
       </c>
       <c r="M364" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="365" spans="1:13">
@@ -12106,7 +11929,7 @@
         <v>1565</v>
       </c>
       <c r="M365" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="366" spans="1:13">
@@ -12123,7 +11946,7 @@
         <v>1565</v>
       </c>
       <c r="M366" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="367" spans="1:13">
@@ -12140,7 +11963,7 @@
         <v>1565</v>
       </c>
       <c r="M367" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="368" spans="1:13">
@@ -12157,7 +11980,7 @@
         <v>1565</v>
       </c>
       <c r="M368" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="369" spans="1:13">
@@ -12174,7 +11997,7 @@
         <v>1565</v>
       </c>
       <c r="M369" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="370" spans="1:13">
@@ -12191,7 +12014,7 @@
         <v>1565</v>
       </c>
       <c r="M370" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="371" spans="1:13">
@@ -12208,7 +12031,7 @@
         <v>1565</v>
       </c>
       <c r="M371" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="372" spans="1:13">
@@ -12225,7 +12048,7 @@
         <v>1565</v>
       </c>
       <c r="M372" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="373" spans="1:13">
@@ -12242,7 +12065,7 @@
         <v>1565</v>
       </c>
       <c r="M373" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="374" spans="1:13">
@@ -12259,7 +12082,7 @@
         <v>1565</v>
       </c>
       <c r="M374" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="375" spans="1:13">
@@ -12276,7 +12099,7 @@
         <v>1565</v>
       </c>
       <c r="M375" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="376" spans="1:13">
@@ -12293,7 +12116,7 @@
         <v>1565</v>
       </c>
       <c r="M376" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="377" spans="1:13">
@@ -12310,7 +12133,7 @@
         <v>1565</v>
       </c>
       <c r="M377" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="378" spans="1:13">
@@ -12327,7 +12150,7 @@
         <v>1565</v>
       </c>
       <c r="M378" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="379" spans="1:13">
@@ -12344,7 +12167,7 @@
         <v>1565</v>
       </c>
       <c r="M379" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="380" spans="1:13">
@@ -12361,7 +12184,7 @@
         <v>1565</v>
       </c>
       <c r="M380" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="381" spans="1:13">
@@ -12378,7 +12201,7 @@
         <v>1565</v>
       </c>
       <c r="M381" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="382" spans="1:13">
@@ -12395,7 +12218,7 @@
         <v>1565</v>
       </c>
       <c r="M382" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="383" spans="1:13">
@@ -12412,7 +12235,7 @@
         <v>1565</v>
       </c>
       <c r="M383" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="384" spans="1:13">
@@ -12429,7 +12252,7 @@
         <v>1565</v>
       </c>
       <c r="M384" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="385" spans="1:13">
@@ -12446,7 +12269,7 @@
         <v>1565</v>
       </c>
       <c r="M385" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="386" spans="1:13">
@@ -12463,7 +12286,7 @@
         <v>1565</v>
       </c>
       <c r="M386" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="387" spans="1:13">
@@ -12480,7 +12303,7 @@
         <v>1565</v>
       </c>
       <c r="M387" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="388" spans="1:13">
@@ -12497,7 +12320,7 @@
         <v>1565</v>
       </c>
       <c r="M388" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="389" spans="1:13">
@@ -12514,7 +12337,7 @@
         <v>1565</v>
       </c>
       <c r="M389" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="390" spans="1:13">
@@ -12531,7 +12354,7 @@
         <v>1565</v>
       </c>
       <c r="M390" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="391" spans="1:13">
@@ -12545,7 +12368,7 @@
         <v>1544</v>
       </c>
       <c r="M391" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="392" spans="1:13">
@@ -12559,7 +12382,7 @@
         <v>1544</v>
       </c>
       <c r="M392" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="393" spans="1:13">
@@ -12573,7 +12396,7 @@
         <v>1544</v>
       </c>
       <c r="M393" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="394" spans="1:13">
@@ -12587,7 +12410,7 @@
         <v>1544</v>
       </c>
       <c r="M394" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="395" spans="1:13">
@@ -12601,7 +12424,7 @@
         <v>1544</v>
       </c>
       <c r="M395" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="396" spans="1:13">
@@ -12618,7 +12441,7 @@
         <v>1565</v>
       </c>
       <c r="M396" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="397" spans="1:13">
@@ -12635,7 +12458,7 @@
         <v>1565</v>
       </c>
       <c r="M397" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="398" spans="1:13">
@@ -12652,7 +12475,7 @@
         <v>1565</v>
       </c>
       <c r="M398" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="399" spans="1:13">
@@ -12669,7 +12492,7 @@
         <v>1565</v>
       </c>
       <c r="M399" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="400" spans="1:13">
@@ -12683,7 +12506,7 @@
         <v>1544</v>
       </c>
       <c r="M400" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="401" spans="1:13">
@@ -12697,7 +12520,7 @@
         <v>1544</v>
       </c>
       <c r="M401" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="402" spans="1:13">
@@ -12711,7 +12534,7 @@
         <v>1544</v>
       </c>
       <c r="M402" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="403" spans="1:13">
@@ -12725,7 +12548,7 @@
         <v>1544</v>
       </c>
       <c r="M403" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="404" spans="1:13">
@@ -12739,7 +12562,7 @@
         <v>1544</v>
       </c>
       <c r="M404" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="405" spans="1:13">
@@ -12753,7 +12576,7 @@
         <v>1544</v>
       </c>
       <c r="M405" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="406" spans="1:13">
@@ -12770,7 +12593,7 @@
         <v>1565</v>
       </c>
       <c r="M406" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="407" spans="1:13">
@@ -12787,7 +12610,7 @@
         <v>1565</v>
       </c>
       <c r="M407" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="408" spans="1:13">
@@ -12804,7 +12627,7 @@
         <v>1565</v>
       </c>
       <c r="M408" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="409" spans="1:13">
@@ -12821,7 +12644,7 @@
         <v>1565</v>
       </c>
       <c r="M409" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="410" spans="1:13">
@@ -12838,7 +12661,7 @@
         <v>1565</v>
       </c>
       <c r="M410" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="411" spans="1:13">
@@ -12855,7 +12678,7 @@
         <v>1565</v>
       </c>
       <c r="M411" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="412" spans="1:13">
@@ -12872,7 +12695,7 @@
         <v>1565</v>
       </c>
       <c r="M412" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="413" spans="1:13">
@@ -12889,7 +12712,7 @@
         <v>1565</v>
       </c>
       <c r="M413" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="414" spans="1:13">
@@ -12906,7 +12729,7 @@
         <v>1565</v>
       </c>
       <c r="M414" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="415" spans="1:13">
@@ -12923,7 +12746,7 @@
         <v>1565</v>
       </c>
       <c r="M415" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="416" spans="1:13">
@@ -12940,7 +12763,7 @@
         <v>1565</v>
       </c>
       <c r="M416" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="417" spans="1:13">
@@ -12957,7 +12780,7 @@
         <v>1565</v>
       </c>
       <c r="M417" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="418" spans="1:13">
@@ -12974,7 +12797,7 @@
         <v>1565</v>
       </c>
       <c r="M418" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="419" spans="1:13">
@@ -12991,7 +12814,7 @@
         <v>1565</v>
       </c>
       <c r="M419" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="420" spans="1:13">
@@ -13008,7 +12831,7 @@
         <v>1565</v>
       </c>
       <c r="M420" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="421" spans="1:13">
@@ -13025,7 +12848,7 @@
         <v>1565</v>
       </c>
       <c r="M421" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="422" spans="1:13">
@@ -13042,7 +12865,7 @@
         <v>1565</v>
       </c>
       <c r="M422" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="423" spans="1:13">
@@ -13059,7 +12882,7 @@
         <v>1565</v>
       </c>
       <c r="M423" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="424" spans="1:13">
@@ -13076,7 +12899,7 @@
         <v>1565</v>
       </c>
       <c r="M424" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="425" spans="1:13">
@@ -13093,7 +12916,7 @@
         <v>1565</v>
       </c>
       <c r="M425" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="426" spans="1:13">
@@ -13110,7 +12933,7 @@
         <v>1565</v>
       </c>
       <c r="M426" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="427" spans="1:13">
@@ -13127,7 +12950,7 @@
         <v>1565</v>
       </c>
       <c r="M427" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="428" spans="1:13">
@@ -13144,7 +12967,7 @@
         <v>1565</v>
       </c>
       <c r="M428" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="429" spans="1:13">
@@ -13161,7 +12984,7 @@
         <v>1565</v>
       </c>
       <c r="M429" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="430" spans="1:13">
@@ -13178,7 +13001,7 @@
         <v>1565</v>
       </c>
       <c r="M430" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="431" spans="1:13">
@@ -13195,7 +13018,7 @@
         <v>1565</v>
       </c>
       <c r="M431" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="432" spans="1:13">
@@ -13212,7 +13035,7 @@
         <v>1565</v>
       </c>
       <c r="M432" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="433" spans="1:13">
@@ -13229,7 +13052,7 @@
         <v>1565</v>
       </c>
       <c r="M433" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="434" spans="1:13">
@@ -13246,7 +13069,7 @@
         <v>1565</v>
       </c>
       <c r="M434" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="435" spans="1:13">
@@ -13263,7 +13086,7 @@
         <v>1565</v>
       </c>
       <c r="M435" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="436" spans="1:13">
@@ -13280,7 +13103,7 @@
         <v>1565</v>
       </c>
       <c r="M436" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="437" spans="1:13">
@@ -13297,7 +13120,7 @@
         <v>1565</v>
       </c>
       <c r="M437" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="438" spans="1:13">
@@ -13311,10 +13134,10 @@
         <v>1544</v>
       </c>
       <c r="E438" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M438" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="439" spans="1:13">
@@ -13331,7 +13154,7 @@
         <v>1565</v>
       </c>
       <c r="M439" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="440" spans="1:13">
@@ -13348,7 +13171,7 @@
         <v>1565</v>
       </c>
       <c r="M440" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="441" spans="1:13">
@@ -13365,7 +13188,7 @@
         <v>1565</v>
       </c>
       <c r="M441" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="442" spans="1:13">
@@ -13382,7 +13205,7 @@
         <v>1565</v>
       </c>
       <c r="M442" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="443" spans="1:13">
@@ -13399,10 +13222,10 @@
         <v>1565</v>
       </c>
       <c r="E443" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M443" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="444" spans="1:13">
@@ -13419,10 +13242,10 @@
         <v>1565</v>
       </c>
       <c r="E444" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M444" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="445" spans="1:13">
@@ -13439,7 +13262,7 @@
         <v>1565</v>
       </c>
       <c r="M445" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="446" spans="1:13">
@@ -13456,7 +13279,7 @@
         <v>1565</v>
       </c>
       <c r="M446" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="447" spans="1:13">
@@ -13476,7 +13299,7 @@
         <v>1565</v>
       </c>
       <c r="M447" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="448" spans="1:13">
@@ -13496,7 +13319,7 @@
         <v>1565</v>
       </c>
       <c r="M448" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="449" spans="1:13">
@@ -13516,7 +13339,7 @@
         <v>1565</v>
       </c>
       <c r="M449" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="450" spans="1:13">
@@ -13533,10 +13356,10 @@
         <v>1578</v>
       </c>
       <c r="E450" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M450" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="451" spans="1:13">
@@ -13553,7 +13376,7 @@
         <v>1565</v>
       </c>
       <c r="M451" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="452" spans="1:13">
@@ -13573,7 +13396,7 @@
         <v>1565</v>
       </c>
       <c r="M452" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="453" spans="1:13">
@@ -13593,7 +13416,7 @@
         <v>1565</v>
       </c>
       <c r="M453" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="454" spans="1:13">
@@ -13610,7 +13433,7 @@
         <v>1565</v>
       </c>
       <c r="M454" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="455" spans="1:13">
@@ -13627,7 +13450,7 @@
         <v>1565</v>
       </c>
       <c r="M455" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="456" spans="1:13">
@@ -13644,7 +13467,7 @@
         <v>1565</v>
       </c>
       <c r="M456" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="457" spans="1:13">
@@ -13661,7 +13484,7 @@
         <v>1565</v>
       </c>
       <c r="M457" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="458" spans="1:13">
@@ -13678,7 +13501,7 @@
         <v>1565</v>
       </c>
       <c r="M458" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="459" spans="1:13">
@@ -13695,7 +13518,7 @@
         <v>1565</v>
       </c>
       <c r="M459" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="460" spans="1:13">
@@ -13712,7 +13535,7 @@
         <v>1565</v>
       </c>
       <c r="M460" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="461" spans="1:13">
@@ -13729,7 +13552,7 @@
         <v>1566</v>
       </c>
       <c r="M461" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="462" spans="1:13">
@@ -13740,13 +13563,13 @@
         <v>1231</v>
       </c>
       <c r="C462" t="s">
-        <v>1534</v>
-      </c>
-      <c r="D462" t="s">
-        <v>1599</v>
+        <v>1544</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1597</v>
       </c>
       <c r="M462" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="463" spans="1:13">
@@ -13760,10 +13583,10 @@
         <v>1544</v>
       </c>
       <c r="E463" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M463" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="464" spans="1:13">
@@ -13777,10 +13600,10 @@
         <v>1544</v>
       </c>
       <c r="E464" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M464" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="465" spans="1:13">
@@ -13794,7 +13617,7 @@
         <v>1544</v>
       </c>
       <c r="M465" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="466" spans="1:13">
@@ -13808,10 +13631,10 @@
         <v>1544</v>
       </c>
       <c r="E466" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="M466" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="467" spans="1:13">
@@ -13825,13 +13648,13 @@
         <v>1549</v>
       </c>
       <c r="D467" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E467" t="s">
         <v>1578</v>
       </c>
       <c r="M467" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="468" spans="1:13">
@@ -13845,13 +13668,13 @@
         <v>1554</v>
       </c>
       <c r="D468" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E468" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="M468" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="469" spans="1:13">
@@ -13865,13 +13688,13 @@
         <v>1554</v>
       </c>
       <c r="D469" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E469" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="M469" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="470" spans="1:13">
@@ -13885,13 +13708,13 @@
         <v>1554</v>
       </c>
       <c r="D470" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E470" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="M470" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="471" spans="1:13">
@@ -13905,10 +13728,10 @@
         <v>1548</v>
       </c>
       <c r="D471" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="M471" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="472" spans="1:13">
@@ -13925,7 +13748,7 @@
         <v>1555</v>
       </c>
       <c r="M472" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="473" spans="1:13">
@@ -13942,7 +13765,7 @@
         <v>1555</v>
       </c>
       <c r="M473" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="474" spans="1:13">
@@ -13959,7 +13782,7 @@
         <v>1555</v>
       </c>
       <c r="M474" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="475" spans="1:13">
@@ -13976,7 +13799,7 @@
         <v>1559</v>
       </c>
       <c r="M475" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="476" spans="1:13">
@@ -13996,7 +13819,7 @@
         <v>1578</v>
       </c>
       <c r="M476" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="477" spans="1:13">
@@ -14013,7 +13836,7 @@
         <v>1559</v>
       </c>
       <c r="M477" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="478" spans="1:13">
@@ -14030,7 +13853,7 @@
         <v>1558</v>
       </c>
       <c r="M478" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="479" spans="1:13">
@@ -14047,7 +13870,7 @@
         <v>1558</v>
       </c>
       <c r="M479" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="480" spans="1:13">
@@ -14064,7 +13887,7 @@
         <v>1558</v>
       </c>
       <c r="M480" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="481" spans="1:13">
@@ -14081,7 +13904,7 @@
         <v>1559</v>
       </c>
       <c r="M481" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="482" spans="1:13">
@@ -14098,7 +13921,7 @@
         <v>1558</v>
       </c>
       <c r="M482" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="483" spans="1:13">
@@ -14115,7 +13938,7 @@
         <v>1558</v>
       </c>
       <c r="M483" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="484" spans="1:13">
@@ -14132,7 +13955,7 @@
         <v>1558</v>
       </c>
       <c r="M484" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="485" spans="1:13">
@@ -14149,7 +13972,7 @@
         <v>1558</v>
       </c>
       <c r="M485" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="486" spans="1:13">
@@ -14166,7 +13989,7 @@
         <v>1558</v>
       </c>
       <c r="M486" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="487" spans="1:13">
@@ -14183,7 +14006,7 @@
         <v>1558</v>
       </c>
       <c r="M487" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="488" spans="1:13">
@@ -14200,7 +14023,7 @@
         <v>1558</v>
       </c>
       <c r="M488" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="489" spans="1:13">
@@ -14217,7 +14040,7 @@
         <v>1558</v>
       </c>
       <c r="M489" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="490" spans="1:13">
@@ -14234,7 +14057,7 @@
         <v>1559</v>
       </c>
       <c r="M490" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="491" spans="1:13">
@@ -14251,7 +14074,7 @@
         <v>1559</v>
       </c>
       <c r="M491" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="492" spans="1:13">
@@ -14268,7 +14091,7 @@
         <v>1559</v>
       </c>
       <c r="M492" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="493" spans="1:13">
@@ -14285,7 +14108,7 @@
         <v>1559</v>
       </c>
       <c r="M493" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="494" spans="1:13">
@@ -14302,7 +14125,7 @@
         <v>1559</v>
       </c>
       <c r="M494" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="495" spans="1:13">
@@ -14319,7 +14142,7 @@
         <v>1559</v>
       </c>
       <c r="M495" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="496" spans="1:13">
@@ -14336,7 +14159,7 @@
         <v>1559</v>
       </c>
       <c r="M496" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="497" spans="1:13">
@@ -14353,7 +14176,7 @@
         <v>1559</v>
       </c>
       <c r="M497" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="498" spans="1:13">
@@ -14370,7 +14193,7 @@
         <v>1559</v>
       </c>
       <c r="M498" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="499" spans="1:13">
@@ -14387,7 +14210,7 @@
         <v>1559</v>
       </c>
       <c r="M499" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="500" spans="1:13">
@@ -14404,7 +14227,7 @@
         <v>1559</v>
       </c>
       <c r="M500" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="501" spans="1:13">
@@ -14421,7 +14244,7 @@
         <v>1559</v>
       </c>
       <c r="M501" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="502" spans="1:13">
@@ -14438,7 +14261,7 @@
         <v>1559</v>
       </c>
       <c r="M502" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="503" spans="1:13">
@@ -14455,7 +14278,7 @@
         <v>1559</v>
       </c>
       <c r="M503" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="504" spans="1:13">
@@ -14472,7 +14295,7 @@
         <v>1559</v>
       </c>
       <c r="M504" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="505" spans="1:13">
@@ -14489,7 +14312,7 @@
         <v>1559</v>
       </c>
       <c r="M505" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="506" spans="1:13">
@@ -14506,7 +14329,7 @@
         <v>1559</v>
       </c>
       <c r="M506" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="507" spans="1:13">
@@ -14523,7 +14346,7 @@
         <v>1559</v>
       </c>
       <c r="M507" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="508" spans="1:13">
@@ -14540,7 +14363,7 @@
         <v>1559</v>
       </c>
       <c r="M508" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="509" spans="1:13">
@@ -14557,7 +14380,7 @@
         <v>1559</v>
       </c>
       <c r="M509" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="510" spans="1:13">
@@ -14574,7 +14397,7 @@
         <v>1559</v>
       </c>
       <c r="M510" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="511" spans="1:13">
@@ -14591,7 +14414,7 @@
         <v>1559</v>
       </c>
       <c r="M511" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="512" spans="1:13">
@@ -14608,7 +14431,7 @@
         <v>1559</v>
       </c>
       <c r="M512" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="513" spans="1:13">
@@ -14625,7 +14448,7 @@
         <v>1559</v>
       </c>
       <c r="M513" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="514" spans="1:13">
@@ -14642,7 +14465,7 @@
         <v>1559</v>
       </c>
       <c r="M514" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="515" spans="1:13">
@@ -14659,7 +14482,7 @@
         <v>1559</v>
       </c>
       <c r="M515" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="516" spans="1:13">
@@ -14676,7 +14499,7 @@
         <v>1559</v>
       </c>
       <c r="M516" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="517" spans="1:13">
@@ -14693,7 +14516,7 @@
         <v>1559</v>
       </c>
       <c r="M517" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="518" spans="1:13">
@@ -14710,7 +14533,7 @@
         <v>1559</v>
       </c>
       <c r="M518" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="519" spans="1:13">
@@ -14727,7 +14550,7 @@
         <v>1559</v>
       </c>
       <c r="M519" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="520" spans="1:13">
@@ -14744,7 +14567,7 @@
         <v>1559</v>
       </c>
       <c r="M520" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="521" spans="1:13">
@@ -14761,7 +14584,7 @@
         <v>1559</v>
       </c>
       <c r="M521" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="522" spans="1:13">
@@ -14778,7 +14601,7 @@
         <v>1559</v>
       </c>
       <c r="M522" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="523" spans="1:13">
@@ -14795,7 +14618,7 @@
         <v>1559</v>
       </c>
       <c r="M523" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="524" spans="1:13">
@@ -14812,7 +14635,7 @@
         <v>1559</v>
       </c>
       <c r="M524" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="525" spans="1:13">
@@ -14829,7 +14652,7 @@
         <v>1559</v>
       </c>
       <c r="M525" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="526" spans="1:13">
@@ -14846,7 +14669,7 @@
         <v>1559</v>
       </c>
       <c r="M526" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="527" spans="1:13">
@@ -14863,7 +14686,7 @@
         <v>1559</v>
       </c>
       <c r="M527" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="528" spans="1:13">
@@ -14880,7 +14703,7 @@
         <v>1559</v>
       </c>
       <c r="M528" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="529" spans="1:13">
@@ -14897,7 +14720,7 @@
         <v>1559</v>
       </c>
       <c r="M529" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="530" spans="1:13">
@@ -14914,7 +14737,7 @@
         <v>1559</v>
       </c>
       <c r="M530" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="531" spans="1:13">
@@ -14931,7 +14754,7 @@
         <v>1559</v>
       </c>
       <c r="M531" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="532" spans="1:13">
@@ -14948,7 +14771,7 @@
         <v>1559</v>
       </c>
       <c r="M532" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="533" spans="1:13">
@@ -14965,7 +14788,7 @@
         <v>1559</v>
       </c>
       <c r="M533" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="534" spans="1:13">
@@ -14982,7 +14805,7 @@
         <v>1559</v>
       </c>
       <c r="M534" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="535" spans="1:13">
@@ -14999,7 +14822,7 @@
         <v>1559</v>
       </c>
       <c r="M535" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="536" spans="1:13">
@@ -15016,7 +14839,7 @@
         <v>1559</v>
       </c>
       <c r="M536" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="537" spans="1:13">
@@ -15033,7 +14856,7 @@
         <v>1559</v>
       </c>
       <c r="M537" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="538" spans="1:13">
@@ -15050,7 +14873,7 @@
         <v>1559</v>
       </c>
       <c r="M538" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="539" spans="1:13">
@@ -15067,7 +14890,7 @@
         <v>1559</v>
       </c>
       <c r="M539" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="540" spans="1:13">
@@ -15084,7 +14907,7 @@
         <v>1559</v>
       </c>
       <c r="M540" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="541" spans="1:13">
@@ -15101,7 +14924,7 @@
         <v>1559</v>
       </c>
       <c r="M541" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="542" spans="1:13">
@@ -15118,7 +14941,7 @@
         <v>1559</v>
       </c>
       <c r="M542" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="543" spans="1:13">
@@ -15135,7 +14958,7 @@
         <v>1559</v>
       </c>
       <c r="M543" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="544" spans="1:13">
@@ -15152,7 +14975,7 @@
         <v>1559</v>
       </c>
       <c r="M544" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="545" spans="1:13">
@@ -15169,7 +14992,7 @@
         <v>1559</v>
       </c>
       <c r="M545" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="546" spans="1:13">
@@ -15186,7 +15009,7 @@
         <v>1559</v>
       </c>
       <c r="M546" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="547" spans="1:13">
@@ -15203,7 +15026,7 @@
         <v>1559</v>
       </c>
       <c r="M547" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="548" spans="1:13">
@@ -15220,7 +15043,7 @@
         <v>1559</v>
       </c>
       <c r="M548" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="549" spans="1:13">
@@ -15237,7 +15060,7 @@
         <v>1559</v>
       </c>
       <c r="M549" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="550" spans="1:13">
@@ -15254,7 +15077,7 @@
         <v>1559</v>
       </c>
       <c r="M550" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="551" spans="1:13">
@@ -15271,7 +15094,7 @@
         <v>1559</v>
       </c>
       <c r="M551" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="552" spans="1:13">
@@ -15288,7 +15111,7 @@
         <v>1559</v>
       </c>
       <c r="M552" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="553" spans="1:13">
@@ -15305,7 +15128,7 @@
         <v>1559</v>
       </c>
       <c r="M553" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="554" spans="1:13">
@@ -15322,7 +15145,7 @@
         <v>1559</v>
       </c>
       <c r="M554" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="555" spans="1:13">
@@ -15339,7 +15162,7 @@
         <v>1559</v>
       </c>
       <c r="M555" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="556" spans="1:13">
@@ -15356,7 +15179,7 @@
         <v>1559</v>
       </c>
       <c r="M556" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="557" spans="1:13">
@@ -15373,7 +15196,7 @@
         <v>1559</v>
       </c>
       <c r="M557" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="558" spans="1:13">
@@ -15390,7 +15213,7 @@
         <v>1559</v>
       </c>
       <c r="M558" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="559" spans="1:13">
@@ -15407,7 +15230,7 @@
         <v>1559</v>
       </c>
       <c r="M559" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="560" spans="1:13">
@@ -15424,7 +15247,7 @@
         <v>1559</v>
       </c>
       <c r="M560" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="561" spans="1:13">
@@ -15441,7 +15264,7 @@
         <v>1559</v>
       </c>
       <c r="M561" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="562" spans="1:13">
@@ -15458,7 +15281,7 @@
         <v>1559</v>
       </c>
       <c r="M562" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="563" spans="1:13">
@@ -15475,7 +15298,7 @@
         <v>1559</v>
       </c>
       <c r="M563" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="564" spans="1:13">
@@ -15492,7 +15315,7 @@
         <v>1559</v>
       </c>
       <c r="M564" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="565" spans="1:13">
@@ -15509,7 +15332,7 @@
         <v>1559</v>
       </c>
       <c r="M565" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="566" spans="1:13">
@@ -15526,7 +15349,7 @@
         <v>1559</v>
       </c>
       <c r="M566" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="567" spans="1:13">
@@ -15543,7 +15366,7 @@
         <v>1559</v>
       </c>
       <c r="M567" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="568" spans="1:13">
@@ -15560,7 +15383,7 @@
         <v>1559</v>
       </c>
       <c r="M568" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="569" spans="1:13">
@@ -15577,7 +15400,7 @@
         <v>1559</v>
       </c>
       <c r="M569" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="570" spans="1:13">
@@ -15594,7 +15417,7 @@
         <v>1559</v>
       </c>
       <c r="M570" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="571" spans="1:13">
@@ -15611,7 +15434,7 @@
         <v>1559</v>
       </c>
       <c r="M571" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="572" spans="1:13">
@@ -15628,7 +15451,7 @@
         <v>1559</v>
       </c>
       <c r="M572" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="573" spans="1:13">
@@ -15645,7 +15468,7 @@
         <v>1559</v>
       </c>
       <c r="M573" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="574" spans="1:13">
@@ -15662,7 +15485,7 @@
         <v>1559</v>
       </c>
       <c r="M574" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="575" spans="1:13">
@@ -15679,7 +15502,7 @@
         <v>1559</v>
       </c>
       <c r="M575" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="576" spans="1:13">
@@ -15696,7 +15519,7 @@
         <v>1559</v>
       </c>
       <c r="M576" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="577" spans="1:13">
@@ -15713,7 +15536,7 @@
         <v>1559</v>
       </c>
       <c r="M577" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="578" spans="1:13">
@@ -15730,7 +15553,7 @@
         <v>1559</v>
       </c>
       <c r="M578" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="579" spans="1:13">
@@ -15747,7 +15570,7 @@
         <v>1559</v>
       </c>
       <c r="M579" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="580" spans="1:13">
@@ -15764,7 +15587,7 @@
         <v>1559</v>
       </c>
       <c r="M580" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="581" spans="1:13">
@@ -15781,7 +15604,7 @@
         <v>1559</v>
       </c>
       <c r="M581" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="582" spans="1:13">
@@ -15798,7 +15621,7 @@
         <v>1559</v>
       </c>
       <c r="M582" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="583" spans="1:13">
@@ -15815,7 +15638,7 @@
         <v>1559</v>
       </c>
       <c r="M583" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="584" spans="1:13">
@@ -15832,7 +15655,7 @@
         <v>1559</v>
       </c>
       <c r="M584" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="585" spans="1:13">
@@ -15849,7 +15672,7 @@
         <v>1559</v>
       </c>
       <c r="M585" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="586" spans="1:13">
@@ -15866,7 +15689,7 @@
         <v>1559</v>
       </c>
       <c r="M586" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="587" spans="1:13">
@@ -15883,7 +15706,7 @@
         <v>1559</v>
       </c>
       <c r="M587" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="588" spans="1:13">
@@ -15900,7 +15723,7 @@
         <v>1559</v>
       </c>
       <c r="M588" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="589" spans="1:13">
@@ -15917,7 +15740,7 @@
         <v>1559</v>
       </c>
       <c r="M589" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="590" spans="1:13">
@@ -15934,7 +15757,7 @@
         <v>1559</v>
       </c>
       <c r="M590" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="591" spans="1:13">
@@ -15951,7 +15774,7 @@
         <v>1559</v>
       </c>
       <c r="M591" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="592" spans="1:13">
@@ -15968,7 +15791,7 @@
         <v>1559</v>
       </c>
       <c r="M592" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="593" spans="1:13">
@@ -15985,7 +15808,7 @@
         <v>1559</v>
       </c>
       <c r="M593" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="594" spans="1:13">
@@ -16002,7 +15825,7 @@
         <v>1559</v>
       </c>
       <c r="M594" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="595" spans="1:13">
@@ -16019,7 +15842,7 @@
         <v>1559</v>
       </c>
       <c r="M595" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="596" spans="1:13">
@@ -16036,7 +15859,7 @@
         <v>1559</v>
       </c>
       <c r="M596" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="597" spans="1:13">
@@ -16053,7 +15876,7 @@
         <v>1559</v>
       </c>
       <c r="M597" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="598" spans="1:13">
@@ -16070,7 +15893,7 @@
         <v>1559</v>
       </c>
       <c r="M598" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="599" spans="1:13">
@@ -16087,7 +15910,7 @@
         <v>1559</v>
       </c>
       <c r="M599" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="600" spans="1:13">
@@ -16104,7 +15927,7 @@
         <v>1559</v>
       </c>
       <c r="M600" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="601" spans="1:13">
@@ -16121,7 +15944,7 @@
         <v>1559</v>
       </c>
       <c r="M601" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="602" spans="1:13">
@@ -16138,7 +15961,7 @@
         <v>1559</v>
       </c>
       <c r="M602" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="603" spans="1:13">
@@ -16155,7 +15978,7 @@
         <v>1559</v>
       </c>
       <c r="M603" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="604" spans="1:13">
@@ -16172,7 +15995,7 @@
         <v>1559</v>
       </c>
       <c r="M604" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="605" spans="1:13">
@@ -16189,7 +16012,7 @@
         <v>1559</v>
       </c>
       <c r="M605" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="606" spans="1:13">
@@ -16206,7 +16029,7 @@
         <v>1559</v>
       </c>
       <c r="M606" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="607" spans="1:13">
@@ -16223,7 +16046,7 @@
         <v>1559</v>
       </c>
       <c r="M607" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="608" spans="1:13">
@@ -16240,7 +16063,7 @@
         <v>1559</v>
       </c>
       <c r="M608" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="609" spans="1:13">
@@ -16257,7 +16080,7 @@
         <v>1559</v>
       </c>
       <c r="M609" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="610" spans="1:13">
@@ -16274,7 +16097,7 @@
         <v>1559</v>
       </c>
       <c r="M610" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="611" spans="1:13">
@@ -16291,7 +16114,7 @@
         <v>1559</v>
       </c>
       <c r="M611" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="612" spans="1:13">
@@ -16308,7 +16131,7 @@
         <v>1559</v>
       </c>
       <c r="M612" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="613" spans="1:13">
@@ -16325,7 +16148,7 @@
         <v>1559</v>
       </c>
       <c r="M613" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="614" spans="1:13">
@@ -16342,7 +16165,7 @@
         <v>1559</v>
       </c>
       <c r="M614" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="615" spans="1:13">
@@ -16359,7 +16182,7 @@
         <v>1559</v>
       </c>
       <c r="M615" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="616" spans="1:13">
@@ -16376,7 +16199,7 @@
         <v>1559</v>
       </c>
       <c r="M616" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="617" spans="1:13">
@@ -16393,7 +16216,7 @@
         <v>1559</v>
       </c>
       <c r="M617" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="618" spans="1:13">
@@ -16410,7 +16233,7 @@
         <v>1559</v>
       </c>
       <c r="M618" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="619" spans="1:13">
@@ -16427,7 +16250,7 @@
         <v>1559</v>
       </c>
       <c r="M619" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="620" spans="1:13">
@@ -16444,7 +16267,7 @@
         <v>1559</v>
       </c>
       <c r="M620" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="621" spans="1:13">
@@ -16461,7 +16284,7 @@
         <v>1559</v>
       </c>
       <c r="M621" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="622" spans="1:13">
@@ -16478,7 +16301,7 @@
         <v>1559</v>
       </c>
       <c r="M622" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="623" spans="1:13">
@@ -16495,7 +16318,7 @@
         <v>1559</v>
       </c>
       <c r="M623" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="624" spans="1:13">
@@ -16512,7 +16335,7 @@
         <v>1559</v>
       </c>
       <c r="M624" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="625" spans="1:13">
@@ -16529,7 +16352,7 @@
         <v>1559</v>
       </c>
       <c r="M625" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="626" spans="1:13">
@@ -16546,7 +16369,7 @@
         <v>1559</v>
       </c>
       <c r="M626" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="627" spans="1:13">
@@ -16563,7 +16386,7 @@
         <v>1559</v>
       </c>
       <c r="M627" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="628" spans="1:13">
@@ -16580,7 +16403,7 @@
         <v>1559</v>
       </c>
       <c r="M628" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="629" spans="1:13">
@@ -16597,7 +16420,7 @@
         <v>1559</v>
       </c>
       <c r="M629" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="630" spans="1:13">
@@ -16614,7 +16437,7 @@
         <v>1559</v>
       </c>
       <c r="M630" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="631" spans="1:13">
@@ -16631,7 +16454,7 @@
         <v>1559</v>
       </c>
       <c r="M631" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="632" spans="1:13">
@@ -16648,7 +16471,7 @@
         <v>1559</v>
       </c>
       <c r="M632" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="633" spans="1:13">
@@ -16665,7 +16488,7 @@
         <v>1559</v>
       </c>
       <c r="M633" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="634" spans="1:13">
@@ -16682,7 +16505,7 @@
         <v>1559</v>
       </c>
       <c r="M634" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="635" spans="1:13">
@@ -16699,7 +16522,7 @@
         <v>1559</v>
       </c>
       <c r="M635" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="636" spans="1:13">
@@ -16716,7 +16539,7 @@
         <v>1559</v>
       </c>
       <c r="M636" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="637" spans="1:13">
@@ -16733,7 +16556,7 @@
         <v>1559</v>
       </c>
       <c r="M637" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="638" spans="1:13">
@@ -16750,7 +16573,7 @@
         <v>1559</v>
       </c>
       <c r="M638" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="639" spans="1:13">
@@ -16767,7 +16590,7 @@
         <v>1559</v>
       </c>
       <c r="M639" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="640" spans="1:13">
@@ -16784,7 +16607,7 @@
         <v>1559</v>
       </c>
       <c r="M640" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="641" spans="1:13">
@@ -16801,7 +16624,7 @@
         <v>1559</v>
       </c>
       <c r="M641" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="642" spans="1:13">
@@ -16818,7 +16641,7 @@
         <v>1559</v>
       </c>
       <c r="M642" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="643" spans="1:13">
@@ -16835,7 +16658,7 @@
         <v>1559</v>
       </c>
       <c r="M643" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="644" spans="1:13">
@@ -16852,7 +16675,7 @@
         <v>1559</v>
       </c>
       <c r="M644" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="645" spans="1:13">
@@ -16869,7 +16692,7 @@
         <v>1559</v>
       </c>
       <c r="M645" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="646" spans="1:13">
@@ -16886,7 +16709,7 @@
         <v>1559</v>
       </c>
       <c r="M646" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="647" spans="1:13">
@@ -16903,7 +16726,7 @@
         <v>1559</v>
       </c>
       <c r="M647" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="648" spans="1:13">
@@ -16920,7 +16743,7 @@
         <v>1559</v>
       </c>
       <c r="M648" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="649" spans="1:13">
@@ -16937,7 +16760,7 @@
         <v>1559</v>
       </c>
       <c r="M649" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="650" spans="1:13">
@@ -16954,7 +16777,7 @@
         <v>1559</v>
       </c>
       <c r="M650" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="651" spans="1:13">
@@ -16971,7 +16794,7 @@
         <v>1559</v>
       </c>
       <c r="M651" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="652" spans="1:13">
@@ -16988,7 +16811,7 @@
         <v>1559</v>
       </c>
       <c r="M652" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="653" spans="1:13">
@@ -17005,7 +16828,7 @@
         <v>1559</v>
       </c>
       <c r="M653" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="654" spans="1:13">
@@ -17022,7 +16845,7 @@
         <v>1559</v>
       </c>
       <c r="M654" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="655" spans="1:13">
@@ -17039,7 +16862,7 @@
         <v>1559</v>
       </c>
       <c r="M655" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="656" spans="1:13">
@@ -17056,7 +16879,7 @@
         <v>1559</v>
       </c>
       <c r="M656" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="657" spans="1:13">
@@ -17073,7 +16896,7 @@
         <v>1559</v>
       </c>
       <c r="M657" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="658" spans="1:13">
@@ -17090,7 +16913,7 @@
         <v>1559</v>
       </c>
       <c r="M658" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="659" spans="1:13">
@@ -17107,7 +16930,7 @@
         <v>1559</v>
       </c>
       <c r="M659" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="660" spans="1:13">
@@ -17124,7 +16947,7 @@
         <v>1559</v>
       </c>
       <c r="M660" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="661" spans="1:13">
@@ -17141,7 +16964,7 @@
         <v>1559</v>
       </c>
       <c r="M661" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="662" spans="1:13">
@@ -17158,7 +16981,7 @@
         <v>1559</v>
       </c>
       <c r="M662" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="663" spans="1:13">
@@ -17175,7 +16998,7 @@
         <v>1559</v>
       </c>
       <c r="M663" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="664" spans="1:13">
@@ -17192,7 +17015,7 @@
         <v>1559</v>
       </c>
       <c r="M664" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="665" spans="1:13">
@@ -17209,7 +17032,7 @@
         <v>1559</v>
       </c>
       <c r="M665" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="666" spans="1:13">
@@ -17226,7 +17049,7 @@
         <v>1559</v>
       </c>
       <c r="M666" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="667" spans="1:13">
@@ -17243,7 +17066,7 @@
         <v>1559</v>
       </c>
       <c r="M667" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="668" spans="1:13">
@@ -17260,7 +17083,7 @@
         <v>1559</v>
       </c>
       <c r="M668" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="669" spans="1:13">
@@ -17277,7 +17100,7 @@
         <v>1559</v>
       </c>
       <c r="M669" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="670" spans="1:13">
@@ -17294,7 +17117,7 @@
         <v>1559</v>
       </c>
       <c r="M670" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="671" spans="1:13">
@@ -17311,7 +17134,7 @@
         <v>1559</v>
       </c>
       <c r="M671" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="672" spans="1:13">
@@ -17328,7 +17151,7 @@
         <v>1559</v>
       </c>
       <c r="M672" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="673" spans="1:13">
@@ -17345,7 +17168,7 @@
         <v>1559</v>
       </c>
       <c r="M673" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="674" spans="1:13">
@@ -17362,7 +17185,7 @@
         <v>1559</v>
       </c>
       <c r="M674" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="675" spans="1:13">
@@ -17379,7 +17202,7 @@
         <v>1559</v>
       </c>
       <c r="M675" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="676" spans="1:13">
@@ -17396,7 +17219,7 @@
         <v>1559</v>
       </c>
       <c r="M676" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="677" spans="1:13">
@@ -17413,7 +17236,7 @@
         <v>1559</v>
       </c>
       <c r="M677" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="678" spans="1:13">
@@ -17430,7 +17253,7 @@
         <v>1559</v>
       </c>
       <c r="M678" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="679" spans="1:13">
@@ -17447,7 +17270,7 @@
         <v>1559</v>
       </c>
       <c r="M679" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="680" spans="1:13">
@@ -17464,7 +17287,7 @@
         <v>1559</v>
       </c>
       <c r="M680" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="681" spans="1:13">
@@ -17481,7 +17304,7 @@
         <v>1559</v>
       </c>
       <c r="M681" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="682" spans="1:13">
@@ -17498,7 +17321,7 @@
         <v>1559</v>
       </c>
       <c r="M682" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="683" spans="1:13">
@@ -17515,7 +17338,7 @@
         <v>1559</v>
       </c>
       <c r="M683" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="684" spans="1:13">
@@ -17532,7 +17355,7 @@
         <v>1559</v>
       </c>
       <c r="M684" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="685" spans="1:13">
@@ -17549,7 +17372,7 @@
         <v>1559</v>
       </c>
       <c r="M685" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="686" spans="1:13">
@@ -17566,7 +17389,7 @@
         <v>1559</v>
       </c>
       <c r="M686" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="687" spans="1:13">
@@ -17583,7 +17406,7 @@
         <v>1559</v>
       </c>
       <c r="M687" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="688" spans="1:13">
@@ -17600,7 +17423,7 @@
         <v>1559</v>
       </c>
       <c r="M688" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="689" spans="1:13">
@@ -17617,7 +17440,7 @@
         <v>1559</v>
       </c>
       <c r="M689" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="690" spans="1:13">
@@ -17634,7 +17457,7 @@
         <v>1559</v>
       </c>
       <c r="M690" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="691" spans="1:13">
@@ -17651,7 +17474,7 @@
         <v>1559</v>
       </c>
       <c r="M691" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="692" spans="1:13">
@@ -17668,7 +17491,7 @@
         <v>1559</v>
       </c>
       <c r="M692" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="693" spans="1:13">
@@ -17685,7 +17508,7 @@
         <v>1559</v>
       </c>
       <c r="M693" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="694" spans="1:13">
@@ -17702,7 +17525,7 @@
         <v>1559</v>
       </c>
       <c r="M694" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="695" spans="1:13">
@@ -17719,7 +17542,7 @@
         <v>1559</v>
       </c>
       <c r="M695" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="696" spans="1:13">
@@ -17736,7 +17559,7 @@
         <v>1559</v>
       </c>
       <c r="M696" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="697" spans="1:13">
@@ -17753,7 +17576,7 @@
         <v>1559</v>
       </c>
       <c r="M697" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="698" spans="1:13">
@@ -17770,7 +17593,7 @@
         <v>1559</v>
       </c>
       <c r="M698" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="699" spans="1:13">
@@ -17787,7 +17610,7 @@
         <v>1559</v>
       </c>
       <c r="M699" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="700" spans="1:13">
@@ -17804,7 +17627,7 @@
         <v>1559</v>
       </c>
       <c r="M700" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="701" spans="1:13">
@@ -17821,7 +17644,7 @@
         <v>1559</v>
       </c>
       <c r="M701" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="702" spans="1:13">
@@ -17838,7 +17661,7 @@
         <v>1559</v>
       </c>
       <c r="M702" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="703" spans="1:13">
@@ -17855,7 +17678,7 @@
         <v>1559</v>
       </c>
       <c r="M703" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="704" spans="1:13">
@@ -17872,7 +17695,7 @@
         <v>1559</v>
       </c>
       <c r="M704" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="705" spans="1:13">
@@ -17889,7 +17712,7 @@
         <v>1559</v>
       </c>
       <c r="M705" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="706" spans="1:13">
@@ -17906,7 +17729,7 @@
         <v>1559</v>
       </c>
       <c r="M706" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="707" spans="1:13">
@@ -17923,7 +17746,7 @@
         <v>1559</v>
       </c>
       <c r="M707" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="708" spans="1:13">
@@ -17940,7 +17763,7 @@
         <v>1559</v>
       </c>
       <c r="M708" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="709" spans="1:13">
@@ -17957,7 +17780,7 @@
         <v>1559</v>
       </c>
       <c r="M709" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="710" spans="1:13">
@@ -17974,7 +17797,7 @@
         <v>1559</v>
       </c>
       <c r="M710" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="711" spans="1:13">
@@ -17991,7 +17814,7 @@
         <v>1559</v>
       </c>
       <c r="M711" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="712" spans="1:13">
@@ -18008,7 +17831,7 @@
         <v>1559</v>
       </c>
       <c r="M712" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="713" spans="1:13">
@@ -18025,7 +17848,7 @@
         <v>1559</v>
       </c>
       <c r="M713" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="714" spans="1:13">
@@ -18042,7 +17865,7 @@
         <v>1559</v>
       </c>
       <c r="M714" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="715" spans="1:13">
@@ -18059,7 +17882,7 @@
         <v>1559</v>
       </c>
       <c r="M715" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="716" spans="1:13">
@@ -18076,7 +17899,7 @@
         <v>1559</v>
       </c>
       <c r="M716" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="717" spans="1:13">
@@ -18093,7 +17916,7 @@
         <v>1559</v>
       </c>
       <c r="M717" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="718" spans="1:13">
@@ -18110,7 +17933,7 @@
         <v>1559</v>
       </c>
       <c r="M718" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="719" spans="1:13">
@@ -18127,7 +17950,7 @@
         <v>1559</v>
       </c>
       <c r="M719" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="720" spans="1:13">
@@ -18144,7 +17967,7 @@
         <v>1559</v>
       </c>
       <c r="M720" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="721" spans="1:13">
@@ -18161,7 +17984,7 @@
         <v>1559</v>
       </c>
       <c r="M721" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="722" spans="1:13">
@@ -18178,7 +18001,7 @@
         <v>1559</v>
       </c>
       <c r="M722" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="723" spans="1:13">
@@ -18195,7 +18018,7 @@
         <v>1559</v>
       </c>
       <c r="M723" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="724" spans="1:13">
@@ -18212,7 +18035,7 @@
         <v>1559</v>
       </c>
       <c r="M724" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="725" spans="1:13">
@@ -18229,7 +18052,7 @@
         <v>1559</v>
       </c>
       <c r="M725" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="726" spans="1:13">
@@ -18246,7 +18069,7 @@
         <v>1559</v>
       </c>
       <c r="M726" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="727" spans="1:13">
@@ -18263,7 +18086,7 @@
         <v>1559</v>
       </c>
       <c r="M727" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="728" spans="1:13">
@@ -18280,7 +18103,7 @@
         <v>1559</v>
       </c>
       <c r="M728" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="729" spans="1:13">
@@ -18297,7 +18120,7 @@
         <v>1559</v>
       </c>
       <c r="M729" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="730" spans="1:13">
@@ -18314,7 +18137,7 @@
         <v>1559</v>
       </c>
       <c r="M730" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="731" spans="1:13">
@@ -18331,7 +18154,7 @@
         <v>1559</v>
       </c>
       <c r="M731" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="732" spans="1:13">
@@ -18348,7 +18171,7 @@
         <v>1559</v>
       </c>
       <c r="M732" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="733" spans="1:13">
@@ -18365,7 +18188,7 @@
         <v>1559</v>
       </c>
       <c r="M733" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="734" spans="1:13">
@@ -18382,7 +18205,7 @@
         <v>1559</v>
       </c>
       <c r="M734" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="735" spans="1:13">
@@ -18399,7 +18222,7 @@
         <v>1559</v>
       </c>
       <c r="M735" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="736" spans="1:13">
@@ -18416,7 +18239,7 @@
         <v>1559</v>
       </c>
       <c r="M736" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="737" spans="1:13">
@@ -18433,7 +18256,7 @@
         <v>1559</v>
       </c>
       <c r="M737" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="738" spans="1:13">
@@ -18450,7 +18273,7 @@
         <v>1559</v>
       </c>
       <c r="M738" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="739" spans="1:13">
@@ -18467,7 +18290,7 @@
         <v>1559</v>
       </c>
       <c r="M739" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="740" spans="1:13">
@@ -18484,7 +18307,7 @@
         <v>1559</v>
       </c>
       <c r="M740" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="741" spans="1:13">
@@ -18501,7 +18324,7 @@
         <v>1559</v>
       </c>
       <c r="M741" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="742" spans="1:13">
@@ -18518,7 +18341,7 @@
         <v>1559</v>
       </c>
       <c r="M742" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="743" spans="1:13">
@@ -18526,7 +18349,7 @@
         <v>754</v>
       </c>
       <c r="B743" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="C743" t="s">
         <v>1532</v>
@@ -18535,7 +18358,7 @@
         <v>1559</v>
       </c>
       <c r="M743" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="744" spans="1:13">
@@ -18543,7 +18366,7 @@
         <v>755</v>
       </c>
       <c r="B744" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="C744" t="s">
         <v>1532</v>
@@ -18552,7 +18375,7 @@
         <v>1559</v>
       </c>
       <c r="M744" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="745" spans="1:13">
@@ -18560,7 +18383,7 @@
         <v>756</v>
       </c>
       <c r="B745" t="s">
-        <v>1028</v>
+        <v>1507</v>
       </c>
       <c r="C745" t="s">
         <v>1532</v>
@@ -18569,7 +18392,7 @@
         <v>1559</v>
       </c>
       <c r="M745" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="746" spans="1:13">
@@ -18577,7 +18400,7 @@
         <v>757</v>
       </c>
       <c r="B746" t="s">
-        <v>1507</v>
+        <v>1028</v>
       </c>
       <c r="C746" t="s">
         <v>1532</v>
@@ -18586,7 +18409,7 @@
         <v>1559</v>
       </c>
       <c r="M746" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="747" spans="1:13">
@@ -18603,7 +18426,7 @@
         <v>1559</v>
       </c>
       <c r="M747" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="748" spans="1:13">
@@ -18620,7 +18443,7 @@
         <v>1559</v>
       </c>
       <c r="M748" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="749" spans="1:13">
@@ -18637,7 +18460,7 @@
         <v>1559</v>
       </c>
       <c r="M749" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="750" spans="1:13">
@@ -18654,7 +18477,7 @@
         <v>1559</v>
       </c>
       <c r="M750" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="751" spans="1:13">
@@ -18671,7 +18494,7 @@
         <v>1559</v>
       </c>
       <c r="M751" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="752" spans="1:13">
@@ -18688,7 +18511,7 @@
         <v>1559</v>
       </c>
       <c r="M752" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="753" spans="1:13">
@@ -18705,7 +18528,7 @@
         <v>1559</v>
       </c>
       <c r="M753" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="754" spans="1:13">
@@ -18722,7 +18545,7 @@
         <v>1559</v>
       </c>
       <c r="M754" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="755" spans="1:13">
@@ -18739,7 +18562,7 @@
         <v>1559</v>
       </c>
       <c r="M755" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="756" spans="1:13">
@@ -18756,7 +18579,7 @@
         <v>1559</v>
       </c>
       <c r="M756" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="757" spans="1:13">
@@ -18773,7 +18596,7 @@
         <v>1559</v>
       </c>
       <c r="M757" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="758" spans="1:13">
@@ -18790,7 +18613,7 @@
         <v>1559</v>
       </c>
       <c r="M758" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="759" spans="1:13">
@@ -18807,7 +18630,7 @@
         <v>1559</v>
       </c>
       <c r="M759" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="760" spans="1:13">
@@ -18824,7 +18647,7 @@
         <v>1559</v>
       </c>
       <c r="M760" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="761" spans="1:13">
@@ -18841,7 +18664,7 @@
         <v>1559</v>
       </c>
       <c r="M761" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="762" spans="1:13">
@@ -18858,7 +18681,7 @@
         <v>1559</v>
       </c>
       <c r="M762" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="763" spans="1:13">
@@ -18875,7 +18698,7 @@
         <v>1559</v>
       </c>
       <c r="M763" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="764" spans="1:13">
@@ -18892,7 +18715,7 @@
         <v>1559</v>
       </c>
       <c r="M764" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="765" spans="1:13">
@@ -18909,7 +18732,7 @@
         <v>1559</v>
       </c>
       <c r="M765" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="766" spans="1:13">
@@ -18926,7 +18749,7 @@
         <v>1559</v>
       </c>
       <c r="M766" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="767" spans="1:13">
@@ -18943,7 +18766,7 @@
         <v>1559</v>
       </c>
       <c r="M767" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="768" spans="1:13">
@@ -18960,7 +18783,7 @@
         <v>1559</v>
       </c>
       <c r="M768" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="769" spans="1:13">
@@ -18977,7 +18800,7 @@
         <v>1559</v>
       </c>
       <c r="M769" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="770" spans="1:13">
@@ -18994,7 +18817,7 @@
         <v>1559</v>
       </c>
       <c r="M770" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
   </sheetData>

--- a/data/empresas/[GRUPO] Consolidado Terra Parent/map_balance.xlsx
+++ b/data/empresas/[GRUPO] Consolidado Terra Parent/map_balance.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4216" uniqueCount="1751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4228" uniqueCount="1754">
   <si>
     <t>N° de Cuenta</t>
   </si>
@@ -5086,6 +5086,15 @@
     <t>Créditos renta</t>
   </si>
   <si>
+    <t xml:space="preserve">Licencias </t>
+  </si>
+  <si>
+    <t>Concesiones</t>
+  </si>
+  <si>
+    <t>Licencias</t>
+  </si>
+  <si>
     <t>Plusvalía por Adquisiciones de Empresas</t>
   </si>
   <si>
@@ -5101,30 +5110,33 @@
     <t>Redes de transmisión</t>
   </si>
   <si>
+    <t>Plantas transmisoras</t>
+  </si>
+  <si>
     <t>Equipos portátiles</t>
   </si>
   <si>
+    <t>Muebles y útiles</t>
+  </si>
+  <si>
+    <t>Equipos de computación</t>
+  </si>
+  <si>
+    <t>Equipos seriados</t>
+  </si>
+  <si>
+    <t>Vehículos</t>
+  </si>
+  <si>
+    <t>Activos en leasing</t>
+  </si>
+  <si>
     <t>Otros activos</t>
   </si>
   <si>
     <t>Obras en curso</t>
   </si>
   <si>
-    <t>Muebles y útiles</t>
-  </si>
-  <si>
-    <t>Equipos de computación</t>
-  </si>
-  <si>
-    <t>Equipos seriados</t>
-  </si>
-  <si>
-    <t>Vehículos</t>
-  </si>
-  <si>
-    <t>Activos en leasing</t>
-  </si>
-  <si>
     <t>Instalaciones domiciliarias</t>
   </si>
   <si>
@@ -5212,10 +5224,7 @@
     <t>Yuan</t>
   </si>
   <si>
-    <t>Licencias</t>
-  </si>
-  <si>
-    <t>Activo fijo bruto</t>
+    <t>Deterioro PPE</t>
   </si>
   <si>
     <t>x</t>
@@ -5656,7 +5665,7 @@
         <v>1667</v>
       </c>
       <c r="M2" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5673,10 +5682,10 @@
         <v>1668</v>
       </c>
       <c r="E3" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M3" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -5693,10 +5702,10 @@
         <v>1668</v>
       </c>
       <c r="E4" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M4" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -5713,10 +5722,10 @@
         <v>1668</v>
       </c>
       <c r="E5" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M5" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -5733,10 +5742,10 @@
         <v>1668</v>
       </c>
       <c r="E6" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M6" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -5753,10 +5762,10 @@
         <v>1669</v>
       </c>
       <c r="E7" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M7" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -5773,10 +5782,10 @@
         <v>1669</v>
       </c>
       <c r="E8" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M8" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5793,10 +5802,10 @@
         <v>1669</v>
       </c>
       <c r="E9" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M9" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -5813,10 +5822,10 @@
         <v>1669</v>
       </c>
       <c r="E10" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M10" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -5833,10 +5842,10 @@
         <v>1670</v>
       </c>
       <c r="E11" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M11" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5853,10 +5862,10 @@
         <v>1670</v>
       </c>
       <c r="E12" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M12" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -5873,10 +5882,10 @@
         <v>1670</v>
       </c>
       <c r="E13" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M13" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -5893,10 +5902,10 @@
         <v>1670</v>
       </c>
       <c r="E14" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M14" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -5913,10 +5922,10 @@
         <v>1670</v>
       </c>
       <c r="E15" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M15" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -5933,10 +5942,10 @@
         <v>1670</v>
       </c>
       <c r="E16" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M16" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5953,10 +5962,10 @@
         <v>1670</v>
       </c>
       <c r="E17" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M17" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -5973,10 +5982,10 @@
         <v>1670</v>
       </c>
       <c r="E18" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M18" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -5993,10 +6002,10 @@
         <v>1670</v>
       </c>
       <c r="E19" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M19" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -6013,10 +6022,10 @@
         <v>1670</v>
       </c>
       <c r="E20" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M20" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -6033,10 +6042,10 @@
         <v>1670</v>
       </c>
       <c r="E21" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M21" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -6053,10 +6062,10 @@
         <v>1670</v>
       </c>
       <c r="E22" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M22" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -6073,10 +6082,10 @@
         <v>1670</v>
       </c>
       <c r="E23" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M23" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -6093,10 +6102,10 @@
         <v>1670</v>
       </c>
       <c r="E24" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M24" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -6113,10 +6122,10 @@
         <v>1670</v>
       </c>
       <c r="E25" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M25" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -6133,10 +6142,10 @@
         <v>1670</v>
       </c>
       <c r="E26" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M26" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -6153,10 +6162,10 @@
         <v>1670</v>
       </c>
       <c r="E27" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M27" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -6173,10 +6182,10 @@
         <v>1670</v>
       </c>
       <c r="E28" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M28" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -6193,10 +6202,10 @@
         <v>1670</v>
       </c>
       <c r="E29" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M29" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -6213,10 +6222,10 @@
         <v>1670</v>
       </c>
       <c r="E30" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M30" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -6233,10 +6242,10 @@
         <v>1670</v>
       </c>
       <c r="E31" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M31" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -6253,10 +6262,10 @@
         <v>1670</v>
       </c>
       <c r="E32" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M32" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -6273,10 +6282,10 @@
         <v>1670</v>
       </c>
       <c r="E33" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M33" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -6293,10 +6302,10 @@
         <v>1670</v>
       </c>
       <c r="E34" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M34" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -6313,10 +6322,10 @@
         <v>1670</v>
       </c>
       <c r="E35" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M35" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -6333,10 +6342,10 @@
         <v>1670</v>
       </c>
       <c r="E36" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M36" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -6353,10 +6362,10 @@
         <v>1670</v>
       </c>
       <c r="E37" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M37" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -6373,10 +6382,10 @@
         <v>1670</v>
       </c>
       <c r="E38" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M38" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -6393,10 +6402,10 @@
         <v>1670</v>
       </c>
       <c r="E39" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M39" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -6413,10 +6422,10 @@
         <v>1670</v>
       </c>
       <c r="E40" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M40" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -6433,10 +6442,10 @@
         <v>1670</v>
       </c>
       <c r="E41" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M41" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -6453,10 +6462,10 @@
         <v>1670</v>
       </c>
       <c r="E42" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M42" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -6473,10 +6482,10 @@
         <v>1670</v>
       </c>
       <c r="E43" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M43" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -6493,10 +6502,10 @@
         <v>1670</v>
       </c>
       <c r="E44" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M44" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -6513,10 +6522,10 @@
         <v>1670</v>
       </c>
       <c r="E45" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M45" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -6533,10 +6542,10 @@
         <v>1670</v>
       </c>
       <c r="E46" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M46" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -6553,10 +6562,10 @@
         <v>1670</v>
       </c>
       <c r="E47" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M47" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6573,10 +6582,10 @@
         <v>1670</v>
       </c>
       <c r="E48" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M48" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6593,10 +6602,10 @@
         <v>1670</v>
       </c>
       <c r="E49" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M49" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -6613,10 +6622,10 @@
         <v>1670</v>
       </c>
       <c r="E50" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="M50" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -6633,10 +6642,10 @@
         <v>1670</v>
       </c>
       <c r="E51" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M51" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -6653,10 +6662,10 @@
         <v>1670</v>
       </c>
       <c r="E52" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M52" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -6673,10 +6682,10 @@
         <v>1670</v>
       </c>
       <c r="E53" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M53" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6693,10 +6702,10 @@
         <v>1670</v>
       </c>
       <c r="E54" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M54" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -6713,10 +6722,10 @@
         <v>1670</v>
       </c>
       <c r="E55" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M55" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -6733,10 +6742,10 @@
         <v>1670</v>
       </c>
       <c r="E56" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M56" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -6753,7 +6762,7 @@
         <v>1671</v>
       </c>
       <c r="M57" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -6770,10 +6779,10 @@
         <v>1672</v>
       </c>
       <c r="E58" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M58" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -6790,10 +6799,10 @@
         <v>1669</v>
       </c>
       <c r="E59" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="M59" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -6810,10 +6819,10 @@
         <v>1669</v>
       </c>
       <c r="E60" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="M60" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -6830,7 +6839,7 @@
         <v>1673</v>
       </c>
       <c r="M61" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -6847,7 +6856,7 @@
         <v>1673</v>
       </c>
       <c r="M62" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6864,7 +6873,7 @@
         <v>1673</v>
       </c>
       <c r="M63" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -6878,7 +6887,7 @@
         <v>1633</v>
       </c>
       <c r="M64" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -6895,7 +6904,7 @@
         <v>1673</v>
       </c>
       <c r="M65" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6912,7 +6921,7 @@
         <v>1674</v>
       </c>
       <c r="M66" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -6929,7 +6938,7 @@
         <v>1675</v>
       </c>
       <c r="M67" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -6946,7 +6955,7 @@
         <v>1676</v>
       </c>
       <c r="M68" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6963,7 +6972,7 @@
         <v>1676</v>
       </c>
       <c r="M69" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -6980,7 +6989,7 @@
         <v>1676</v>
       </c>
       <c r="M70" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -6997,7 +7006,7 @@
         <v>1676</v>
       </c>
       <c r="M71" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -7014,7 +7023,7 @@
         <v>1676</v>
       </c>
       <c r="M72" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -7031,7 +7040,7 @@
         <v>1676</v>
       </c>
       <c r="M73" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -7048,7 +7057,7 @@
         <v>1676</v>
       </c>
       <c r="M74" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -7065,7 +7074,7 @@
         <v>1676</v>
       </c>
       <c r="M75" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -7082,7 +7091,7 @@
         <v>1677</v>
       </c>
       <c r="M76" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -7099,7 +7108,7 @@
         <v>1677</v>
       </c>
       <c r="M77" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -7116,7 +7125,7 @@
         <v>1678</v>
       </c>
       <c r="M78" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -7133,7 +7142,7 @@
         <v>1678</v>
       </c>
       <c r="M79" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -7150,7 +7159,7 @@
         <v>1679</v>
       </c>
       <c r="M80" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -7167,7 +7176,7 @@
         <v>1679</v>
       </c>
       <c r="M81" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -7184,7 +7193,7 @@
         <v>1676</v>
       </c>
       <c r="M82" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -7201,7 +7210,7 @@
         <v>1671</v>
       </c>
       <c r="M83" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -7218,10 +7227,10 @@
         <v>1680</v>
       </c>
       <c r="E84" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M84" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -7238,7 +7247,7 @@
         <v>1676</v>
       </c>
       <c r="M85" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -7255,7 +7264,7 @@
         <v>1679</v>
       </c>
       <c r="M86" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -7272,7 +7281,7 @@
         <v>1679</v>
       </c>
       <c r="M87" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -7289,7 +7298,7 @@
         <v>1681</v>
       </c>
       <c r="M88" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -7306,10 +7315,10 @@
         <v>1680</v>
       </c>
       <c r="E89" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M89" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -7326,7 +7335,7 @@
         <v>1681</v>
       </c>
       <c r="M90" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -7343,7 +7352,7 @@
         <v>1681</v>
       </c>
       <c r="M91" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -7360,7 +7369,7 @@
         <v>1679</v>
       </c>
       <c r="M92" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -7377,7 +7386,7 @@
         <v>1671</v>
       </c>
       <c r="M93" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -7394,10 +7403,10 @@
         <v>1682</v>
       </c>
       <c r="E94" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M94" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -7414,10 +7423,10 @@
         <v>1680</v>
       </c>
       <c r="E95" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M95" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -7434,10 +7443,10 @@
         <v>1680</v>
       </c>
       <c r="E96" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M96" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -7454,10 +7463,10 @@
         <v>1682</v>
       </c>
       <c r="E97" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="M97" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -7474,10 +7483,10 @@
         <v>1682</v>
       </c>
       <c r="E98" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M98" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -7494,7 +7503,7 @@
         <v>1683</v>
       </c>
       <c r="M99" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -7514,7 +7523,7 @@
         <v>1686</v>
       </c>
       <c r="M100" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -7531,10 +7540,10 @@
         <v>1682</v>
       </c>
       <c r="E101" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="M101" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -7551,7 +7560,7 @@
         <v>1684</v>
       </c>
       <c r="M102" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -7568,7 +7577,7 @@
         <v>1684</v>
       </c>
       <c r="M103" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -7585,7 +7594,7 @@
         <v>1684</v>
       </c>
       <c r="M104" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -7602,7 +7611,7 @@
         <v>1684</v>
       </c>
       <c r="M105" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -7616,7 +7625,7 @@
         <v>1638</v>
       </c>
       <c r="M106" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -7630,7 +7639,7 @@
         <v>1638</v>
       </c>
       <c r="M107" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -7644,7 +7653,7 @@
         <v>1638</v>
       </c>
       <c r="M108" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -7658,7 +7667,7 @@
         <v>1638</v>
       </c>
       <c r="M109" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -7675,7 +7684,7 @@
         <v>1685</v>
       </c>
       <c r="M110" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -7689,7 +7698,7 @@
         <v>1639</v>
       </c>
       <c r="M111" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -7709,7 +7718,7 @@
         <v>1686</v>
       </c>
       <c r="M112" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -7726,7 +7735,7 @@
         <v>1685</v>
       </c>
       <c r="M113" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -7740,7 +7749,7 @@
         <v>1638</v>
       </c>
       <c r="M114" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -7757,7 +7766,7 @@
         <v>1685</v>
       </c>
       <c r="M115" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -7774,7 +7783,7 @@
         <v>1684</v>
       </c>
       <c r="M116" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -7791,7 +7800,7 @@
         <v>1684</v>
       </c>
       <c r="M117" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -7808,7 +7817,7 @@
         <v>1684</v>
       </c>
       <c r="M118" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -7825,7 +7834,7 @@
         <v>1684</v>
       </c>
       <c r="M119" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -7842,7 +7851,7 @@
         <v>1684</v>
       </c>
       <c r="M120" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -7859,7 +7868,7 @@
         <v>1684</v>
       </c>
       <c r="M121" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -7876,7 +7885,7 @@
         <v>1684</v>
       </c>
       <c r="M122" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -7893,7 +7902,7 @@
         <v>1684</v>
       </c>
       <c r="M123" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -7910,7 +7919,7 @@
         <v>1684</v>
       </c>
       <c r="M124" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -7927,7 +7936,7 @@
         <v>1684</v>
       </c>
       <c r="M125" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -7944,7 +7953,7 @@
         <v>1684</v>
       </c>
       <c r="M126" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -7961,7 +7970,7 @@
         <v>1684</v>
       </c>
       <c r="M127" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -7978,7 +7987,7 @@
         <v>1684</v>
       </c>
       <c r="M128" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="129" spans="1:13">
@@ -7995,7 +8004,7 @@
         <v>1684</v>
       </c>
       <c r="M129" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="130" spans="1:13">
@@ -8012,7 +8021,7 @@
         <v>1684</v>
       </c>
       <c r="M130" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="131" spans="1:13">
@@ -8029,7 +8038,7 @@
         <v>1684</v>
       </c>
       <c r="M131" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="132" spans="1:13">
@@ -8046,7 +8055,7 @@
         <v>1684</v>
       </c>
       <c r="M132" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="133" spans="1:13">
@@ -8063,7 +8072,7 @@
         <v>1684</v>
       </c>
       <c r="M133" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="134" spans="1:13">
@@ -8080,7 +8089,7 @@
         <v>1684</v>
       </c>
       <c r="M134" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="135" spans="1:13">
@@ -8097,7 +8106,7 @@
         <v>1684</v>
       </c>
       <c r="M135" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="136" spans="1:13">
@@ -8114,7 +8123,7 @@
         <v>1684</v>
       </c>
       <c r="M136" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="137" spans="1:13">
@@ -8131,7 +8140,7 @@
         <v>1684</v>
       </c>
       <c r="M137" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="138" spans="1:13">
@@ -8148,7 +8157,7 @@
         <v>1684</v>
       </c>
       <c r="M138" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="139" spans="1:13">
@@ -8165,7 +8174,7 @@
         <v>1684</v>
       </c>
       <c r="M139" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="140" spans="1:13">
@@ -8182,7 +8191,7 @@
         <v>1684</v>
       </c>
       <c r="M140" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="141" spans="1:13">
@@ -8199,7 +8208,7 @@
         <v>1687</v>
       </c>
       <c r="M141" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="142" spans="1:13">
@@ -8216,7 +8225,7 @@
         <v>1687</v>
       </c>
       <c r="M142" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="143" spans="1:13">
@@ -8233,7 +8242,7 @@
         <v>1688</v>
       </c>
       <c r="M143" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="144" spans="1:13">
@@ -8250,7 +8259,7 @@
         <v>1689</v>
       </c>
       <c r="M144" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="145" spans="1:13">
@@ -8267,7 +8276,7 @@
         <v>1689</v>
       </c>
       <c r="M145" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="146" spans="1:13">
@@ -8284,7 +8293,7 @@
         <v>1689</v>
       </c>
       <c r="M146" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="147" spans="1:13">
@@ -8298,7 +8307,7 @@
         <v>1642</v>
       </c>
       <c r="M147" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="148" spans="1:13">
@@ -8312,7 +8321,7 @@
         <v>1642</v>
       </c>
       <c r="M148" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="149" spans="1:13">
@@ -8329,7 +8338,7 @@
         <v>1690</v>
       </c>
       <c r="M149" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="150" spans="1:13">
@@ -8342,11 +8351,8 @@
       <c r="C150" t="s">
         <v>1643</v>
       </c>
-      <c r="D150" t="s">
-        <v>1690</v>
-      </c>
       <c r="M150" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="151" spans="1:13">
@@ -8359,11 +8365,8 @@
       <c r="C151" t="s">
         <v>1643</v>
       </c>
-      <c r="D151" t="s">
-        <v>1690</v>
-      </c>
       <c r="M151" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="152" spans="1:13">
@@ -8377,10 +8380,10 @@
         <v>1643</v>
       </c>
       <c r="D152" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="M152" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="153" spans="1:13">
@@ -8393,11 +8396,14 @@
       <c r="C153" t="s">
         <v>1644</v>
       </c>
+      <c r="D153" t="s">
+        <v>1690</v>
+      </c>
       <c r="E153" t="s">
         <v>1674</v>
       </c>
       <c r="M153" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="154" spans="1:13">
@@ -8414,7 +8420,7 @@
         <v>1690</v>
       </c>
       <c r="M154" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="155" spans="1:13">
@@ -8428,7 +8434,7 @@
         <v>1644</v>
       </c>
       <c r="M155" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="156" spans="1:13">
@@ -8442,7 +8448,7 @@
         <v>1644</v>
       </c>
       <c r="M156" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="157" spans="1:13">
@@ -8456,7 +8462,7 @@
         <v>1644</v>
       </c>
       <c r="M157" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="158" spans="1:13">
@@ -8470,7 +8476,7 @@
         <v>1644</v>
       </c>
       <c r="M158" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="159" spans="1:13">
@@ -8484,13 +8490,10 @@
         <v>1643</v>
       </c>
       <c r="D159" t="s">
-        <v>1690</v>
-      </c>
-      <c r="E159" t="s">
-        <v>1686</v>
+        <v>1692</v>
       </c>
       <c r="M159" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="160" spans="1:13">
@@ -8507,7 +8510,7 @@
         <v>1675</v>
       </c>
       <c r="M160" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -8521,10 +8524,10 @@
         <v>1645</v>
       </c>
       <c r="D161" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="M161" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -8538,10 +8541,10 @@
         <v>1646</v>
       </c>
       <c r="D162" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="M162" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -8555,10 +8558,10 @@
         <v>1646</v>
       </c>
       <c r="E163" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="M163" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -8572,10 +8575,10 @@
         <v>1646</v>
       </c>
       <c r="D164" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="M164" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -8589,10 +8592,10 @@
         <v>1646</v>
       </c>
       <c r="D165" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="M165" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -8605,11 +8608,11 @@
       <c r="C166" t="s">
         <v>1646</v>
       </c>
-      <c r="D166" t="s">
-        <v>1691</v>
+      <c r="E166" t="s">
+        <v>1694</v>
       </c>
       <c r="M166" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -8622,11 +8625,11 @@
       <c r="C167" t="s">
         <v>1646</v>
       </c>
-      <c r="D167" t="s">
-        <v>1691</v>
+      <c r="E167" t="s">
+        <v>1694</v>
       </c>
       <c r="M167" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -8640,13 +8643,13 @@
         <v>1647</v>
       </c>
       <c r="D168" t="s">
-        <v>1692</v>
-      </c>
-      <c r="L168" t="s">
-        <v>1734</v>
+        <v>1695</v>
+      </c>
+      <c r="E168" t="s">
+        <v>1686</v>
       </c>
       <c r="M168" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -8660,13 +8663,13 @@
         <v>1647</v>
       </c>
       <c r="D169" t="s">
-        <v>1693</v>
-      </c>
-      <c r="L169" t="s">
-        <v>1734</v>
+        <v>1696</v>
+      </c>
+      <c r="E169" t="s">
+        <v>1686</v>
       </c>
       <c r="M169" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -8680,13 +8683,13 @@
         <v>1647</v>
       </c>
       <c r="D170" t="s">
-        <v>1694</v>
-      </c>
-      <c r="L170" t="s">
-        <v>1734</v>
+        <v>1697</v>
+      </c>
+      <c r="E170" t="s">
+        <v>1686</v>
       </c>
       <c r="M170" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="171" spans="1:13">
@@ -8700,13 +8703,13 @@
         <v>1647</v>
       </c>
       <c r="D171" t="s">
-        <v>1694</v>
-      </c>
-      <c r="L171" t="s">
-        <v>1734</v>
+        <v>1698</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1686</v>
       </c>
       <c r="M171" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="172" spans="1:13">
@@ -8720,13 +8723,13 @@
         <v>1647</v>
       </c>
       <c r="D172" t="s">
-        <v>1695</v>
-      </c>
-      <c r="L172" t="s">
-        <v>1734</v>
+        <v>1699</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1686</v>
       </c>
       <c r="M172" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="173" spans="1:13">
@@ -8740,13 +8743,13 @@
         <v>1647</v>
       </c>
       <c r="D173" t="s">
-        <v>1696</v>
-      </c>
-      <c r="L173" t="s">
-        <v>1734</v>
+        <v>1697</v>
+      </c>
+      <c r="E173" t="s">
+        <v>1686</v>
       </c>
       <c r="M173" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="174" spans="1:13">
@@ -8760,13 +8763,13 @@
         <v>1647</v>
       </c>
       <c r="D174" t="s">
-        <v>1696</v>
-      </c>
-      <c r="L174" t="s">
-        <v>1734</v>
+        <v>1697</v>
+      </c>
+      <c r="E174" t="s">
+        <v>1686</v>
       </c>
       <c r="M174" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="175" spans="1:13">
@@ -8780,13 +8783,13 @@
         <v>1647</v>
       </c>
       <c r="D175" t="s">
-        <v>1696</v>
-      </c>
-      <c r="L175" t="s">
-        <v>1734</v>
+        <v>1698</v>
+      </c>
+      <c r="E175" t="s">
+        <v>1686</v>
       </c>
       <c r="M175" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="176" spans="1:13">
@@ -8800,13 +8803,13 @@
         <v>1647</v>
       </c>
       <c r="D176" t="s">
-        <v>1694</v>
-      </c>
-      <c r="L176" t="s">
-        <v>1734</v>
+        <v>1697</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1686</v>
       </c>
       <c r="M176" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="177" spans="1:13">
@@ -8819,14 +8822,8 @@
       <c r="C177" t="s">
         <v>1647</v>
       </c>
-      <c r="D177" t="s">
-        <v>1696</v>
-      </c>
-      <c r="L177" t="s">
-        <v>1734</v>
-      </c>
       <c r="M177" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="178" spans="1:13">
@@ -8839,14 +8836,8 @@
       <c r="C178" t="s">
         <v>1647</v>
       </c>
-      <c r="D178" t="s">
-        <v>1697</v>
-      </c>
-      <c r="L178" t="s">
-        <v>1734</v>
-      </c>
       <c r="M178" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="179" spans="1:13">
@@ -8860,13 +8851,13 @@
         <v>1647</v>
       </c>
       <c r="D179" t="s">
-        <v>1698</v>
-      </c>
-      <c r="L179" t="s">
-        <v>1734</v>
+        <v>1700</v>
+      </c>
+      <c r="E179" t="s">
+        <v>1686</v>
       </c>
       <c r="M179" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="180" spans="1:13">
@@ -8880,13 +8871,13 @@
         <v>1647</v>
       </c>
       <c r="D180" t="s">
-        <v>1699</v>
-      </c>
-      <c r="L180" t="s">
-        <v>1734</v>
+        <v>1701</v>
+      </c>
+      <c r="E180" t="s">
+        <v>1686</v>
       </c>
       <c r="M180" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="181" spans="1:13">
@@ -8900,13 +8891,13 @@
         <v>1647</v>
       </c>
       <c r="D181" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L181" t="s">
-        <v>1734</v>
+        <v>1702</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1686</v>
       </c>
       <c r="M181" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="182" spans="1:13">
@@ -8920,13 +8911,13 @@
         <v>1647</v>
       </c>
       <c r="D182" t="s">
-        <v>1696</v>
-      </c>
-      <c r="L182" t="s">
-        <v>1734</v>
+        <v>1697</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1686</v>
       </c>
       <c r="M182" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="183" spans="1:13">
@@ -8939,14 +8930,8 @@
       <c r="C183" t="s">
         <v>1647</v>
       </c>
-      <c r="D183" t="s">
-        <v>1700</v>
-      </c>
-      <c r="L183" t="s">
-        <v>1734</v>
-      </c>
       <c r="M183" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="184" spans="1:13">
@@ -8960,10 +8945,13 @@
         <v>1647</v>
       </c>
       <c r="D184" t="s">
-        <v>1700</v>
+        <v>1686</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1736</v>
       </c>
       <c r="M184" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="185" spans="1:13">
@@ -8977,10 +8965,13 @@
         <v>1647</v>
       </c>
       <c r="D185" t="s">
-        <v>1701</v>
+        <v>1703</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1686</v>
       </c>
       <c r="M185" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="186" spans="1:13">
@@ -8994,10 +8985,13 @@
         <v>1647</v>
       </c>
       <c r="D186" t="s">
-        <v>1702</v>
+        <v>1704</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1686</v>
       </c>
       <c r="M186" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -9011,10 +9005,13 @@
         <v>1647</v>
       </c>
       <c r="D187" t="s">
-        <v>1696</v>
+        <v>1705</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1686</v>
       </c>
       <c r="M187" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -9028,10 +9025,13 @@
         <v>1647</v>
       </c>
       <c r="D188" t="s">
-        <v>1697</v>
+        <v>1706</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1686</v>
       </c>
       <c r="M188" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -9045,10 +9045,13 @@
         <v>1647</v>
       </c>
       <c r="D189" t="s">
-        <v>1703</v>
+        <v>1707</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1686</v>
       </c>
       <c r="M189" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -9062,10 +9065,13 @@
         <v>1647</v>
       </c>
       <c r="D190" t="s">
-        <v>1696</v>
+        <v>1706</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1686</v>
       </c>
       <c r="M190" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -9082,10 +9088,10 @@
         <v>1680</v>
       </c>
       <c r="E191" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M191" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -9102,10 +9108,10 @@
         <v>1682</v>
       </c>
       <c r="E192" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M192" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="193" spans="1:13">
@@ -9119,10 +9125,13 @@
         <v>1647</v>
       </c>
       <c r="D193" t="s">
-        <v>1696</v>
+        <v>1707</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1686</v>
       </c>
       <c r="M193" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="194" spans="1:13">
@@ -9135,11 +9144,14 @@
       <c r="C194" t="s">
         <v>1647</v>
       </c>
+      <c r="D194" t="s">
+        <v>1686</v>
+      </c>
       <c r="E194" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="M194" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="195" spans="1:13">
@@ -9152,11 +9164,14 @@
       <c r="C195" t="s">
         <v>1647</v>
       </c>
+      <c r="D195" t="s">
+        <v>1686</v>
+      </c>
       <c r="E195" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="M195" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="196" spans="1:13">
@@ -9169,11 +9184,14 @@
       <c r="C196" t="s">
         <v>1647</v>
       </c>
+      <c r="D196" t="s">
+        <v>1686</v>
+      </c>
       <c r="E196" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="M196" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -9186,11 +9204,14 @@
       <c r="C197" t="s">
         <v>1647</v>
       </c>
+      <c r="D197" t="s">
+        <v>1686</v>
+      </c>
       <c r="E197" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="M197" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="198" spans="1:13">
@@ -9203,11 +9224,14 @@
       <c r="C198" t="s">
         <v>1647</v>
       </c>
+      <c r="D198" t="s">
+        <v>1686</v>
+      </c>
       <c r="E198" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="M198" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="199" spans="1:13">
@@ -9220,11 +9244,14 @@
       <c r="C199" t="s">
         <v>1647</v>
       </c>
+      <c r="D199" t="s">
+        <v>1686</v>
+      </c>
       <c r="E199" t="s">
-        <v>1696</v>
+        <v>1705</v>
       </c>
       <c r="M199" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="200" spans="1:13">
@@ -9237,11 +9264,14 @@
       <c r="C200" t="s">
         <v>1647</v>
       </c>
+      <c r="D200" t="s">
+        <v>1686</v>
+      </c>
       <c r="E200" t="s">
-        <v>1696</v>
+        <v>1704</v>
       </c>
       <c r="M200" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="201" spans="1:13">
@@ -9254,11 +9284,14 @@
       <c r="C201" t="s">
         <v>1647</v>
       </c>
+      <c r="D201" t="s">
+        <v>1686</v>
+      </c>
       <c r="E201" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="M201" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="202" spans="1:13">
@@ -9271,11 +9304,14 @@
       <c r="C202" t="s">
         <v>1647</v>
       </c>
+      <c r="D202" t="s">
+        <v>1686</v>
+      </c>
       <c r="E202" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="M202" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="203" spans="1:13">
@@ -9288,11 +9324,14 @@
       <c r="C203" t="s">
         <v>1647</v>
       </c>
+      <c r="D203" t="s">
+        <v>1686</v>
+      </c>
       <c r="E203" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="M203" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="204" spans="1:13">
@@ -9305,11 +9344,14 @@
       <c r="C204" t="s">
         <v>1647</v>
       </c>
+      <c r="D204" t="s">
+        <v>1686</v>
+      </c>
       <c r="E204" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="M204" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="205" spans="1:13">
@@ -9322,11 +9364,14 @@
       <c r="C205" t="s">
         <v>1647</v>
       </c>
+      <c r="D205" t="s">
+        <v>1686</v>
+      </c>
       <c r="E205" t="s">
-        <v>1696</v>
+        <v>1707</v>
       </c>
       <c r="M205" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -9339,11 +9384,14 @@
       <c r="C206" t="s">
         <v>1647</v>
       </c>
+      <c r="D206" t="s">
+        <v>1686</v>
+      </c>
       <c r="E206" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="M206" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="207" spans="1:13">
@@ -9356,11 +9404,14 @@
       <c r="C207" t="s">
         <v>1647</v>
       </c>
+      <c r="D207" t="s">
+        <v>1686</v>
+      </c>
       <c r="E207" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="M207" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="208" spans="1:13">
@@ -9373,11 +9424,14 @@
       <c r="C208" t="s">
         <v>1647</v>
       </c>
+      <c r="D208" t="s">
+        <v>1686</v>
+      </c>
       <c r="E208" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="M208" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="209" spans="1:13">
@@ -9390,11 +9444,14 @@
       <c r="C209" t="s">
         <v>1647</v>
       </c>
+      <c r="D209" t="s">
+        <v>1686</v>
+      </c>
       <c r="E209" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="M209" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="210" spans="1:13">
@@ -9407,11 +9464,8 @@
       <c r="C210" t="s">
         <v>1647</v>
       </c>
-      <c r="E210" t="s">
-        <v>1700</v>
-      </c>
       <c r="M210" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="211" spans="1:13">
@@ -9424,14 +9478,11 @@
       <c r="C211" t="s">
         <v>1643</v>
       </c>
-      <c r="D211" t="s">
-        <v>1690</v>
-      </c>
       <c r="E211" t="s">
-        <v>1732</v>
+        <v>1692</v>
       </c>
       <c r="M211" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="212" spans="1:13">
@@ -9444,14 +9495,8 @@
       <c r="C212" t="s">
         <v>1647</v>
       </c>
-      <c r="D212" t="s">
-        <v>1698</v>
-      </c>
-      <c r="E212" t="s">
-        <v>1733</v>
-      </c>
       <c r="M212" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="213" spans="1:13">
@@ -9465,10 +9510,10 @@
         <v>1648</v>
       </c>
       <c r="D213" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="M213" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -9485,7 +9530,7 @@
         <v>1674</v>
       </c>
       <c r="M214" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="215" spans="1:13">
@@ -9502,7 +9547,7 @@
         <v>1674</v>
       </c>
       <c r="M215" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="216" spans="1:13">
@@ -9519,7 +9564,7 @@
         <v>1674</v>
       </c>
       <c r="M216" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="217" spans="1:13">
@@ -9536,7 +9581,7 @@
         <v>1674</v>
       </c>
       <c r="M217" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="218" spans="1:13">
@@ -9553,7 +9598,7 @@
         <v>1674</v>
       </c>
       <c r="M218" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="219" spans="1:13">
@@ -9570,7 +9615,7 @@
         <v>1674</v>
       </c>
       <c r="M219" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="220" spans="1:13">
@@ -9584,10 +9629,10 @@
         <v>1634</v>
       </c>
       <c r="D220" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M220" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="221" spans="1:13">
@@ -9601,10 +9646,10 @@
         <v>1644</v>
       </c>
       <c r="E221" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M221" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="222" spans="1:13">
@@ -9621,7 +9666,7 @@
         <v>1674</v>
       </c>
       <c r="M222" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="223" spans="1:13">
@@ -9635,10 +9680,10 @@
         <v>1644</v>
       </c>
       <c r="E223" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M223" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="224" spans="1:13">
@@ -9652,10 +9697,10 @@
         <v>1634</v>
       </c>
       <c r="D224" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M224" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="225" spans="1:13">
@@ -9672,7 +9717,7 @@
         <v>1674</v>
       </c>
       <c r="M225" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="226" spans="1:13">
@@ -9689,7 +9734,7 @@
         <v>1674</v>
       </c>
       <c r="M226" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="227" spans="1:13">
@@ -9706,7 +9751,7 @@
         <v>1674</v>
       </c>
       <c r="M227" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="228" spans="1:13">
@@ -9723,7 +9768,7 @@
         <v>1674</v>
       </c>
       <c r="M228" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="229" spans="1:13">
@@ -9740,7 +9785,7 @@
         <v>1674</v>
       </c>
       <c r="M229" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="230" spans="1:13">
@@ -9757,7 +9802,7 @@
         <v>1674</v>
       </c>
       <c r="M230" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="231" spans="1:13">
@@ -9774,7 +9819,7 @@
         <v>1674</v>
       </c>
       <c r="M231" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="232" spans="1:13">
@@ -9794,7 +9839,7 @@
         <v>1686</v>
       </c>
       <c r="M232" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="233" spans="1:13">
@@ -9814,7 +9859,7 @@
         <v>1686</v>
       </c>
       <c r="M233" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -9834,7 +9879,7 @@
         <v>1686</v>
       </c>
       <c r="M234" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="235" spans="1:13">
@@ -9854,7 +9899,7 @@
         <v>1686</v>
       </c>
       <c r="M235" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="236" spans="1:13">
@@ -9874,7 +9919,7 @@
         <v>1686</v>
       </c>
       <c r="M236" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="237" spans="1:13">
@@ -9894,7 +9939,7 @@
         <v>1686</v>
       </c>
       <c r="M237" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="238" spans="1:13">
@@ -9914,7 +9959,7 @@
         <v>1686</v>
       </c>
       <c r="M238" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="239" spans="1:13">
@@ -9934,7 +9979,7 @@
         <v>1686</v>
       </c>
       <c r="M239" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="240" spans="1:13">
@@ -9954,7 +9999,7 @@
         <v>1686</v>
       </c>
       <c r="M240" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -9974,7 +10019,7 @@
         <v>1686</v>
       </c>
       <c r="M241" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -9994,7 +10039,7 @@
         <v>1686</v>
       </c>
       <c r="M242" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -10014,7 +10059,7 @@
         <v>1686</v>
       </c>
       <c r="M243" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -10031,7 +10076,7 @@
         <v>1674</v>
       </c>
       <c r="M244" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -10048,7 +10093,7 @@
         <v>1674</v>
       </c>
       <c r="M245" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -10068,7 +10113,7 @@
         <v>1686</v>
       </c>
       <c r="M246" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -10088,7 +10133,7 @@
         <v>1686</v>
       </c>
       <c r="M247" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -10108,7 +10153,7 @@
         <v>1686</v>
       </c>
       <c r="M248" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -10128,7 +10173,7 @@
         <v>1686</v>
       </c>
       <c r="M249" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -10148,7 +10193,7 @@
         <v>1686</v>
       </c>
       <c r="M250" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="251" spans="1:13">
@@ -10168,7 +10213,7 @@
         <v>1686</v>
       </c>
       <c r="M251" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="252" spans="1:13">
@@ -10185,7 +10230,7 @@
         <v>1674</v>
       </c>
       <c r="M252" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="253" spans="1:13">
@@ -10202,7 +10247,7 @@
         <v>1674</v>
       </c>
       <c r="M253" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="254" spans="1:13">
@@ -10216,10 +10261,10 @@
         <v>1634</v>
       </c>
       <c r="D254" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M254" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="255" spans="1:13">
@@ -10233,10 +10278,10 @@
         <v>1634</v>
       </c>
       <c r="D255" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M255" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="256" spans="1:13">
@@ -10253,7 +10298,7 @@
         <v>1675</v>
       </c>
       <c r="M256" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="257" spans="1:13">
@@ -10270,7 +10315,7 @@
         <v>1675</v>
       </c>
       <c r="M257" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="258" spans="1:13">
@@ -10284,10 +10329,10 @@
         <v>1634</v>
       </c>
       <c r="D258" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M258" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="259" spans="1:13">
@@ -10301,10 +10346,10 @@
         <v>1634</v>
       </c>
       <c r="D259" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M259" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="260" spans="1:13">
@@ -10318,10 +10363,10 @@
         <v>1634</v>
       </c>
       <c r="D260" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M260" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="261" spans="1:13">
@@ -10335,10 +10380,10 @@
         <v>1634</v>
       </c>
       <c r="D261" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M261" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="262" spans="1:13">
@@ -10352,10 +10397,10 @@
         <v>1634</v>
       </c>
       <c r="D262" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M262" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="263" spans="1:13">
@@ -10369,10 +10414,10 @@
         <v>1634</v>
       </c>
       <c r="D263" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M263" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="264" spans="1:13">
@@ -10386,10 +10431,10 @@
         <v>1649</v>
       </c>
       <c r="D264" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="M264" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="265" spans="1:13">
@@ -10403,10 +10448,10 @@
         <v>1649</v>
       </c>
       <c r="D265" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="M265" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="266" spans="1:13">
@@ -10423,7 +10468,7 @@
         <v>1674</v>
       </c>
       <c r="M266" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="267" spans="1:13">
@@ -10437,10 +10482,10 @@
         <v>1634</v>
       </c>
       <c r="D267" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M267" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="268" spans="1:13">
@@ -10454,10 +10499,10 @@
         <v>1634</v>
       </c>
       <c r="D268" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M268" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="269" spans="1:13">
@@ -10471,13 +10516,13 @@
         <v>1634</v>
       </c>
       <c r="D269" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="E269" t="s">
         <v>1686</v>
       </c>
       <c r="M269" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="270" spans="1:13">
@@ -10491,13 +10536,13 @@
         <v>1634</v>
       </c>
       <c r="D270" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="E270" t="s">
         <v>1686</v>
       </c>
       <c r="M270" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="271" spans="1:13">
@@ -10514,10 +10559,10 @@
         <v>1680</v>
       </c>
       <c r="E271" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M271" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="272" spans="1:13">
@@ -10534,10 +10579,10 @@
         <v>1682</v>
       </c>
       <c r="E272" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M272" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="273" spans="1:13">
@@ -10554,10 +10599,10 @@
         <v>1682</v>
       </c>
       <c r="E273" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="M273" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="274" spans="1:13">
@@ -10574,10 +10619,10 @@
         <v>1680</v>
       </c>
       <c r="E274" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M274" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="275" spans="1:13">
@@ -10594,10 +10639,10 @@
         <v>1682</v>
       </c>
       <c r="E275" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="M275" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="276" spans="1:13">
@@ -10611,10 +10656,10 @@
         <v>1635</v>
       </c>
       <c r="E276" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M276" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="277" spans="1:13">
@@ -10628,13 +10673,13 @@
         <v>1635</v>
       </c>
       <c r="D277" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="E277" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M277" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="278" spans="1:13">
@@ -10648,10 +10693,10 @@
         <v>1650</v>
       </c>
       <c r="D278" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="M278" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="279" spans="1:13">
@@ -10665,10 +10710,10 @@
         <v>1650</v>
       </c>
       <c r="D279" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="M279" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="280" spans="1:13">
@@ -10682,13 +10727,13 @@
         <v>1635</v>
       </c>
       <c r="D280" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="E280" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M280" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="281" spans="1:13">
@@ -10702,13 +10747,13 @@
         <v>1635</v>
       </c>
       <c r="D281" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E281" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M281" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="282" spans="1:13">
@@ -10722,16 +10767,16 @@
         <v>1635</v>
       </c>
       <c r="D282" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E282" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L282" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M282" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="283" spans="1:13">
@@ -10745,16 +10790,16 @@
         <v>1635</v>
       </c>
       <c r="D283" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E283" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L283" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M283" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="284" spans="1:13">
@@ -10768,16 +10813,16 @@
         <v>1635</v>
       </c>
       <c r="D284" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E284" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L284" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M284" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="285" spans="1:13">
@@ -10791,16 +10836,16 @@
         <v>1635</v>
       </c>
       <c r="D285" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E285" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L285" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M285" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="286" spans="1:13">
@@ -10814,16 +10859,16 @@
         <v>1635</v>
       </c>
       <c r="D286" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E286" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L286" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M286" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="287" spans="1:13">
@@ -10837,16 +10882,16 @@
         <v>1635</v>
       </c>
       <c r="D287" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E287" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L287" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M287" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="288" spans="1:13">
@@ -10860,16 +10905,16 @@
         <v>1635</v>
       </c>
       <c r="D288" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E288" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L288" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M288" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="289" spans="1:13">
@@ -10883,13 +10928,13 @@
         <v>1635</v>
       </c>
       <c r="D289" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E289" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M289" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="290" spans="1:13">
@@ -10903,16 +10948,16 @@
         <v>1635</v>
       </c>
       <c r="D290" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E290" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L290" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M290" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="291" spans="1:13">
@@ -10926,16 +10971,16 @@
         <v>1635</v>
       </c>
       <c r="D291" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E291" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L291" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M291" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="292" spans="1:13">
@@ -10949,16 +10994,16 @@
         <v>1635</v>
       </c>
       <c r="D292" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E292" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L292" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M292" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="293" spans="1:13">
@@ -10972,16 +11017,16 @@
         <v>1635</v>
       </c>
       <c r="D293" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E293" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L293" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M293" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="294" spans="1:13">
@@ -10995,10 +11040,10 @@
         <v>1651</v>
       </c>
       <c r="D294" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="M294" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="295" spans="1:13">
@@ -11015,7 +11060,7 @@
         <v>1679</v>
       </c>
       <c r="M295" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="296" spans="1:13">
@@ -11029,16 +11074,16 @@
         <v>1635</v>
       </c>
       <c r="D296" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E296" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L296" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M296" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="297" spans="1:13">
@@ -11052,16 +11097,16 @@
         <v>1635</v>
       </c>
       <c r="D297" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E297" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L297" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M297" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="298" spans="1:13">
@@ -11075,16 +11120,16 @@
         <v>1635</v>
       </c>
       <c r="D298" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E298" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L298" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M298" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="299" spans="1:13">
@@ -11098,16 +11143,16 @@
         <v>1635</v>
       </c>
       <c r="D299" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E299" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L299" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M299" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="300" spans="1:13">
@@ -11121,16 +11166,16 @@
         <v>1635</v>
       </c>
       <c r="D300" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="E300" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="L300" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="M300" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="301" spans="1:13">
@@ -11144,13 +11189,13 @@
         <v>1635</v>
       </c>
       <c r="D301" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="E301" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M301" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="302" spans="1:13">
@@ -11167,7 +11212,7 @@
         <v>1684</v>
       </c>
       <c r="M302" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="303" spans="1:13">
@@ -11181,13 +11226,13 @@
         <v>1635</v>
       </c>
       <c r="D303" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E303" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="M303" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="304" spans="1:13">
@@ -11201,13 +11246,13 @@
         <v>1635</v>
       </c>
       <c r="D304" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E304" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M304" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="305" spans="1:13">
@@ -11221,13 +11266,13 @@
         <v>1635</v>
       </c>
       <c r="D305" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="E305" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M305" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="306" spans="1:13">
@@ -11244,7 +11289,7 @@
         <v>1684</v>
       </c>
       <c r="M306" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="307" spans="1:13">
@@ -11261,7 +11306,7 @@
         <v>1684</v>
       </c>
       <c r="M307" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="308" spans="1:13">
@@ -11275,13 +11320,13 @@
         <v>1635</v>
       </c>
       <c r="D308" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E308" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M308" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="309" spans="1:13">
@@ -11295,13 +11340,13 @@
         <v>1635</v>
       </c>
       <c r="D309" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E309" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M309" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="310" spans="1:13">
@@ -11315,13 +11360,13 @@
         <v>1635</v>
       </c>
       <c r="D310" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E310" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M310" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="311" spans="1:13">
@@ -11335,13 +11380,13 @@
         <v>1635</v>
       </c>
       <c r="D311" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="E311" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M311" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="312" spans="1:13">
@@ -11355,10 +11400,10 @@
         <v>1644</v>
       </c>
       <c r="E312" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="M312" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="313" spans="1:13">
@@ -11372,10 +11417,10 @@
         <v>1644</v>
       </c>
       <c r="E313" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="M313" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="314" spans="1:13">
@@ -11392,7 +11437,7 @@
         <v>1685</v>
       </c>
       <c r="M314" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="315" spans="1:13">
@@ -11406,7 +11451,7 @@
         <v>1652</v>
       </c>
       <c r="M315" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="316" spans="1:13">
@@ -11420,7 +11465,7 @@
         <v>1638</v>
       </c>
       <c r="M316" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="317" spans="1:13">
@@ -11437,7 +11482,7 @@
         <v>1685</v>
       </c>
       <c r="M317" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="318" spans="1:13">
@@ -11451,7 +11496,7 @@
         <v>1639</v>
       </c>
       <c r="M318" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="319" spans="1:13">
@@ -11471,7 +11516,7 @@
         <v>1686</v>
       </c>
       <c r="M319" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="320" spans="1:13">
@@ -11488,7 +11533,7 @@
         <v>1685</v>
       </c>
       <c r="M320" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="321" spans="1:13">
@@ -11505,7 +11550,7 @@
         <v>1685</v>
       </c>
       <c r="M321" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="322" spans="1:13">
@@ -11519,10 +11564,10 @@
         <v>1641</v>
       </c>
       <c r="D322" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="M322" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="323" spans="1:13">
@@ -11536,10 +11581,10 @@
         <v>1641</v>
       </c>
       <c r="D323" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="M323" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="324" spans="1:13">
@@ -11553,10 +11598,10 @@
         <v>1641</v>
       </c>
       <c r="D324" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="M324" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="325" spans="1:13">
@@ -11570,10 +11615,10 @@
         <v>1641</v>
       </c>
       <c r="D325" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="M325" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="326" spans="1:13">
@@ -11587,10 +11632,10 @@
         <v>1641</v>
       </c>
       <c r="D326" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="M326" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="327" spans="1:13">
@@ -11604,10 +11649,10 @@
         <v>1641</v>
       </c>
       <c r="D327" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="M327" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="328" spans="1:13">
@@ -11621,10 +11666,10 @@
         <v>1641</v>
       </c>
       <c r="D328" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="M328" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="329" spans="1:13">
@@ -11638,7 +11683,7 @@
         <v>1641</v>
       </c>
       <c r="M329" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="330" spans="1:13">
@@ -11652,10 +11697,10 @@
         <v>1641</v>
       </c>
       <c r="D330" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="M330" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="331" spans="1:13">
@@ -11669,10 +11714,10 @@
         <v>1653</v>
       </c>
       <c r="D331" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="M331" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="332" spans="1:13">
@@ -11686,13 +11731,13 @@
         <v>1635</v>
       </c>
       <c r="D332" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="E332" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M332" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="333" spans="1:13">
@@ -11706,13 +11751,13 @@
         <v>1635</v>
       </c>
       <c r="D333" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="E333" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M333" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="334" spans="1:13">
@@ -11729,7 +11774,7 @@
         <v>1674</v>
       </c>
       <c r="M334" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="335" spans="1:13">
@@ -11746,7 +11791,7 @@
         <v>1674</v>
       </c>
       <c r="M335" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="336" spans="1:13">
@@ -11763,7 +11808,7 @@
         <v>1674</v>
       </c>
       <c r="M336" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="337" spans="1:13">
@@ -11780,7 +11825,7 @@
         <v>1674</v>
       </c>
       <c r="M337" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="338" spans="1:13">
@@ -11797,7 +11842,7 @@
         <v>1674</v>
       </c>
       <c r="M338" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="339" spans="1:13">
@@ -11814,7 +11859,7 @@
         <v>1674</v>
       </c>
       <c r="M339" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="340" spans="1:13">
@@ -11831,7 +11876,7 @@
         <v>1674</v>
       </c>
       <c r="M340" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="341" spans="1:13">
@@ -11848,7 +11893,7 @@
         <v>1674</v>
       </c>
       <c r="M341" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="342" spans="1:13">
@@ -11865,7 +11910,7 @@
         <v>1674</v>
       </c>
       <c r="M342" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="343" spans="1:13">
@@ -11882,7 +11927,7 @@
         <v>1674</v>
       </c>
       <c r="M343" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="344" spans="1:13">
@@ -11899,7 +11944,7 @@
         <v>1674</v>
       </c>
       <c r="M344" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="345" spans="1:13">
@@ -11916,7 +11961,7 @@
         <v>1674</v>
       </c>
       <c r="M345" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="346" spans="1:13">
@@ -11933,7 +11978,7 @@
         <v>1674</v>
       </c>
       <c r="M346" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="347" spans="1:13">
@@ -11950,7 +11995,7 @@
         <v>1674</v>
       </c>
       <c r="M347" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="348" spans="1:13">
@@ -11967,7 +12012,7 @@
         <v>1674</v>
       </c>
       <c r="M348" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="349" spans="1:13">
@@ -11984,7 +12029,7 @@
         <v>1674</v>
       </c>
       <c r="M349" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="350" spans="1:13">
@@ -12001,7 +12046,7 @@
         <v>1674</v>
       </c>
       <c r="M350" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="351" spans="1:13">
@@ -12018,7 +12063,7 @@
         <v>1674</v>
       </c>
       <c r="M351" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="352" spans="1:13">
@@ -12035,7 +12080,7 @@
         <v>1674</v>
       </c>
       <c r="M352" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="353" spans="1:13">
@@ -12052,7 +12097,7 @@
         <v>1674</v>
       </c>
       <c r="M353" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="354" spans="1:13">
@@ -12069,7 +12114,7 @@
         <v>1674</v>
       </c>
       <c r="M354" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="355" spans="1:13">
@@ -12086,7 +12131,7 @@
         <v>1674</v>
       </c>
       <c r="M355" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="356" spans="1:13">
@@ -12103,7 +12148,7 @@
         <v>1674</v>
       </c>
       <c r="M356" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="357" spans="1:13">
@@ -12120,7 +12165,7 @@
         <v>1674</v>
       </c>
       <c r="M357" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="358" spans="1:13">
@@ -12137,7 +12182,7 @@
         <v>1674</v>
       </c>
       <c r="M358" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="359" spans="1:13">
@@ -12154,7 +12199,7 @@
         <v>1674</v>
       </c>
       <c r="M359" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="360" spans="1:13">
@@ -12171,7 +12216,7 @@
         <v>1674</v>
       </c>
       <c r="M360" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="361" spans="1:13">
@@ -12188,7 +12233,7 @@
         <v>1674</v>
       </c>
       <c r="M361" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="362" spans="1:13">
@@ -12205,7 +12250,7 @@
         <v>1674</v>
       </c>
       <c r="M362" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="363" spans="1:13">
@@ -12222,7 +12267,7 @@
         <v>1674</v>
       </c>
       <c r="M363" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="364" spans="1:13">
@@ -12239,7 +12284,7 @@
         <v>1674</v>
       </c>
       <c r="M364" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="365" spans="1:13">
@@ -12256,7 +12301,7 @@
         <v>1674</v>
       </c>
       <c r="M365" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="366" spans="1:13">
@@ -12273,7 +12318,7 @@
         <v>1674</v>
       </c>
       <c r="M366" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="367" spans="1:13">
@@ -12290,7 +12335,7 @@
         <v>1674</v>
       </c>
       <c r="M367" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="368" spans="1:13">
@@ -12307,7 +12352,7 @@
         <v>1674</v>
       </c>
       <c r="M368" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="369" spans="1:13">
@@ -12324,7 +12369,7 @@
         <v>1674</v>
       </c>
       <c r="M369" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="370" spans="1:13">
@@ -12341,7 +12386,7 @@
         <v>1674</v>
       </c>
       <c r="M370" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="371" spans="1:13">
@@ -12358,7 +12403,7 @@
         <v>1674</v>
       </c>
       <c r="M371" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="372" spans="1:13">
@@ -12375,7 +12420,7 @@
         <v>1674</v>
       </c>
       <c r="M372" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="373" spans="1:13">
@@ -12392,7 +12437,7 @@
         <v>1674</v>
       </c>
       <c r="M373" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="374" spans="1:13">
@@ -12409,7 +12454,7 @@
         <v>1674</v>
       </c>
       <c r="M374" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="375" spans="1:13">
@@ -12426,7 +12471,7 @@
         <v>1674</v>
       </c>
       <c r="M375" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="376" spans="1:13">
@@ -12443,7 +12488,7 @@
         <v>1674</v>
       </c>
       <c r="M376" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="377" spans="1:13">
@@ -12460,7 +12505,7 @@
         <v>1674</v>
       </c>
       <c r="M377" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="378" spans="1:13">
@@ -12477,7 +12522,7 @@
         <v>1674</v>
       </c>
       <c r="M378" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="379" spans="1:13">
@@ -12494,7 +12539,7 @@
         <v>1674</v>
       </c>
       <c r="M379" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="380" spans="1:13">
@@ -12511,7 +12556,7 @@
         <v>1674</v>
       </c>
       <c r="M380" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="381" spans="1:13">
@@ -12528,7 +12573,7 @@
         <v>1674</v>
       </c>
       <c r="M381" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="382" spans="1:13">
@@ -12545,7 +12590,7 @@
         <v>1674</v>
       </c>
       <c r="M382" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="383" spans="1:13">
@@ -12562,7 +12607,7 @@
         <v>1674</v>
       </c>
       <c r="M383" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="384" spans="1:13">
@@ -12579,7 +12624,7 @@
         <v>1674</v>
       </c>
       <c r="M384" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="385" spans="1:13">
@@ -12596,7 +12641,7 @@
         <v>1674</v>
       </c>
       <c r="M385" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="386" spans="1:13">
@@ -12613,7 +12658,7 @@
         <v>1674</v>
       </c>
       <c r="M386" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="387" spans="1:13">
@@ -12630,7 +12675,7 @@
         <v>1674</v>
       </c>
       <c r="M387" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="388" spans="1:13">
@@ -12647,7 +12692,7 @@
         <v>1674</v>
       </c>
       <c r="M388" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="389" spans="1:13">
@@ -12664,7 +12709,7 @@
         <v>1674</v>
       </c>
       <c r="M389" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="390" spans="1:13">
@@ -12681,7 +12726,7 @@
         <v>1674</v>
       </c>
       <c r="M390" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="391" spans="1:13">
@@ -12698,7 +12743,7 @@
         <v>1674</v>
       </c>
       <c r="M391" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="392" spans="1:13">
@@ -12712,7 +12757,7 @@
         <v>1644</v>
       </c>
       <c r="M392" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="393" spans="1:13">
@@ -12726,7 +12771,7 @@
         <v>1644</v>
       </c>
       <c r="M393" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="394" spans="1:13">
@@ -12740,7 +12785,7 @@
         <v>1644</v>
       </c>
       <c r="M394" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="395" spans="1:13">
@@ -12754,7 +12799,7 @@
         <v>1644</v>
       </c>
       <c r="M395" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="396" spans="1:13">
@@ -12768,7 +12813,7 @@
         <v>1644</v>
       </c>
       <c r="M396" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="397" spans="1:13">
@@ -12785,7 +12830,7 @@
         <v>1674</v>
       </c>
       <c r="M397" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="398" spans="1:13">
@@ -12802,7 +12847,7 @@
         <v>1674</v>
       </c>
       <c r="M398" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="399" spans="1:13">
@@ -12819,7 +12864,7 @@
         <v>1674</v>
       </c>
       <c r="M399" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="400" spans="1:13">
@@ -12836,7 +12881,7 @@
         <v>1674</v>
       </c>
       <c r="M400" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="401" spans="1:13">
@@ -12850,7 +12895,7 @@
         <v>1644</v>
       </c>
       <c r="M401" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="402" spans="1:13">
@@ -12864,7 +12909,7 @@
         <v>1644</v>
       </c>
       <c r="M402" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="403" spans="1:13">
@@ -12878,7 +12923,7 @@
         <v>1644</v>
       </c>
       <c r="M403" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="404" spans="1:13">
@@ -12892,7 +12937,7 @@
         <v>1644</v>
       </c>
       <c r="M404" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="405" spans="1:13">
@@ -12906,7 +12951,7 @@
         <v>1644</v>
       </c>
       <c r="M405" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="406" spans="1:13">
@@ -12920,7 +12965,7 @@
         <v>1644</v>
       </c>
       <c r="M406" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="407" spans="1:13">
@@ -12937,7 +12982,7 @@
         <v>1674</v>
       </c>
       <c r="M407" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="408" spans="1:13">
@@ -12954,7 +12999,7 @@
         <v>1674</v>
       </c>
       <c r="M408" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="409" spans="1:13">
@@ -12971,7 +13016,7 @@
         <v>1674</v>
       </c>
       <c r="M409" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="410" spans="1:13">
@@ -12988,7 +13033,7 @@
         <v>1674</v>
       </c>
       <c r="M410" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="411" spans="1:13">
@@ -13005,7 +13050,7 @@
         <v>1674</v>
       </c>
       <c r="M411" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="412" spans="1:13">
@@ -13022,7 +13067,7 @@
         <v>1674</v>
       </c>
       <c r="M412" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="413" spans="1:13">
@@ -13039,7 +13084,7 @@
         <v>1674</v>
       </c>
       <c r="M413" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="414" spans="1:13">
@@ -13056,7 +13101,7 @@
         <v>1674</v>
       </c>
       <c r="M414" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="415" spans="1:13">
@@ -13073,7 +13118,7 @@
         <v>1674</v>
       </c>
       <c r="M415" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="416" spans="1:13">
@@ -13090,7 +13135,7 @@
         <v>1674</v>
       </c>
       <c r="M416" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="417" spans="1:13">
@@ -13107,7 +13152,7 @@
         <v>1674</v>
       </c>
       <c r="M417" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="418" spans="1:13">
@@ -13124,7 +13169,7 @@
         <v>1674</v>
       </c>
       <c r="M418" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="419" spans="1:13">
@@ -13141,7 +13186,7 @@
         <v>1674</v>
       </c>
       <c r="M419" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="420" spans="1:13">
@@ -13158,7 +13203,7 @@
         <v>1674</v>
       </c>
       <c r="M420" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="421" spans="1:13">
@@ -13175,7 +13220,7 @@
         <v>1674</v>
       </c>
       <c r="M421" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="422" spans="1:13">
@@ -13192,7 +13237,7 @@
         <v>1674</v>
       </c>
       <c r="M422" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="423" spans="1:13">
@@ -13209,7 +13254,7 @@
         <v>1674</v>
       </c>
       <c r="M423" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="424" spans="1:13">
@@ -13226,7 +13271,7 @@
         <v>1674</v>
       </c>
       <c r="M424" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="425" spans="1:13">
@@ -13243,7 +13288,7 @@
         <v>1674</v>
       </c>
       <c r="M425" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="426" spans="1:13">
@@ -13260,7 +13305,7 @@
         <v>1674</v>
       </c>
       <c r="M426" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="427" spans="1:13">
@@ -13277,7 +13322,7 @@
         <v>1674</v>
       </c>
       <c r="M427" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="428" spans="1:13">
@@ -13294,7 +13339,7 @@
         <v>1674</v>
       </c>
       <c r="M428" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="429" spans="1:13">
@@ -13311,7 +13356,7 @@
         <v>1674</v>
       </c>
       <c r="M429" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="430" spans="1:13">
@@ -13328,7 +13373,7 @@
         <v>1674</v>
       </c>
       <c r="M430" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="431" spans="1:13">
@@ -13345,7 +13390,7 @@
         <v>1674</v>
       </c>
       <c r="M431" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="432" spans="1:13">
@@ -13362,7 +13407,7 @@
         <v>1674</v>
       </c>
       <c r="M432" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="433" spans="1:13">
@@ -13379,7 +13424,7 @@
         <v>1674</v>
       </c>
       <c r="M433" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="434" spans="1:13">
@@ -13396,7 +13441,7 @@
         <v>1674</v>
       </c>
       <c r="M434" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="435" spans="1:13">
@@ -13413,7 +13458,7 @@
         <v>1674</v>
       </c>
       <c r="M435" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="436" spans="1:13">
@@ -13430,7 +13475,7 @@
         <v>1674</v>
       </c>
       <c r="M436" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="437" spans="1:13">
@@ -13447,7 +13492,7 @@
         <v>1674</v>
       </c>
       <c r="M437" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="438" spans="1:13">
@@ -13464,7 +13509,7 @@
         <v>1674</v>
       </c>
       <c r="M438" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="439" spans="1:13">
@@ -13478,10 +13523,10 @@
         <v>1644</v>
       </c>
       <c r="E439" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M439" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="440" spans="1:13">
@@ -13498,7 +13543,7 @@
         <v>1674</v>
       </c>
       <c r="M440" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="441" spans="1:13">
@@ -13515,7 +13560,7 @@
         <v>1674</v>
       </c>
       <c r="M441" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="442" spans="1:13">
@@ -13532,7 +13577,7 @@
         <v>1674</v>
       </c>
       <c r="M442" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="443" spans="1:13">
@@ -13549,7 +13594,7 @@
         <v>1674</v>
       </c>
       <c r="M443" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="444" spans="1:13">
@@ -13566,10 +13611,10 @@
         <v>1674</v>
       </c>
       <c r="E444" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M444" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="445" spans="1:13">
@@ -13586,10 +13631,10 @@
         <v>1674</v>
       </c>
       <c r="E445" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="M445" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="446" spans="1:13">
@@ -13606,7 +13651,7 @@
         <v>1674</v>
       </c>
       <c r="M446" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="447" spans="1:13">
@@ -13623,7 +13668,7 @@
         <v>1674</v>
       </c>
       <c r="M447" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="448" spans="1:13">
@@ -13643,7 +13688,7 @@
         <v>1674</v>
       </c>
       <c r="M448" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="449" spans="1:13">
@@ -13663,7 +13708,7 @@
         <v>1674</v>
       </c>
       <c r="M449" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="450" spans="1:13">
@@ -13683,7 +13728,7 @@
         <v>1674</v>
       </c>
       <c r="M450" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="451" spans="1:13">
@@ -13700,10 +13745,10 @@
         <v>1686</v>
       </c>
       <c r="E451" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M451" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="452" spans="1:13">
@@ -13720,7 +13765,7 @@
         <v>1674</v>
       </c>
       <c r="M452" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="453" spans="1:13">
@@ -13740,7 +13785,7 @@
         <v>1674</v>
       </c>
       <c r="M453" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="454" spans="1:13">
@@ -13760,7 +13805,7 @@
         <v>1674</v>
       </c>
       <c r="M454" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="455" spans="1:13">
@@ -13777,7 +13822,7 @@
         <v>1674</v>
       </c>
       <c r="M455" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="456" spans="1:13">
@@ -13794,7 +13839,7 @@
         <v>1674</v>
       </c>
       <c r="M456" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="457" spans="1:13">
@@ -13811,7 +13856,7 @@
         <v>1674</v>
       </c>
       <c r="M457" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="458" spans="1:13">
@@ -13828,7 +13873,7 @@
         <v>1674</v>
       </c>
       <c r="M458" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="459" spans="1:13">
@@ -13845,7 +13890,7 @@
         <v>1674</v>
       </c>
       <c r="M459" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="460" spans="1:13">
@@ -13862,7 +13907,7 @@
         <v>1674</v>
       </c>
       <c r="M460" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="461" spans="1:13">
@@ -13879,7 +13924,7 @@
         <v>1674</v>
       </c>
       <c r="M461" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="462" spans="1:13">
@@ -13896,7 +13941,7 @@
         <v>1675</v>
       </c>
       <c r="M462" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="463" spans="1:13">
@@ -13910,10 +13955,10 @@
         <v>1644</v>
       </c>
       <c r="E463" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="M463" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="464" spans="1:13">
@@ -13927,10 +13972,10 @@
         <v>1644</v>
       </c>
       <c r="E464" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M464" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="465" spans="1:13">
@@ -13944,10 +13989,10 @@
         <v>1644</v>
       </c>
       <c r="E465" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M465" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="466" spans="1:13">
@@ -13961,7 +14006,7 @@
         <v>1644</v>
       </c>
       <c r="M466" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="467" spans="1:13">
@@ -13975,10 +14020,10 @@
         <v>1644</v>
       </c>
       <c r="E467" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="M467" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="468" spans="1:13">
@@ -13992,13 +14037,13 @@
         <v>1649</v>
       </c>
       <c r="D468" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="E468" t="s">
         <v>1686</v>
       </c>
       <c r="M468" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="469" spans="1:13">
@@ -14012,13 +14057,13 @@
         <v>1654</v>
       </c>
       <c r="D469" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="E469" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="M469" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="470" spans="1:13">
@@ -14032,13 +14077,13 @@
         <v>1654</v>
       </c>
       <c r="D470" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="E470" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="M470" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="471" spans="1:13">
@@ -14052,13 +14097,13 @@
         <v>1654</v>
       </c>
       <c r="D471" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="E471" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="M471" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="472" spans="1:13">
@@ -14072,10 +14117,10 @@
         <v>1648</v>
       </c>
       <c r="D472" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="M472" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="473" spans="1:13">
@@ -14092,7 +14137,7 @@
         <v>1655</v>
       </c>
       <c r="M473" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="474" spans="1:13">
@@ -14109,7 +14154,7 @@
         <v>1655</v>
       </c>
       <c r="M474" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="475" spans="1:13">
@@ -14126,7 +14171,7 @@
         <v>1655</v>
       </c>
       <c r="M475" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="476" spans="1:13">
@@ -14143,7 +14188,7 @@
         <v>1667</v>
       </c>
       <c r="M476" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="477" spans="1:13">
@@ -14163,7 +14208,7 @@
         <v>1686</v>
       </c>
       <c r="M477" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="478" spans="1:13">
@@ -14180,7 +14225,7 @@
         <v>1667</v>
       </c>
       <c r="M478" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="479" spans="1:13">
@@ -14197,7 +14242,7 @@
         <v>1658</v>
       </c>
       <c r="M479" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="480" spans="1:13">
@@ -14214,7 +14259,7 @@
         <v>1658</v>
       </c>
       <c r="M480" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="481" spans="1:13">
@@ -14231,7 +14276,7 @@
         <v>1658</v>
       </c>
       <c r="M481" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="482" spans="1:13">
@@ -14248,7 +14293,7 @@
         <v>1667</v>
       </c>
       <c r="M482" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="483" spans="1:13">
@@ -14265,7 +14310,7 @@
         <v>1658</v>
       </c>
       <c r="M483" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="484" spans="1:13">
@@ -14282,7 +14327,7 @@
         <v>1658</v>
       </c>
       <c r="M484" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="485" spans="1:13">
@@ -14299,7 +14344,7 @@
         <v>1658</v>
       </c>
       <c r="M485" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="486" spans="1:13">
@@ -14316,7 +14361,7 @@
         <v>1658</v>
       </c>
       <c r="M486" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="487" spans="1:13">
@@ -14333,7 +14378,7 @@
         <v>1658</v>
       </c>
       <c r="M487" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="488" spans="1:13">
@@ -14350,7 +14395,7 @@
         <v>1658</v>
       </c>
       <c r="M488" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="489" spans="1:13">
@@ -14367,7 +14412,7 @@
         <v>1658</v>
       </c>
       <c r="M489" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="490" spans="1:13">
@@ -14384,7 +14429,7 @@
         <v>1658</v>
       </c>
       <c r="M490" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="491" spans="1:13">
@@ -14401,7 +14446,7 @@
         <v>1667</v>
       </c>
       <c r="M491" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="492" spans="1:13">
@@ -14418,7 +14463,7 @@
         <v>1667</v>
       </c>
       <c r="M492" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="493" spans="1:13">
@@ -14435,7 +14480,7 @@
         <v>1667</v>
       </c>
       <c r="M493" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="494" spans="1:13">
@@ -14452,7 +14497,7 @@
         <v>1667</v>
       </c>
       <c r="M494" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="495" spans="1:13">
@@ -14469,7 +14514,7 @@
         <v>1667</v>
       </c>
       <c r="M495" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="496" spans="1:13">
@@ -14486,7 +14531,7 @@
         <v>1667</v>
       </c>
       <c r="M496" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="497" spans="1:13">
@@ -14503,7 +14548,7 @@
         <v>1667</v>
       </c>
       <c r="M497" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="498" spans="1:13">
@@ -14520,7 +14565,7 @@
         <v>1667</v>
       </c>
       <c r="M498" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="499" spans="1:13">
@@ -14537,7 +14582,7 @@
         <v>1667</v>
       </c>
       <c r="M499" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="500" spans="1:13">
@@ -14554,7 +14599,7 @@
         <v>1667</v>
       </c>
       <c r="M500" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="501" spans="1:13">
@@ -14571,7 +14616,7 @@
         <v>1667</v>
       </c>
       <c r="M501" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="502" spans="1:13">
@@ -14588,7 +14633,7 @@
         <v>1667</v>
       </c>
       <c r="M502" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="503" spans="1:13">
@@ -14605,7 +14650,7 @@
         <v>1667</v>
       </c>
       <c r="M503" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="504" spans="1:13">
@@ -14622,7 +14667,7 @@
         <v>1667</v>
       </c>
       <c r="M504" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="505" spans="1:13">
@@ -14639,7 +14684,7 @@
         <v>1667</v>
       </c>
       <c r="M505" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="506" spans="1:13">
@@ -14656,7 +14701,7 @@
         <v>1667</v>
       </c>
       <c r="M506" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="507" spans="1:13">
@@ -14673,7 +14718,7 @@
         <v>1667</v>
       </c>
       <c r="M507" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="508" spans="1:13">
@@ -14690,7 +14735,7 @@
         <v>1667</v>
       </c>
       <c r="M508" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="509" spans="1:13">
@@ -14707,7 +14752,7 @@
         <v>1667</v>
       </c>
       <c r="M509" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="510" spans="1:13">
@@ -14724,7 +14769,7 @@
         <v>1667</v>
       </c>
       <c r="M510" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="511" spans="1:13">
@@ -14741,7 +14786,7 @@
         <v>1667</v>
       </c>
       <c r="M511" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="512" spans="1:13">
@@ -14758,7 +14803,7 @@
         <v>1667</v>
       </c>
       <c r="M512" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="513" spans="1:13">
@@ -14775,7 +14820,7 @@
         <v>1667</v>
       </c>
       <c r="M513" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="514" spans="1:13">
@@ -14792,7 +14837,7 @@
         <v>1667</v>
       </c>
       <c r="M514" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="515" spans="1:13">
@@ -14809,7 +14854,7 @@
         <v>1667</v>
       </c>
       <c r="M515" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="516" spans="1:13">
@@ -14826,7 +14871,7 @@
         <v>1667</v>
       </c>
       <c r="M516" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="517" spans="1:13">
@@ -14843,7 +14888,7 @@
         <v>1667</v>
       </c>
       <c r="M517" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="518" spans="1:13">
@@ -14860,7 +14905,7 @@
         <v>1667</v>
       </c>
       <c r="M518" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="519" spans="1:13">
@@ -14877,7 +14922,7 @@
         <v>1667</v>
       </c>
       <c r="M519" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="520" spans="1:13">
@@ -14894,7 +14939,7 @@
         <v>1667</v>
       </c>
       <c r="M520" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="521" spans="1:13">
@@ -14911,7 +14956,7 @@
         <v>1667</v>
       </c>
       <c r="M521" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="522" spans="1:13">
@@ -14928,7 +14973,7 @@
         <v>1667</v>
       </c>
       <c r="M522" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="523" spans="1:13">
@@ -14945,7 +14990,7 @@
         <v>1667</v>
       </c>
       <c r="M523" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="524" spans="1:13">
@@ -14962,7 +15007,7 @@
         <v>1667</v>
       </c>
       <c r="M524" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="525" spans="1:13">
@@ -14979,7 +15024,7 @@
         <v>1667</v>
       </c>
       <c r="M525" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="526" spans="1:13">
@@ -14996,7 +15041,7 @@
         <v>1667</v>
       </c>
       <c r="M526" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="527" spans="1:13">
@@ -15013,7 +15058,7 @@
         <v>1667</v>
       </c>
       <c r="M527" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="528" spans="1:13">
@@ -15030,7 +15075,7 @@
         <v>1667</v>
       </c>
       <c r="M528" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="529" spans="1:13">
@@ -15047,7 +15092,7 @@
         <v>1667</v>
       </c>
       <c r="M529" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="530" spans="1:13">
@@ -15064,7 +15109,7 @@
         <v>1667</v>
       </c>
       <c r="M530" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="531" spans="1:13">
@@ -15081,7 +15126,7 @@
         <v>1667</v>
       </c>
       <c r="M531" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="532" spans="1:13">
@@ -15098,7 +15143,7 @@
         <v>1667</v>
       </c>
       <c r="M532" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="533" spans="1:13">
@@ -15115,7 +15160,7 @@
         <v>1667</v>
       </c>
       <c r="M533" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="534" spans="1:13">
@@ -15132,7 +15177,7 @@
         <v>1667</v>
       </c>
       <c r="M534" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="535" spans="1:13">
@@ -15149,7 +15194,7 @@
         <v>1667</v>
       </c>
       <c r="M535" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="536" spans="1:13">
@@ -15166,7 +15211,7 @@
         <v>1667</v>
       </c>
       <c r="M536" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="537" spans="1:13">
@@ -15183,7 +15228,7 @@
         <v>1667</v>
       </c>
       <c r="M537" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="538" spans="1:13">
@@ -15200,7 +15245,7 @@
         <v>1667</v>
       </c>
       <c r="M538" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="539" spans="1:13">
@@ -15217,7 +15262,7 @@
         <v>1667</v>
       </c>
       <c r="M539" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="540" spans="1:13">
@@ -15234,7 +15279,7 @@
         <v>1667</v>
       </c>
       <c r="M540" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="541" spans="1:13">
@@ -15251,7 +15296,7 @@
         <v>1667</v>
       </c>
       <c r="M541" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="542" spans="1:13">
@@ -15268,7 +15313,7 @@
         <v>1667</v>
       </c>
       <c r="M542" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="543" spans="1:13">
@@ -15285,7 +15330,7 @@
         <v>1667</v>
       </c>
       <c r="M543" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="544" spans="1:13">
@@ -15302,7 +15347,7 @@
         <v>1667</v>
       </c>
       <c r="M544" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="545" spans="1:13">
@@ -15319,7 +15364,7 @@
         <v>1667</v>
       </c>
       <c r="M545" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="546" spans="1:13">
@@ -15336,7 +15381,7 @@
         <v>1667</v>
       </c>
       <c r="M546" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="547" spans="1:13">
@@ -15353,7 +15398,7 @@
         <v>1667</v>
       </c>
       <c r="M547" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="548" spans="1:13">
@@ -15370,7 +15415,7 @@
         <v>1667</v>
       </c>
       <c r="M548" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="549" spans="1:13">
@@ -15387,7 +15432,7 @@
         <v>1667</v>
       </c>
       <c r="M549" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="550" spans="1:13">
@@ -15404,7 +15449,7 @@
         <v>1667</v>
       </c>
       <c r="M550" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="551" spans="1:13">
@@ -15421,7 +15466,7 @@
         <v>1667</v>
       </c>
       <c r="M551" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="552" spans="1:13">
@@ -15438,7 +15483,7 @@
         <v>1667</v>
       </c>
       <c r="M552" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="553" spans="1:13">
@@ -15455,7 +15500,7 @@
         <v>1667</v>
       </c>
       <c r="M553" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="554" spans="1:13">
@@ -15472,7 +15517,7 @@
         <v>1667</v>
       </c>
       <c r="M554" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="555" spans="1:13">
@@ -15489,7 +15534,7 @@
         <v>1667</v>
       </c>
       <c r="M555" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="556" spans="1:13">
@@ -15506,7 +15551,7 @@
         <v>1667</v>
       </c>
       <c r="M556" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="557" spans="1:13">
@@ -15523,7 +15568,7 @@
         <v>1667</v>
       </c>
       <c r="M557" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="558" spans="1:13">
@@ -15540,7 +15585,7 @@
         <v>1667</v>
       </c>
       <c r="M558" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="559" spans="1:13">
@@ -15557,7 +15602,7 @@
         <v>1667</v>
       </c>
       <c r="M559" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="560" spans="1:13">
@@ -15574,7 +15619,7 @@
         <v>1667</v>
       </c>
       <c r="M560" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="561" spans="1:13">
@@ -15591,7 +15636,7 @@
         <v>1667</v>
       </c>
       <c r="M561" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="562" spans="1:13">
@@ -15608,7 +15653,7 @@
         <v>1667</v>
       </c>
       <c r="M562" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="563" spans="1:13">
@@ -15625,7 +15670,7 @@
         <v>1667</v>
       </c>
       <c r="M563" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="564" spans="1:13">
@@ -15642,7 +15687,7 @@
         <v>1667</v>
       </c>
       <c r="M564" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="565" spans="1:13">
@@ -15659,7 +15704,7 @@
         <v>1667</v>
       </c>
       <c r="M565" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="566" spans="1:13">
@@ -15676,7 +15721,7 @@
         <v>1667</v>
       </c>
       <c r="M566" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="567" spans="1:13">
@@ -15693,7 +15738,7 @@
         <v>1667</v>
       </c>
       <c r="M567" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="568" spans="1:13">
@@ -15710,7 +15755,7 @@
         <v>1667</v>
       </c>
       <c r="M568" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="569" spans="1:13">
@@ -15727,7 +15772,7 @@
         <v>1667</v>
       </c>
       <c r="M569" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="570" spans="1:13">
@@ -15744,7 +15789,7 @@
         <v>1667</v>
       </c>
       <c r="M570" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="571" spans="1:13">
@@ -15761,7 +15806,7 @@
         <v>1667</v>
       </c>
       <c r="M571" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="572" spans="1:13">
@@ -15778,7 +15823,7 @@
         <v>1667</v>
       </c>
       <c r="M572" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="573" spans="1:13">
@@ -15795,7 +15840,7 @@
         <v>1667</v>
       </c>
       <c r="M573" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="574" spans="1:13">
@@ -15812,7 +15857,7 @@
         <v>1667</v>
       </c>
       <c r="M574" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="575" spans="1:13">
@@ -15829,7 +15874,7 @@
         <v>1667</v>
       </c>
       <c r="M575" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="576" spans="1:13">
@@ -15846,7 +15891,7 @@
         <v>1667</v>
       </c>
       <c r="M576" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="577" spans="1:13">
@@ -15863,7 +15908,7 @@
         <v>1667</v>
       </c>
       <c r="M577" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="578" spans="1:13">
@@ -15880,7 +15925,7 @@
         <v>1667</v>
       </c>
       <c r="M578" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="579" spans="1:13">
@@ -15897,7 +15942,7 @@
         <v>1667</v>
       </c>
       <c r="M579" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="580" spans="1:13">
@@ -15914,7 +15959,7 @@
         <v>1667</v>
       </c>
       <c r="M580" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="581" spans="1:13">
@@ -15931,7 +15976,7 @@
         <v>1667</v>
       </c>
       <c r="M581" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="582" spans="1:13">
@@ -15948,7 +15993,7 @@
         <v>1667</v>
       </c>
       <c r="M582" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="583" spans="1:13">
@@ -15965,7 +16010,7 @@
         <v>1667</v>
       </c>
       <c r="M583" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="584" spans="1:13">
@@ -15982,7 +16027,7 @@
         <v>1667</v>
       </c>
       <c r="M584" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="585" spans="1:13">
@@ -15999,7 +16044,7 @@
         <v>1667</v>
       </c>
       <c r="M585" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="586" spans="1:13">
@@ -16016,7 +16061,7 @@
         <v>1667</v>
       </c>
       <c r="M586" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="587" spans="1:13">
@@ -16033,7 +16078,7 @@
         <v>1667</v>
       </c>
       <c r="M587" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="588" spans="1:13">
@@ -16050,7 +16095,7 @@
         <v>1667</v>
       </c>
       <c r="M588" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="589" spans="1:13">
@@ -16067,7 +16112,7 @@
         <v>1667</v>
       </c>
       <c r="M589" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="590" spans="1:13">
@@ -16084,7 +16129,7 @@
         <v>1667</v>
       </c>
       <c r="M590" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="591" spans="1:13">
@@ -16101,7 +16146,7 @@
         <v>1667</v>
       </c>
       <c r="M591" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="592" spans="1:13">
@@ -16118,7 +16163,7 @@
         <v>1667</v>
       </c>
       <c r="M592" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="593" spans="1:13">
@@ -16135,7 +16180,7 @@
         <v>1667</v>
       </c>
       <c r="M593" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="594" spans="1:13">
@@ -16152,7 +16197,7 @@
         <v>1667</v>
       </c>
       <c r="M594" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="595" spans="1:13">
@@ -16169,7 +16214,7 @@
         <v>1667</v>
       </c>
       <c r="M595" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="596" spans="1:13">
@@ -16186,7 +16231,7 @@
         <v>1667</v>
       </c>
       <c r="M596" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="597" spans="1:13">
@@ -16203,7 +16248,7 @@
         <v>1667</v>
       </c>
       <c r="M597" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="598" spans="1:13">
@@ -16220,7 +16265,7 @@
         <v>1667</v>
       </c>
       <c r="M598" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="599" spans="1:13">
@@ -16237,7 +16282,7 @@
         <v>1667</v>
       </c>
       <c r="M599" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="600" spans="1:13">
@@ -16254,7 +16299,7 @@
         <v>1667</v>
       </c>
       <c r="M600" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="601" spans="1:13">
@@ -16271,7 +16316,7 @@
         <v>1667</v>
       </c>
       <c r="M601" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="602" spans="1:13">
@@ -16288,7 +16333,7 @@
         <v>1667</v>
       </c>
       <c r="M602" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="603" spans="1:13">
@@ -16305,7 +16350,7 @@
         <v>1667</v>
       </c>
       <c r="M603" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="604" spans="1:13">
@@ -16322,7 +16367,7 @@
         <v>1667</v>
       </c>
       <c r="M604" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="605" spans="1:13">
@@ -16339,7 +16384,7 @@
         <v>1667</v>
       </c>
       <c r="M605" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="606" spans="1:13">
@@ -16356,7 +16401,7 @@
         <v>1667</v>
       </c>
       <c r="M606" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="607" spans="1:13">
@@ -16373,7 +16418,7 @@
         <v>1667</v>
       </c>
       <c r="M607" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="608" spans="1:13">
@@ -16390,7 +16435,7 @@
         <v>1667</v>
       </c>
       <c r="M608" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="609" spans="1:13">
@@ -16407,7 +16452,7 @@
         <v>1667</v>
       </c>
       <c r="M609" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="610" spans="1:13">
@@ -16424,7 +16469,7 @@
         <v>1667</v>
       </c>
       <c r="M610" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="611" spans="1:13">
@@ -16441,7 +16486,7 @@
         <v>1667</v>
       </c>
       <c r="M611" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="612" spans="1:13">
@@ -16458,7 +16503,7 @@
         <v>1667</v>
       </c>
       <c r="M612" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="613" spans="1:13">
@@ -16475,7 +16520,7 @@
         <v>1667</v>
       </c>
       <c r="M613" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="614" spans="1:13">
@@ -16492,7 +16537,7 @@
         <v>1667</v>
       </c>
       <c r="M614" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="615" spans="1:13">
@@ -16509,7 +16554,7 @@
         <v>1667</v>
       </c>
       <c r="M615" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="616" spans="1:13">
@@ -16526,7 +16571,7 @@
         <v>1667</v>
       </c>
       <c r="M616" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="617" spans="1:13">
@@ -16543,7 +16588,7 @@
         <v>1667</v>
       </c>
       <c r="M617" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="618" spans="1:13">
@@ -16560,7 +16605,7 @@
         <v>1667</v>
       </c>
       <c r="M618" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="619" spans="1:13">
@@ -16577,7 +16622,7 @@
         <v>1667</v>
       </c>
       <c r="M619" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="620" spans="1:13">
@@ -16594,7 +16639,7 @@
         <v>1667</v>
       </c>
       <c r="M620" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="621" spans="1:13">
@@ -16611,7 +16656,7 @@
         <v>1667</v>
       </c>
       <c r="M621" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="622" spans="1:13">
@@ -16628,7 +16673,7 @@
         <v>1667</v>
       </c>
       <c r="M622" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="623" spans="1:13">
@@ -16645,7 +16690,7 @@
         <v>1667</v>
       </c>
       <c r="M623" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="624" spans="1:13">
@@ -16662,7 +16707,7 @@
         <v>1667</v>
       </c>
       <c r="M624" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="625" spans="1:13">
@@ -16679,7 +16724,7 @@
         <v>1667</v>
       </c>
       <c r="M625" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="626" spans="1:13">
@@ -16696,7 +16741,7 @@
         <v>1667</v>
       </c>
       <c r="M626" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="627" spans="1:13">
@@ -16713,7 +16758,7 @@
         <v>1667</v>
       </c>
       <c r="M627" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="628" spans="1:13">
@@ -16730,7 +16775,7 @@
         <v>1667</v>
       </c>
       <c r="M628" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="629" spans="1:13">
@@ -16747,7 +16792,7 @@
         <v>1667</v>
       </c>
       <c r="M629" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="630" spans="1:13">
@@ -16764,7 +16809,7 @@
         <v>1667</v>
       </c>
       <c r="M630" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="631" spans="1:13">
@@ -16781,7 +16826,7 @@
         <v>1667</v>
       </c>
       <c r="M631" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="632" spans="1:13">
@@ -16798,7 +16843,7 @@
         <v>1667</v>
       </c>
       <c r="M632" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="633" spans="1:13">
@@ -16815,7 +16860,7 @@
         <v>1667</v>
       </c>
       <c r="M633" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="634" spans="1:13">
@@ -16832,7 +16877,7 @@
         <v>1667</v>
       </c>
       <c r="M634" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="635" spans="1:13">
@@ -16849,7 +16894,7 @@
         <v>1667</v>
       </c>
       <c r="M635" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="636" spans="1:13">
@@ -16866,7 +16911,7 @@
         <v>1667</v>
       </c>
       <c r="M636" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="637" spans="1:13">
@@ -16883,7 +16928,7 @@
         <v>1667</v>
       </c>
       <c r="M637" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="638" spans="1:13">
@@ -16900,7 +16945,7 @@
         <v>1667</v>
       </c>
       <c r="M638" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="639" spans="1:13">
@@ -16917,7 +16962,7 @@
         <v>1667</v>
       </c>
       <c r="M639" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="640" spans="1:13">
@@ -16934,7 +16979,7 @@
         <v>1667</v>
       </c>
       <c r="M640" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="641" spans="1:13">
@@ -16951,7 +16996,7 @@
         <v>1667</v>
       </c>
       <c r="M641" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="642" spans="1:13">
@@ -16968,7 +17013,7 @@
         <v>1667</v>
       </c>
       <c r="M642" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="643" spans="1:13">
@@ -16985,7 +17030,7 @@
         <v>1667</v>
       </c>
       <c r="M643" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="644" spans="1:13">
@@ -17002,7 +17047,7 @@
         <v>1667</v>
       </c>
       <c r="M644" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="645" spans="1:13">
@@ -17019,7 +17064,7 @@
         <v>1667</v>
       </c>
       <c r="M645" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="646" spans="1:13">
@@ -17036,7 +17081,7 @@
         <v>1667</v>
       </c>
       <c r="M646" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="647" spans="1:13">
@@ -17053,7 +17098,7 @@
         <v>1667</v>
       </c>
       <c r="M647" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="648" spans="1:13">
@@ -17070,7 +17115,7 @@
         <v>1667</v>
       </c>
       <c r="M648" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="649" spans="1:13">
@@ -17087,7 +17132,7 @@
         <v>1667</v>
       </c>
       <c r="M649" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="650" spans="1:13">
@@ -17104,7 +17149,7 @@
         <v>1667</v>
       </c>
       <c r="M650" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="651" spans="1:13">
@@ -17121,7 +17166,7 @@
         <v>1667</v>
       </c>
       <c r="M651" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="652" spans="1:13">
@@ -17138,7 +17183,7 @@
         <v>1667</v>
       </c>
       <c r="M652" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="653" spans="1:13">
@@ -17155,7 +17200,7 @@
         <v>1667</v>
       </c>
       <c r="M653" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="654" spans="1:13">
@@ -17172,7 +17217,7 @@
         <v>1667</v>
       </c>
       <c r="M654" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="655" spans="1:13">
@@ -17189,7 +17234,7 @@
         <v>1667</v>
       </c>
       <c r="M655" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="656" spans="1:13">
@@ -17206,7 +17251,7 @@
         <v>1667</v>
       </c>
       <c r="M656" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="657" spans="1:13">
@@ -17223,7 +17268,7 @@
         <v>1667</v>
       </c>
       <c r="M657" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="658" spans="1:13">
@@ -17240,7 +17285,7 @@
         <v>1667</v>
       </c>
       <c r="M658" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="659" spans="1:13">
@@ -17257,7 +17302,7 @@
         <v>1667</v>
       </c>
       <c r="M659" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="660" spans="1:13">
@@ -17274,7 +17319,7 @@
         <v>1667</v>
       </c>
       <c r="M660" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="661" spans="1:13">
@@ -17291,7 +17336,7 @@
         <v>1667</v>
       </c>
       <c r="M661" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="662" spans="1:13">
@@ -17308,7 +17353,7 @@
         <v>1667</v>
       </c>
       <c r="M662" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="663" spans="1:13">
@@ -17325,7 +17370,7 @@
         <v>1667</v>
       </c>
       <c r="M663" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="664" spans="1:13">
@@ -17342,7 +17387,7 @@
         <v>1667</v>
       </c>
       <c r="M664" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="665" spans="1:13">
@@ -17359,7 +17404,7 @@
         <v>1667</v>
       </c>
       <c r="M665" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="666" spans="1:13">
@@ -17376,7 +17421,7 @@
         <v>1667</v>
       </c>
       <c r="M666" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="667" spans="1:13">
@@ -17393,7 +17438,7 @@
         <v>1667</v>
       </c>
       <c r="M667" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="668" spans="1:13">
@@ -17410,7 +17455,7 @@
         <v>1667</v>
       </c>
       <c r="M668" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="669" spans="1:13">
@@ -17427,7 +17472,7 @@
         <v>1667</v>
       </c>
       <c r="M669" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="670" spans="1:13">
@@ -17444,7 +17489,7 @@
         <v>1667</v>
       </c>
       <c r="M670" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="671" spans="1:13">
@@ -17461,7 +17506,7 @@
         <v>1667</v>
       </c>
       <c r="M671" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="672" spans="1:13">
@@ -17478,7 +17523,7 @@
         <v>1667</v>
       </c>
       <c r="M672" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="673" spans="1:13">
@@ -17495,7 +17540,7 @@
         <v>1667</v>
       </c>
       <c r="M673" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="674" spans="1:13">
@@ -17512,7 +17557,7 @@
         <v>1667</v>
       </c>
       <c r="M674" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="675" spans="1:13">
@@ -17529,7 +17574,7 @@
         <v>1667</v>
       </c>
       <c r="M675" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="676" spans="1:13">
@@ -17546,7 +17591,7 @@
         <v>1667</v>
       </c>
       <c r="M676" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="677" spans="1:13">
@@ -17563,7 +17608,7 @@
         <v>1667</v>
       </c>
       <c r="M677" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="678" spans="1:13">
@@ -17580,7 +17625,7 @@
         <v>1667</v>
       </c>
       <c r="M678" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="679" spans="1:13">
@@ -17597,7 +17642,7 @@
         <v>1667</v>
       </c>
       <c r="M679" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="680" spans="1:13">
@@ -17614,7 +17659,7 @@
         <v>1667</v>
       </c>
       <c r="M680" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="681" spans="1:13">
@@ -17631,7 +17676,7 @@
         <v>1667</v>
       </c>
       <c r="M681" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="682" spans="1:13">
@@ -17648,7 +17693,7 @@
         <v>1667</v>
       </c>
       <c r="M682" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="683" spans="1:13">
@@ -17665,7 +17710,7 @@
         <v>1667</v>
       </c>
       <c r="M683" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="684" spans="1:13">
@@ -17682,7 +17727,7 @@
         <v>1667</v>
       </c>
       <c r="M684" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="685" spans="1:13">
@@ -17699,7 +17744,7 @@
         <v>1667</v>
       </c>
       <c r="M685" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="686" spans="1:13">
@@ -17716,7 +17761,7 @@
         <v>1667</v>
       </c>
       <c r="M686" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="687" spans="1:13">
@@ -17733,7 +17778,7 @@
         <v>1667</v>
       </c>
       <c r="M687" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="688" spans="1:13">
@@ -17750,7 +17795,7 @@
         <v>1667</v>
       </c>
       <c r="M688" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="689" spans="1:13">
@@ -17767,7 +17812,7 @@
         <v>1667</v>
       </c>
       <c r="M689" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="690" spans="1:13">
@@ -17784,7 +17829,7 @@
         <v>1667</v>
       </c>
       <c r="M690" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="691" spans="1:13">
@@ -17801,7 +17846,7 @@
         <v>1667</v>
       </c>
       <c r="M691" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="692" spans="1:13">
@@ -17818,7 +17863,7 @@
         <v>1667</v>
       </c>
       <c r="M692" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="693" spans="1:13">
@@ -17835,7 +17880,7 @@
         <v>1667</v>
       </c>
       <c r="M693" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="694" spans="1:13">
@@ -17852,7 +17897,7 @@
         <v>1667</v>
       </c>
       <c r="M694" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="695" spans="1:13">
@@ -17869,7 +17914,7 @@
         <v>1667</v>
       </c>
       <c r="M695" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="696" spans="1:13">
@@ -17886,7 +17931,7 @@
         <v>1667</v>
       </c>
       <c r="M696" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="697" spans="1:13">
@@ -17903,7 +17948,7 @@
         <v>1667</v>
       </c>
       <c r="M697" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="698" spans="1:13">
@@ -17920,7 +17965,7 @@
         <v>1667</v>
       </c>
       <c r="M698" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="699" spans="1:13">
@@ -17937,7 +17982,7 @@
         <v>1667</v>
       </c>
       <c r="M699" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="700" spans="1:13">
@@ -17954,7 +17999,7 @@
         <v>1667</v>
       </c>
       <c r="M700" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="701" spans="1:13">
@@ -17971,7 +18016,7 @@
         <v>1667</v>
       </c>
       <c r="M701" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="702" spans="1:13">
@@ -17988,7 +18033,7 @@
         <v>1667</v>
       </c>
       <c r="M702" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="703" spans="1:13">
@@ -18005,7 +18050,7 @@
         <v>1667</v>
       </c>
       <c r="M703" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="704" spans="1:13">
@@ -18022,7 +18067,7 @@
         <v>1667</v>
       </c>
       <c r="M704" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="705" spans="1:13">
@@ -18039,7 +18084,7 @@
         <v>1667</v>
       </c>
       <c r="M705" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="706" spans="1:13">
@@ -18056,7 +18101,7 @@
         <v>1667</v>
       </c>
       <c r="M706" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="707" spans="1:13">
@@ -18073,7 +18118,7 @@
         <v>1667</v>
       </c>
       <c r="M707" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="708" spans="1:13">
@@ -18090,7 +18135,7 @@
         <v>1667</v>
       </c>
       <c r="M708" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="709" spans="1:13">
@@ -18107,7 +18152,7 @@
         <v>1667</v>
       </c>
       <c r="M709" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="710" spans="1:13">
@@ -18124,7 +18169,7 @@
         <v>1667</v>
       </c>
       <c r="M710" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="711" spans="1:13">
@@ -18141,7 +18186,7 @@
         <v>1667</v>
       </c>
       <c r="M711" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="712" spans="1:13">
@@ -18158,7 +18203,7 @@
         <v>1667</v>
       </c>
       <c r="M712" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="713" spans="1:13">
@@ -18175,7 +18220,7 @@
         <v>1667</v>
       </c>
       <c r="M713" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="714" spans="1:13">
@@ -18192,7 +18237,7 @@
         <v>1667</v>
       </c>
       <c r="M714" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="715" spans="1:13">
@@ -18209,7 +18254,7 @@
         <v>1667</v>
       </c>
       <c r="M715" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="716" spans="1:13">
@@ -18226,7 +18271,7 @@
         <v>1667</v>
       </c>
       <c r="M716" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="717" spans="1:13">
@@ -18243,7 +18288,7 @@
         <v>1667</v>
       </c>
       <c r="M717" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="718" spans="1:13">
@@ -18260,7 +18305,7 @@
         <v>1667</v>
       </c>
       <c r="M718" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="719" spans="1:13">
@@ -18277,7 +18322,7 @@
         <v>1667</v>
       </c>
       <c r="M719" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="720" spans="1:13">
@@ -18294,7 +18339,7 @@
         <v>1667</v>
       </c>
       <c r="M720" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="721" spans="1:13">
@@ -18311,7 +18356,7 @@
         <v>1667</v>
       </c>
       <c r="M721" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="722" spans="1:13">
@@ -18328,7 +18373,7 @@
         <v>1667</v>
       </c>
       <c r="M722" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="723" spans="1:13">
@@ -18345,7 +18390,7 @@
         <v>1667</v>
       </c>
       <c r="M723" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="724" spans="1:13">
@@ -18362,7 +18407,7 @@
         <v>1667</v>
       </c>
       <c r="M724" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="725" spans="1:13">
@@ -18379,7 +18424,7 @@
         <v>1667</v>
       </c>
       <c r="M725" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="726" spans="1:13">
@@ -18396,7 +18441,7 @@
         <v>1667</v>
       </c>
       <c r="M726" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="727" spans="1:13">
@@ -18413,7 +18458,7 @@
         <v>1667</v>
       </c>
       <c r="M727" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="728" spans="1:13">
@@ -18430,7 +18475,7 @@
         <v>1667</v>
       </c>
       <c r="M728" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="729" spans="1:13">
@@ -18447,7 +18492,7 @@
         <v>1667</v>
       </c>
       <c r="M729" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="730" spans="1:13">
@@ -18464,7 +18509,7 @@
         <v>1667</v>
       </c>
       <c r="M730" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="731" spans="1:13">
@@ -18481,7 +18526,7 @@
         <v>1667</v>
       </c>
       <c r="M731" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="732" spans="1:13">
@@ -18498,7 +18543,7 @@
         <v>1667</v>
       </c>
       <c r="M732" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="733" spans="1:13">
@@ -18515,7 +18560,7 @@
         <v>1667</v>
       </c>
       <c r="M733" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="734" spans="1:13">
@@ -18532,7 +18577,7 @@
         <v>1667</v>
       </c>
       <c r="M734" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="735" spans="1:13">
@@ -18549,7 +18594,7 @@
         <v>1667</v>
       </c>
       <c r="M735" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="736" spans="1:13">
@@ -18566,7 +18611,7 @@
         <v>1667</v>
       </c>
       <c r="M736" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="737" spans="1:13">
@@ -18583,7 +18628,7 @@
         <v>1667</v>
       </c>
       <c r="M737" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="738" spans="1:13">
@@ -18600,7 +18645,7 @@
         <v>1667</v>
       </c>
       <c r="M738" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="739" spans="1:13">
@@ -18617,7 +18662,7 @@
         <v>1667</v>
       </c>
       <c r="M739" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="740" spans="1:13">
@@ -18634,7 +18679,7 @@
         <v>1667</v>
       </c>
       <c r="M740" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="741" spans="1:13">
@@ -18651,7 +18696,7 @@
         <v>1667</v>
       </c>
       <c r="M741" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="742" spans="1:13">
@@ -18668,7 +18713,7 @@
         <v>1667</v>
       </c>
       <c r="M742" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="743" spans="1:13">
@@ -18685,7 +18730,7 @@
         <v>1667</v>
       </c>
       <c r="M743" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="744" spans="1:13">
@@ -18702,7 +18747,7 @@
         <v>1667</v>
       </c>
       <c r="M744" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="745" spans="1:13">
@@ -18719,7 +18764,7 @@
         <v>1667</v>
       </c>
       <c r="M745" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="746" spans="1:13">
@@ -18736,7 +18781,7 @@
         <v>1667</v>
       </c>
       <c r="M746" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="747" spans="1:13">
@@ -18753,7 +18798,7 @@
         <v>1667</v>
       </c>
       <c r="M747" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="748" spans="1:13">
@@ -18770,7 +18815,7 @@
         <v>1667</v>
       </c>
       <c r="M748" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="749" spans="1:13">
@@ -18787,7 +18832,7 @@
         <v>1667</v>
       </c>
       <c r="M749" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="750" spans="1:13">
@@ -18804,7 +18849,7 @@
         <v>1667</v>
       </c>
       <c r="M750" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="751" spans="1:13">
@@ -18821,7 +18866,7 @@
         <v>1667</v>
       </c>
       <c r="M751" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="752" spans="1:13">
@@ -18838,7 +18883,7 @@
         <v>1667</v>
       </c>
       <c r="M752" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="753" spans="1:13">
@@ -18855,7 +18900,7 @@
         <v>1667</v>
       </c>
       <c r="M753" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="754" spans="1:13">
@@ -18872,7 +18917,7 @@
         <v>1667</v>
       </c>
       <c r="M754" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="755" spans="1:13">
@@ -18889,7 +18934,7 @@
         <v>1667</v>
       </c>
       <c r="M755" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="756" spans="1:13">
@@ -18906,7 +18951,7 @@
         <v>1667</v>
       </c>
       <c r="M756" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="757" spans="1:13">
@@ -18923,7 +18968,7 @@
         <v>1667</v>
       </c>
       <c r="M757" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="758" spans="1:13">
@@ -18940,7 +18985,7 @@
         <v>1667</v>
       </c>
       <c r="M758" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="759" spans="1:13">
@@ -18957,7 +19002,7 @@
         <v>1667</v>
       </c>
       <c r="M759" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="760" spans="1:13">
@@ -18974,7 +19019,7 @@
         <v>1667</v>
       </c>
       <c r="M760" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="761" spans="1:13">
@@ -18991,7 +19036,7 @@
         <v>1667</v>
       </c>
       <c r="M761" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="762" spans="1:13">
@@ -19008,7 +19053,7 @@
         <v>1667</v>
       </c>
       <c r="M762" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="763" spans="1:13">
@@ -19025,7 +19070,7 @@
         <v>1667</v>
       </c>
       <c r="M763" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="764" spans="1:13">
@@ -19042,7 +19087,7 @@
         <v>1667</v>
       </c>
       <c r="M764" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="765" spans="1:13">
@@ -19059,7 +19104,7 @@
         <v>1667</v>
       </c>
       <c r="M765" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="766" spans="1:13">
@@ -19076,7 +19121,7 @@
         <v>1667</v>
       </c>
       <c r="M766" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="767" spans="1:13">
@@ -19093,7 +19138,7 @@
         <v>1667</v>
       </c>
       <c r="M767" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="768" spans="1:13">
@@ -19110,7 +19155,7 @@
         <v>1667</v>
       </c>
       <c r="M768" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="769" spans="1:13">
@@ -19127,7 +19172,7 @@
         <v>1667</v>
       </c>
       <c r="M769" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="770" spans="1:13">
@@ -19144,7 +19189,7 @@
         <v>1667</v>
       </c>
       <c r="M770" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="771" spans="1:13">
@@ -19158,7 +19203,7 @@
         <v>866</v>
       </c>
       <c r="M771" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="772" spans="1:13">
@@ -19183,7 +19228,7 @@
         <v>1633</v>
       </c>
       <c r="M773" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="774" spans="1:13">
@@ -19197,7 +19242,7 @@
         <v>897</v>
       </c>
       <c r="M774" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="775" spans="1:13">
@@ -19225,7 +19270,7 @@
         <v>1687</v>
       </c>
       <c r="M776" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="777" spans="1:13">
@@ -19239,7 +19284,7 @@
         <v>1637</v>
       </c>
       <c r="M777" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="778" spans="1:13">
@@ -19253,7 +19298,7 @@
         <v>1638</v>
       </c>
       <c r="M778" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="779" spans="1:13">
@@ -19267,10 +19312,10 @@
         <v>1643</v>
       </c>
       <c r="D779" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="M779" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="780" spans="1:13">
@@ -19284,10 +19329,10 @@
         <v>1647</v>
       </c>
       <c r="D780" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="M780" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="781" spans="1:13">
@@ -19301,10 +19346,10 @@
         <v>1646</v>
       </c>
       <c r="D781" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="M781" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="782" spans="1:13">
@@ -19318,7 +19363,7 @@
         <v>1642</v>
       </c>
       <c r="M782" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="783" spans="1:13">
@@ -19332,10 +19377,10 @@
         <v>1648</v>
       </c>
       <c r="D783" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="M783" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="784" spans="1:13">
@@ -19360,10 +19405,10 @@
         <v>1645</v>
       </c>
       <c r="D785" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="M785" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="786" spans="1:13">
@@ -19388,7 +19433,7 @@
         <v>1649</v>
       </c>
       <c r="M787" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="788" spans="1:13">
@@ -19402,7 +19447,7 @@
         <v>1635</v>
       </c>
       <c r="M788" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="789" spans="1:13">
@@ -19416,7 +19461,7 @@
         <v>1639</v>
       </c>
       <c r="M789" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="790" spans="1:13">
@@ -19430,10 +19475,10 @@
         <v>1641</v>
       </c>
       <c r="D790" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="M790" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="791" spans="1:13">
@@ -19469,7 +19514,7 @@
         <v>1644</v>
       </c>
       <c r="M793" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="794" spans="1:13">
@@ -19483,7 +19528,7 @@
         <v>1654</v>
       </c>
       <c r="M794" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="795" spans="1:13">
@@ -19497,7 +19542,7 @@
         <v>1652</v>
       </c>
       <c r="M795" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="796" spans="1:13">
@@ -19511,7 +19556,7 @@
         <v>1650</v>
       </c>
       <c r="M796" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="797" spans="1:13">
@@ -19536,7 +19581,7 @@
         <v>1636</v>
       </c>
       <c r="M798" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="799" spans="1:13">
@@ -19561,7 +19606,7 @@
         <v>1655</v>
       </c>
       <c r="M800" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="801" spans="1:13">
@@ -19586,7 +19631,7 @@
         <v>1658</v>
       </c>
       <c r="M802" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="803" spans="1:13">
@@ -19614,7 +19659,7 @@
         <v>1667</v>
       </c>
       <c r="M804" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="805" spans="1:13">
@@ -19631,7 +19676,7 @@
         <v>1667</v>
       </c>
       <c r="M805" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="806" spans="1:13">
@@ -19648,7 +19693,7 @@
         <v>1667</v>
       </c>
       <c r="M806" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="807" spans="1:13">
@@ -19665,7 +19710,7 @@
         <v>1667</v>
       </c>
       <c r="M807" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="808" spans="1:13">
@@ -19682,7 +19727,7 @@
         <v>1667</v>
       </c>
       <c r="M808" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="809" spans="1:13">
@@ -19699,7 +19744,7 @@
         <v>1667</v>
       </c>
       <c r="M809" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="810" spans="1:13">
@@ -19716,7 +19761,7 @@
         <v>1667</v>
       </c>
       <c r="M810" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="811" spans="1:13">
@@ -19733,7 +19778,7 @@
         <v>1667</v>
       </c>
       <c r="M811" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="812" spans="1:13">
@@ -19750,7 +19795,7 @@
         <v>1667</v>
       </c>
       <c r="M812" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="813" spans="1:13">
@@ -19767,7 +19812,7 @@
         <v>1667</v>
       </c>
       <c r="M813" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="814" spans="1:13">
@@ -19784,7 +19829,7 @@
         <v>1667</v>
       </c>
       <c r="M814" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="815" spans="1:13">
@@ -19801,7 +19846,7 @@
         <v>1667</v>
       </c>
       <c r="M815" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="816" spans="1:13">
@@ -19818,7 +19863,7 @@
         <v>1667</v>
       </c>
       <c r="M816" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="817" spans="1:13">
@@ -19835,7 +19880,7 @@
         <v>1667</v>
       </c>
       <c r="M817" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="818" spans="1:13">
@@ -19852,7 +19897,7 @@
         <v>1667</v>
       </c>
       <c r="M818" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="819" spans="1:13">
@@ -19869,7 +19914,7 @@
         <v>1667</v>
       </c>
       <c r="M819" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="820" spans="1:13">
@@ -19886,7 +19931,7 @@
         <v>1667</v>
       </c>
       <c r="M820" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
   </sheetData>
